--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A9544-3E11-4EA9-B23C-23EBA65A32C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27EB698-17A0-47D2-BA46-1841B06D33BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3400" yWindow="7820" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$122</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="194">
   <si>
     <t>lang_code</t>
   </si>
@@ -613,6 +613,12 @@
   </si>
   <si>
     <t>Ciudad</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>Utopia</t>
   </si>
 </sst>
 </file>
@@ -776,9 +782,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -816,7 +822,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -922,7 +928,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,7 +1070,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1073,7 +1079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G281"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
@@ -1113,10 +1119,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>193</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1130,19 +1136,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
@@ -1150,19 +1156,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>11</v>
@@ -1170,22 +1176,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -1193,19 +1196,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1216,19 +1219,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1239,22 +1242,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>11</v>
@@ -1262,19 +1265,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -1285,19 +1288,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -1308,22 +1311,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
@@ -1331,19 +1334,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -1354,19 +1357,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -1377,22 +1380,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
@@ -1400,19 +1403,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -1423,19 +1426,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
         <v>31</v>
@@ -1446,42 +1449,42 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="22.5">
-      <c r="A18" t="s">
-        <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18">
-        <v>14022</v>
+      <c r="C18" t="s">
+        <v>40</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>42</v>
+      <c r="E18" t="s">
+        <v>41</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
@@ -1490,21 +1493,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" ht="22.5">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
-        <v>40</v>
+      <c r="C19">
+        <v>14022</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
-      <c r="E19" t="s">
-        <v>43</v>
+      <c r="E19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F19" t="s">
         <v>35</v>
@@ -1515,22 +1518,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>11</v>
@@ -1538,19 +1541,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
         <v>31</v>
@@ -1561,19 +1564,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
         <v>31</v>
@@ -1584,42 +1587,42 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
         <v>7</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="22.5">
-      <c r="A24" t="s">
-        <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C24">
-        <v>14053</v>
+      <c r="C24" t="s">
+        <v>47</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>42</v>
+      <c r="E24" t="s">
+        <v>41</v>
       </c>
       <c r="F24" t="s">
         <v>44</v>
@@ -1628,21 +1631,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" ht="22.5">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C25" t="s">
-        <v>47</v>
+      <c r="C25">
+        <v>14053</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" t="s">
-        <v>43</v>
+      <c r="E25" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>44</v>
@@ -1653,22 +1656,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>11</v>
@@ -1676,19 +1679,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
@@ -1699,19 +1702,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
         <v>31</v>
@@ -1722,42 +1725,42 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
         <v>7</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="22.5">
-      <c r="A30" t="s">
-        <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C30">
-        <v>14023</v>
+      <c r="C30" t="s">
+        <v>51</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>42</v>
+      <c r="E30" t="s">
+        <v>41</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
@@ -1766,21 +1769,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="22.5">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C31" t="s">
-        <v>51</v>
+      <c r="C31">
+        <v>14023</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
-      <c r="E31" t="s">
-        <v>43</v>
+      <c r="E31" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F31" t="s">
         <v>48</v>
@@ -1791,22 +1794,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>11</v>
@@ -1814,19 +1817,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -1837,19 +1840,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F34" t="s">
         <v>31</v>
@@ -1860,42 +1863,42 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
         <v>7</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="22.5">
-      <c r="A36" t="s">
-        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C36">
-        <v>14000</v>
+      <c r="C36" t="s">
+        <v>55</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>42</v>
+      <c r="E36" t="s">
+        <v>41</v>
       </c>
       <c r="F36" t="s">
         <v>52</v>
@@ -1904,21 +1907,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" ht="22.5">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C37" t="s">
-        <v>55</v>
+      <c r="C37">
+        <v>14000</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="E37" t="s">
-        <v>43</v>
+      <c r="E37" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F37" t="s">
         <v>52</v>
@@ -1929,22 +1932,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>11</v>
@@ -1952,19 +1955,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
         <v>31</v>
@@ -1975,19 +1978,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s">
         <v>31</v>
@@ -1998,42 +2001,42 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
         <v>7</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="22.5">
-      <c r="A42" t="s">
-        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C42">
-        <v>14110</v>
+      <c r="C42" t="s">
+        <v>59</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>42</v>
+      <c r="E42" t="s">
+        <v>41</v>
       </c>
       <c r="F42" t="s">
         <v>56</v>
@@ -2042,21 +2045,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" ht="22.5">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C43" t="s">
-        <v>59</v>
+      <c r="C43">
+        <v>14110</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
-      <c r="E43" t="s">
-        <v>43</v>
+      <c r="E43" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F43" t="s">
         <v>56</v>
@@ -2067,22 +2070,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>11</v>
@@ -2090,19 +2093,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
@@ -2113,19 +2116,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
@@ -2136,42 +2139,42 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
         <v>7</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" t="s">
-        <v>63</v>
-      </c>
-      <c r="D47">
-        <v>5</v>
-      </c>
-      <c r="E47" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="22.5">
-      <c r="A48" t="s">
-        <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C48">
-        <v>14080</v>
+      <c r="C48" t="s">
+        <v>63</v>
       </c>
       <c r="D48">
         <v>5</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>42</v>
+      <c r="E48" t="s">
+        <v>41</v>
       </c>
       <c r="F48" t="s">
         <v>60</v>
@@ -2180,21 +2183,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" ht="22.5">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C49" t="s">
-        <v>63</v>
+      <c r="C49">
+        <v>14080</v>
       </c>
       <c r="D49">
         <v>5</v>
       </c>
-      <c r="E49" t="s">
-        <v>43</v>
+      <c r="E49" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F49" t="s">
         <v>60</v>
@@ -2205,22 +2208,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>11</v>
@@ -2228,19 +2231,19 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F51" t="s">
         <v>31</v>
@@ -2251,19 +2254,19 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F52" t="s">
         <v>31</v>
@@ -2274,42 +2277,42 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
         <v>7</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53">
-        <v>5</v>
-      </c>
-      <c r="E53" t="s">
-        <v>41</v>
-      </c>
-      <c r="F53" t="s">
-        <v>64</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="22.5">
-      <c r="A54" t="s">
-        <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C54">
-        <v>14025</v>
+      <c r="C54" t="s">
+        <v>67</v>
       </c>
       <c r="D54">
         <v>5</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>42</v>
+      <c r="E54" t="s">
+        <v>41</v>
       </c>
       <c r="F54" t="s">
         <v>64</v>
@@ -2318,21 +2321,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" ht="22.5">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C55" t="s">
-        <v>67</v>
+      <c r="C55">
+        <v>14025</v>
       </c>
       <c r="D55">
         <v>5</v>
       </c>
-      <c r="E55" t="s">
-        <v>43</v>
+      <c r="E55" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F55" t="s">
         <v>64</v>
@@ -2343,22 +2346,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>11</v>
@@ -2366,19 +2369,19 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -2389,19 +2392,19 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
@@ -2412,42 +2415,42 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
         <v>7</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59">
-        <v>5</v>
-      </c>
-      <c r="E59" t="s">
-        <v>41</v>
-      </c>
-      <c r="F59" t="s">
-        <v>68</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="22.5">
-      <c r="A60" t="s">
-        <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C60">
-        <v>14050</v>
+      <c r="C60" t="s">
+        <v>71</v>
       </c>
       <c r="D60">
         <v>5</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>42</v>
+      <c r="E60" t="s">
+        <v>41</v>
       </c>
       <c r="F60" t="s">
         <v>68</v>
@@ -2456,21 +2459,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" ht="22.5">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C61" t="s">
-        <v>71</v>
+      <c r="C61">
+        <v>14050</v>
       </c>
       <c r="D61">
         <v>5</v>
       </c>
-      <c r="E61" t="s">
-        <v>43</v>
+      <c r="E61" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F61" t="s">
         <v>68</v>
@@ -2481,22 +2484,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>11</v>
@@ -2504,19 +2507,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -2527,19 +2530,19 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -2550,22 +2553,22 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
         <v>73</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>11</v>
@@ -2573,19 +2576,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
         <v>72</v>
@@ -2596,19 +2599,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
         <v>72</v>
@@ -2619,22 +2622,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>11</v>
@@ -2642,19 +2645,19 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
         <v>75</v>
@@ -2665,19 +2668,19 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F70" t="s">
         <v>75</v>
@@ -2688,42 +2691,42 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" t="s">
+        <v>75</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
         <v>7</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" t="s">
-        <v>79</v>
-      </c>
-      <c r="D71">
-        <v>5</v>
-      </c>
-      <c r="E71" t="s">
-        <v>41</v>
-      </c>
-      <c r="F71" t="s">
-        <v>76</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="22.5">
-      <c r="A72" t="s">
-        <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C72">
-        <v>10106</v>
+      <c r="C72" t="s">
+        <v>79</v>
       </c>
       <c r="D72">
         <v>5</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>42</v>
+      <c r="E72" t="s">
+        <v>41</v>
       </c>
       <c r="F72" t="s">
         <v>76</v>
@@ -2732,21 +2735,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" ht="22.5">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C73" t="s">
-        <v>79</v>
+      <c r="C73">
+        <v>10106</v>
       </c>
       <c r="D73">
         <v>5</v>
       </c>
-      <c r="E73" t="s">
-        <v>43</v>
+      <c r="E73" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F73" t="s">
         <v>76</v>
@@ -2757,22 +2760,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>11</v>
@@ -2780,19 +2783,19 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F75" t="s">
         <v>75</v>
@@ -2803,19 +2806,19 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F76" t="s">
         <v>75</v>
@@ -2826,42 +2829,42 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77" t="s">
+        <v>37</v>
+      </c>
+      <c r="F77" t="s">
+        <v>75</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
         <v>7</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77">
-        <v>5</v>
-      </c>
-      <c r="E77" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" t="s">
-        <v>80</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="22.5">
-      <c r="A78" t="s">
-        <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C78">
-        <v>10000</v>
+      <c r="C78" t="s">
+        <v>83</v>
       </c>
       <c r="D78">
         <v>5</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>42</v>
+      <c r="E78" t="s">
+        <v>41</v>
       </c>
       <c r="F78" t="s">
         <v>80</v>
@@ -2870,21 +2873,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" ht="22.5">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C79" t="s">
-        <v>83</v>
+      <c r="C79">
+        <v>10000</v>
       </c>
       <c r="D79">
         <v>5</v>
       </c>
-      <c r="E79" t="s">
-        <v>43</v>
+      <c r="E79" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F79" t="s">
         <v>80</v>
@@ -2895,22 +2898,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>11</v>
@@ -2918,19 +2921,19 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F81" t="s">
         <v>75</v>
@@ -2941,19 +2944,19 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D82">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
         <v>75</v>
@@ -2964,42 +2967,42 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" t="s">
+        <v>75</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
         <v>7</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" t="s">
-        <v>87</v>
-      </c>
-      <c r="D83">
-        <v>5</v>
-      </c>
-      <c r="E83" t="s">
-        <v>41</v>
-      </c>
-      <c r="F83" t="s">
-        <v>84</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="22.5">
-      <c r="A84" t="s">
-        <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C84">
-        <v>10105</v>
+      <c r="C84" t="s">
+        <v>87</v>
       </c>
       <c r="D84">
         <v>5</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>42</v>
+      <c r="E84" t="s">
+        <v>41</v>
       </c>
       <c r="F84" t="s">
         <v>84</v>
@@ -3008,21 +3011,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" ht="22.5">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C85" t="s">
-        <v>87</v>
+      <c r="C85">
+        <v>10105</v>
       </c>
       <c r="D85">
         <v>5</v>
       </c>
-      <c r="E85" t="s">
-        <v>43</v>
+      <c r="E85" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F85" t="s">
         <v>84</v>
@@ -3033,22 +3036,22 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F86" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>11</v>
@@ -3056,19 +3059,19 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F87" t="s">
         <v>75</v>
@@ -3079,19 +3082,19 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D88">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F88" t="s">
         <v>75</v>
@@ -3102,42 +3105,42 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" t="s">
+        <v>75</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
         <v>7</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" t="s">
-        <v>91</v>
-      </c>
-      <c r="D89">
-        <v>5</v>
-      </c>
-      <c r="E89" t="s">
-        <v>41</v>
-      </c>
-      <c r="F89" t="s">
-        <v>88</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="22.5">
-      <c r="A90" t="s">
-        <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C90">
-        <v>10112</v>
+      <c r="C90" t="s">
+        <v>91</v>
       </c>
       <c r="D90">
         <v>5</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>42</v>
+      <c r="E90" t="s">
+        <v>41</v>
       </c>
       <c r="F90" t="s">
         <v>88</v>
@@ -3146,21 +3149,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" ht="22.5">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C91" t="s">
-        <v>91</v>
+      <c r="C91">
+        <v>10112</v>
       </c>
       <c r="D91">
         <v>5</v>
       </c>
-      <c r="E91" t="s">
-        <v>43</v>
+      <c r="E91" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F91" t="s">
         <v>88</v>
@@ -3171,22 +3174,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>11</v>
@@ -3194,19 +3197,19 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F93" t="s">
         <v>75</v>
@@ -3217,19 +3220,19 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F94" t="s">
         <v>75</v>
@@ -3240,42 +3243,42 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C95" t="s">
+        <v>93</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" t="s">
+        <v>75</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
         <v>7</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C95" t="s">
-        <v>95</v>
-      </c>
-      <c r="D95">
-        <v>5</v>
-      </c>
-      <c r="E95" t="s">
-        <v>41</v>
-      </c>
-      <c r="F95" t="s">
-        <v>92</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="22.5">
-      <c r="A96" t="s">
-        <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C96">
-        <v>10104</v>
+      <c r="C96" t="s">
+        <v>95</v>
       </c>
       <c r="D96">
         <v>5</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>42</v>
+      <c r="E96" t="s">
+        <v>41</v>
       </c>
       <c r="F96" t="s">
         <v>92</v>
@@ -3284,21 +3287,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" ht="22.5">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C97" t="s">
-        <v>95</v>
+      <c r="C97">
+        <v>10104</v>
       </c>
       <c r="D97">
         <v>5</v>
       </c>
-      <c r="E97" t="s">
-        <v>43</v>
+      <c r="E97" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F97" t="s">
         <v>92</v>
@@ -3309,22 +3312,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C98" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F98" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>11</v>
@@ -3332,19 +3335,19 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F99" t="s">
         <v>75</v>
@@ -3355,19 +3358,19 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100">
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F100" t="s">
         <v>75</v>
@@ -3378,42 +3381,42 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" t="s">
+        <v>99</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" t="s">
+        <v>75</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
         <v>7</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C101" t="s">
-        <v>100</v>
-      </c>
-      <c r="D101">
-        <v>5</v>
-      </c>
-      <c r="E101" t="s">
-        <v>41</v>
-      </c>
-      <c r="F101" t="s">
-        <v>96</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="22.5">
-      <c r="A102" t="s">
-        <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C102">
-        <v>10036</v>
+      <c r="C102" t="s">
+        <v>100</v>
       </c>
       <c r="D102">
         <v>5</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>42</v>
+      <c r="E102" t="s">
+        <v>41</v>
       </c>
       <c r="F102" t="s">
         <v>96</v>
@@ -3422,21 +3425,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" ht="22.5">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C103" t="s">
-        <v>100</v>
+      <c r="C103">
+        <v>10036</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
-      <c r="E103" t="s">
-        <v>43</v>
+      <c r="E103" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F103" t="s">
         <v>96</v>
@@ -3447,22 +3450,22 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>11</v>
@@ -3470,19 +3473,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F105" t="s">
         <v>75</v>
@@ -3493,19 +3496,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F106" t="s">
         <v>75</v>
@@ -3516,42 +3519,42 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107">
+        <v>4</v>
+      </c>
+      <c r="E107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
         <v>7</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C107" t="s">
-        <v>104</v>
-      </c>
-      <c r="D107">
-        <v>5</v>
-      </c>
-      <c r="E107" t="s">
-        <v>41</v>
-      </c>
-      <c r="F107" t="s">
-        <v>101</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="22.5">
-      <c r="A108" t="s">
-        <v>12</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C108">
-        <v>10190</v>
+      <c r="C108" t="s">
+        <v>104</v>
       </c>
       <c r="D108">
         <v>5</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>42</v>
+      <c r="E108" t="s">
+        <v>41</v>
       </c>
       <c r="F108" t="s">
         <v>101</v>
@@ -3560,21 +3563,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" ht="22.5">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C109" t="s">
-        <v>104</v>
+      <c r="C109">
+        <v>10190</v>
       </c>
       <c r="D109">
         <v>5</v>
       </c>
-      <c r="E109" t="s">
-        <v>43</v>
+      <c r="E109" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F109" t="s">
         <v>101</v>
@@ -3585,22 +3588,22 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>11</v>
@@ -3611,10 +3614,10 @@
         <v>7</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D111">
         <v>5</v>
@@ -3634,10 +3637,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D112">
         <v>5</v>
@@ -3657,10 +3660,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D113">
         <v>5</v>
@@ -3677,19 +3680,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F114" t="s">
         <v>35</v>
@@ -3703,10 +3706,10 @@
         <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D115">
         <v>5</v>
@@ -3726,10 +3729,10 @@
         <v>15</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D116">
         <v>5</v>
@@ -3749,10 +3752,10 @@
         <v>15</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C117">
-        <v>10114</v>
+        <v>107</v>
+      </c>
+      <c r="C117" t="s">
+        <v>107</v>
       </c>
       <c r="D117">
         <v>5</v>
@@ -3767,21 +3770,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="22.5">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C118">
-        <v>10111</v>
+        <v>10114</v>
       </c>
       <c r="D118">
         <v>5</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>42</v>
+      <c r="E118" t="s">
+        <v>43</v>
       </c>
       <c r="F118" t="s">
         <v>35</v>
@@ -3795,10 +3798,10 @@
         <v>12</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C119">
-        <v>10114</v>
+        <v>10111</v>
       </c>
       <c r="D119">
         <v>5</v>
@@ -3818,10 +3821,10 @@
         <v>12</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C120">
-        <v>10113</v>
+        <v>10114</v>
       </c>
       <c r="D120">
         <v>5</v>
@@ -3841,10 +3844,10 @@
         <v>12</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C121">
-        <v>10110</v>
+        <v>10113</v>
       </c>
       <c r="D121">
         <v>5</v>
@@ -3859,21 +3862,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" ht="22.5">
       <c r="A122" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="C122">
+        <v>10110</v>
       </c>
       <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="E122" t="s">
-        <v>111</v>
+        <v>5</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" t="s">
+        <v>35</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>11</v>
@@ -3884,19 +3890,16 @@
         <v>109</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>113</v>
-      </c>
-      <c r="F123" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>11</v>
@@ -3907,19 +3910,19 @@
         <v>109</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F124" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>11</v>
@@ -3930,19 +3933,19 @@
         <v>109</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C125" t="s">
         <v>114</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>11</v>
@@ -3953,19 +3956,19 @@
         <v>109</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E126" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F126" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>11</v>
@@ -3976,19 +3979,19 @@
         <v>109</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C127" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="D127">
-        <v>5</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="E127" t="s">
+        <v>118</v>
       </c>
       <c r="F127" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>11</v>
@@ -3999,19 +4002,19 @@
         <v>109</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>11</v>
@@ -4022,19 +4025,19 @@
         <v>109</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C129" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F129" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>11</v>
@@ -4045,19 +4048,19 @@
         <v>109</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C130" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>11</v>
@@ -4068,19 +4071,19 @@
         <v>109</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F131" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>11</v>
@@ -4091,19 +4094,19 @@
         <v>109</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F132" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>11</v>
@@ -4114,19 +4117,19 @@
         <v>109</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="D133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F133" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>11</v>
@@ -4137,19 +4140,19 @@
         <v>109</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="D134">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F134" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>11</v>
@@ -4160,19 +4163,19 @@
         <v>109</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C135" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F135" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>11</v>
@@ -4183,19 +4186,19 @@
         <v>109</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C136" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F136" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>11</v>
@@ -4206,19 +4209,19 @@
         <v>109</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C137" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F137" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>11</v>
@@ -4229,19 +4232,19 @@
         <v>109</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C138" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="D138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F138" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>11</v>
@@ -4252,19 +4255,19 @@
         <v>109</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C139" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F139" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>11</v>
@@ -4275,19 +4278,19 @@
         <v>109</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C140" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="D140">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F140" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>11</v>
@@ -4298,19 +4301,19 @@
         <v>109</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C141" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F141" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>11</v>
@@ -4321,19 +4324,19 @@
         <v>109</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="D142">
-        <v>2</v>
-      </c>
-      <c r="E142" t="s">
-        <v>115</v>
+        <v>5</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="F142" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>11</v>
@@ -4344,19 +4347,19 @@
         <v>109</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C143" t="s">
         <v>127</v>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F143" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>11</v>
@@ -4367,19 +4370,19 @@
         <v>109</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D144">
-        <v>4</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>118</v>
+        <v>3</v>
+      </c>
+      <c r="E144" t="s">
+        <v>116</v>
       </c>
       <c r="F144" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>11</v>
@@ -4390,19 +4393,19 @@
         <v>109</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C145" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>11</v>
@@ -4413,19 +4416,19 @@
         <v>109</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F146" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>11</v>
@@ -4436,19 +4439,19 @@
         <v>109</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C147" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F147" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>11</v>
@@ -4459,19 +4462,19 @@
         <v>109</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="D148">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F148" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>11</v>
@@ -4482,19 +4485,19 @@
         <v>109</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C149" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F149" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>11</v>
@@ -4505,19 +4508,19 @@
         <v>109</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="D150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F150" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>11</v>
@@ -4528,19 +4531,19 @@
         <v>109</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F151" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>11</v>
@@ -4551,19 +4554,19 @@
         <v>109</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C152" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="D152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F152" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>11</v>
@@ -4574,19 +4577,19 @@
         <v>109</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C153" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F153" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>11</v>
@@ -4597,19 +4600,19 @@
         <v>109</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F154" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>11</v>
@@ -4620,19 +4623,19 @@
         <v>109</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C155" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D155">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F155" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>11</v>
@@ -4643,19 +4646,19 @@
         <v>109</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F156" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>11</v>
@@ -4666,19 +4669,19 @@
         <v>109</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C157" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D157">
-        <v>5</v>
-      </c>
-      <c r="E157" t="s">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F157" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>11</v>
@@ -4689,10 +4692,10 @@
         <v>109</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C158" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D158">
         <v>5</v>
@@ -4701,7 +4704,7 @@
         <v>119</v>
       </c>
       <c r="F158" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>11</v>
@@ -4712,10 +4715,10 @@
         <v>109</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D159">
         <v>5</v>
@@ -4735,10 +4738,10 @@
         <v>109</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D160">
         <v>5</v>
@@ -4758,10 +4761,10 @@
         <v>109</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D161">
         <v>5</v>
@@ -4778,19 +4781,22 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="C162" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>137</v>
+        <v>119</v>
+      </c>
+      <c r="F162" t="s">
+        <v>35</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>11</v>
@@ -4801,19 +4807,16 @@
         <v>135</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="s">
-        <v>139</v>
-      </c>
-      <c r="F163" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>11</v>
@@ -4824,19 +4827,19 @@
         <v>135</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C164" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F164" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>11</v>
@@ -4847,19 +4850,19 @@
         <v>135</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C165" t="s">
         <v>140</v>
       </c>
       <c r="D165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>11</v>
@@ -4870,19 +4873,19 @@
         <v>135</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C166" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E166" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F166" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>11</v>
@@ -4893,19 +4896,19 @@
         <v>135</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="D167">
-        <v>5</v>
-      </c>
-      <c r="E167" s="5" t="s">
-        <v>145</v>
+        <v>4</v>
+      </c>
+      <c r="E167" t="s">
+        <v>144</v>
       </c>
       <c r="F167" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>11</v>
@@ -4916,19 +4919,19 @@
         <v>135</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C168" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F168" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>11</v>
@@ -4939,19 +4942,19 @@
         <v>135</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C169" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F169" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>11</v>
@@ -4962,19 +4965,19 @@
         <v>135</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="D170">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F170" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>11</v>
@@ -4985,19 +4988,19 @@
         <v>135</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F171" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>11</v>
@@ -5008,19 +5011,19 @@
         <v>135</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C172" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="D172">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F172" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>11</v>
@@ -5031,19 +5034,19 @@
         <v>135</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C173" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F173" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>11</v>
@@ -5054,19 +5057,19 @@
         <v>135</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F174" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>11</v>
@@ -5077,19 +5080,19 @@
         <v>135</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C175" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F175" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>11</v>
@@ -5100,19 +5103,19 @@
         <v>135</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C176" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="D176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F176" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>11</v>
@@ -5123,19 +5126,19 @@
         <v>135</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C177" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="D177">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F177" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>11</v>
@@ -5146,19 +5149,19 @@
         <v>135</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C178" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F178" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>11</v>
@@ -5169,19 +5172,19 @@
         <v>135</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D179">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F179" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>11</v>
@@ -5192,19 +5195,19 @@
         <v>135</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C180" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="D180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F180" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>11</v>
@@ -5215,19 +5218,19 @@
         <v>135</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C181" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F181" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>11</v>
@@ -5238,19 +5241,19 @@
         <v>135</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C182" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="D182">
-        <v>2</v>
-      </c>
-      <c r="E182" t="s">
-        <v>141</v>
+        <v>5</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="F182" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>11</v>
@@ -5261,19 +5264,19 @@
         <v>135</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C183" t="s">
         <v>153</v>
       </c>
       <c r="D183">
-        <v>3</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>142</v>
+        <v>2</v>
+      </c>
+      <c r="E183" t="s">
+        <v>141</v>
       </c>
       <c r="F183" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>11</v>
@@ -5284,19 +5287,19 @@
         <v>135</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F184" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>11</v>
@@ -5307,19 +5310,19 @@
         <v>135</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C185" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F185" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>11</v>
@@ -5330,19 +5333,19 @@
         <v>135</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C186" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>11</v>
@@ -5353,19 +5356,19 @@
         <v>135</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C187" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F187" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>11</v>
@@ -5376,19 +5379,19 @@
         <v>135</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C188" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D188">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>11</v>
@@ -5399,19 +5402,19 @@
         <v>135</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C189" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F189" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>11</v>
@@ -5422,19 +5425,19 @@
         <v>135</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C190" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F190" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>11</v>
@@ -5445,19 +5448,19 @@
         <v>135</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C191" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="D191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F191" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>11</v>
@@ -5468,19 +5471,19 @@
         <v>135</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C192" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F192" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>11</v>
@@ -5491,19 +5494,19 @@
         <v>135</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C193" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F193" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>11</v>
@@ -5514,19 +5517,19 @@
         <v>135</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C194" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="D194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F194" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>11</v>
@@ -5537,19 +5540,19 @@
         <v>135</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C195" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="D195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F195" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>11</v>
@@ -5560,19 +5563,19 @@
         <v>135</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F196" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>11</v>
@@ -5583,19 +5586,19 @@
         <v>135</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C197" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="D197">
-        <v>5</v>
-      </c>
-      <c r="E197" t="s">
-        <v>145</v>
+        <v>4</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="F197" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>11</v>
@@ -5606,10 +5609,10 @@
         <v>135</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C198" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -5618,7 +5621,7 @@
         <v>145</v>
       </c>
       <c r="F198" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>11</v>
@@ -5629,10 +5632,10 @@
         <v>135</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C199" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -5652,10 +5655,10 @@
         <v>135</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C200" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D200">
         <v>5</v>
@@ -5675,10 +5678,10 @@
         <v>135</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C201" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D201">
         <v>5</v>
@@ -5695,19 +5698,22 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="C202" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E202" t="s">
-        <v>162</v>
+        <v>145</v>
+      </c>
+      <c r="F202" t="s">
+        <v>35</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>11</v>
@@ -5718,19 +5724,16 @@
         <v>161</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>164</v>
-      </c>
-      <c r="F203" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>11</v>
@@ -5741,19 +5744,19 @@
         <v>161</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C204" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F204" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>11</v>
@@ -5764,19 +5767,19 @@
         <v>161</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C205" t="s">
         <v>165</v>
       </c>
       <c r="D205">
-        <v>3</v>
-      </c>
-      <c r="E205" s="5" t="s">
-        <v>167</v>
+        <v>2</v>
+      </c>
+      <c r="E205" t="s">
+        <v>166</v>
       </c>
       <c r="F205" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>11</v>
@@ -5787,19 +5790,19 @@
         <v>161</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C206" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D206">
-        <v>4</v>
-      </c>
-      <c r="E206" t="s">
-        <v>169</v>
+        <v>3</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="F206" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>11</v>
@@ -5810,19 +5813,19 @@
         <v>161</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C207" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="D207">
-        <v>5</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>170</v>
+        <v>4</v>
+      </c>
+      <c r="E207" t="s">
+        <v>169</v>
       </c>
       <c r="F207" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>11</v>
@@ -5833,19 +5836,19 @@
         <v>161</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="D208">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F208" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>11</v>
@@ -5856,19 +5859,19 @@
         <v>161</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="D209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F209" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>11</v>
@@ -5879,19 +5882,19 @@
         <v>161</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C210" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="D210">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F210" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>11</v>
@@ -5902,19 +5905,19 @@
         <v>161</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C211" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
       <c r="D211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F211" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>11</v>
@@ -5925,19 +5928,19 @@
         <v>161</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C212" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="D212">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F212" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>11</v>
@@ -5948,19 +5951,19 @@
         <v>161</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C213" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F213" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>11</v>
@@ -5971,19 +5974,19 @@
         <v>161</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F214" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>11</v>
@@ -5994,19 +5997,19 @@
         <v>161</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C215" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F215" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>11</v>
@@ -6017,19 +6020,19 @@
         <v>161</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C216" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="D216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F216" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>11</v>
@@ -6040,19 +6043,19 @@
         <v>161</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C217" t="s">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="D217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F217" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>11</v>
@@ -6063,19 +6066,19 @@
         <v>161</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="D218">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F218" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>11</v>
@@ -6086,19 +6089,19 @@
         <v>161</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C219" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="D219">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F219" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>11</v>
@@ -6109,19 +6112,19 @@
         <v>161</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C220" t="s">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="D220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F220" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>11</v>
@@ -6132,19 +6135,19 @@
         <v>161</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C221" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="D221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F221" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>11</v>
@@ -6155,19 +6158,19 @@
         <v>161</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C222" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F222" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>11</v>
@@ -6178,19 +6181,19 @@
         <v>161</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C223" t="s">
         <v>177</v>
       </c>
       <c r="D223">
-        <v>3</v>
-      </c>
-      <c r="E223" t="s">
-        <v>167</v>
+        <v>2</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="F223" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>11</v>
@@ -6201,19 +6204,19 @@
         <v>161</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C224" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D224">
-        <v>4</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>169</v>
+        <v>3</v>
+      </c>
+      <c r="E224" t="s">
+        <v>167</v>
       </c>
       <c r="F224" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>11</v>
@@ -6224,19 +6227,19 @@
         <v>161</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C225" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F225" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>11</v>
@@ -6247,19 +6250,19 @@
         <v>161</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="D226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F226" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>11</v>
@@ -6270,19 +6273,19 @@
         <v>161</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C227" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F227" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>11</v>
@@ -6293,19 +6296,19 @@
         <v>161</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C228" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F228" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>11</v>
@@ -6316,19 +6319,19 @@
         <v>161</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C229" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F229" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>11</v>
@@ -6339,19 +6342,19 @@
         <v>161</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="D230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F230" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>11</v>
@@ -6362,19 +6365,19 @@
         <v>161</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C231" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="D231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F231" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>11</v>
@@ -6385,19 +6388,19 @@
         <v>161</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C232" t="s">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="D232">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F232" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>11</v>
@@ -6408,19 +6411,19 @@
         <v>161</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C233" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="D233">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F233" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>11</v>
@@ -6431,19 +6434,19 @@
         <v>161</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F234" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>11</v>
@@ -6454,19 +6457,19 @@
         <v>161</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C235" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="D235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F235" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>11</v>
@@ -6477,19 +6480,19 @@
         <v>161</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C236" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="D236">
-        <v>4</v>
-      </c>
-      <c r="E236" t="s">
-        <v>169</v>
+        <v>5</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="F236" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>11</v>
@@ -6500,19 +6503,19 @@
         <v>161</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C237" t="s">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E237" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F237" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>11</v>
@@ -6523,10 +6526,10 @@
         <v>161</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C238" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D238">
         <v>5</v>
@@ -6535,7 +6538,7 @@
         <v>170</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>11</v>
@@ -6546,10 +6549,10 @@
         <v>161</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C239" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D239">
         <v>5</v>
@@ -6569,10 +6572,10 @@
         <v>161</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C240" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D240">
         <v>5</v>
@@ -6592,10 +6595,10 @@
         <v>161</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C241" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D241">
         <v>5</v>
@@ -6612,45 +6615,45 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>184</v>
-      </c>
-      <c r="B242" t="s">
-        <v>88</v>
+        <v>161</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C242" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F242" t="s">
-        <v>75</v>
-      </c>
-      <c r="G242" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
         <v>184</v>
       </c>
-      <c r="B243">
-        <v>10114</v>
-      </c>
-      <c r="C243">
-        <v>10114</v>
+      <c r="B243" t="s">
+        <v>88</v>
+      </c>
+      <c r="C243" t="s">
+        <v>89</v>
       </c>
       <c r="D243">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E243" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
@@ -6660,17 +6663,20 @@
       <c r="A244" t="s">
         <v>184</v>
       </c>
-      <c r="B244" t="s">
-        <v>8</v>
-      </c>
-      <c r="C244" t="s">
-        <v>187</v>
+      <c r="B244">
+        <v>10114</v>
+      </c>
+      <c r="C244">
+        <v>10114</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
-        <v>188</v>
+        <v>186</v>
+      </c>
+      <c r="F244" t="s">
+        <v>35</v>
       </c>
       <c r="G244" t="b">
         <v>1</v>
@@ -6681,19 +6687,16 @@
         <v>184</v>
       </c>
       <c r="B245" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E245" t="s">
-        <v>189</v>
-      </c>
-      <c r="F245" t="s">
-        <v>8</v>
+        <v>188</v>
       </c>
       <c r="G245" t="b">
         <v>1</v>
@@ -6704,19 +6707,19 @@
         <v>184</v>
       </c>
       <c r="B246" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C246" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F246" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G246" t="b">
         <v>1</v>
@@ -6727,19 +6730,19 @@
         <v>184</v>
       </c>
       <c r="B247" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C247" t="s">
         <v>26</v>
       </c>
       <c r="D247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F247" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G247" t="b">
         <v>1</v>
@@ -6750,19 +6753,19 @@
         <v>184</v>
       </c>
       <c r="B248" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C248" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D248">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E248" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F248" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
@@ -6772,20 +6775,20 @@
       <c r="A249" t="s">
         <v>184</v>
       </c>
-      <c r="B249">
-        <v>14022</v>
-      </c>
-      <c r="C249">
-        <v>14022</v>
+      <c r="B249" t="s">
+        <v>35</v>
+      </c>
+      <c r="C249" t="s">
+        <v>36</v>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E249" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F249" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G249" t="b">
         <v>1</v>
@@ -6795,20 +6798,20 @@
       <c r="A250" t="s">
         <v>184</v>
       </c>
-      <c r="B250" t="s">
-        <v>44</v>
-      </c>
-      <c r="C250" t="s">
-        <v>45</v>
+      <c r="B250">
+        <v>14022</v>
+      </c>
+      <c r="C250">
+        <v>14022</v>
       </c>
       <c r="D250">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E250" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F250" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
@@ -6818,20 +6821,20 @@
       <c r="A251" t="s">
         <v>184</v>
       </c>
-      <c r="B251">
-        <v>14053</v>
-      </c>
-      <c r="C251">
-        <v>14053</v>
+      <c r="B251" t="s">
+        <v>44</v>
+      </c>
+      <c r="C251" t="s">
+        <v>45</v>
       </c>
       <c r="D251">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E251" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
@@ -6841,20 +6844,20 @@
       <c r="A252" t="s">
         <v>184</v>
       </c>
-      <c r="B252" t="s">
-        <v>48</v>
-      </c>
-      <c r="C252" t="s">
-        <v>49</v>
+      <c r="B252">
+        <v>14053</v>
+      </c>
+      <c r="C252">
+        <v>14053</v>
       </c>
       <c r="D252">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E252" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F252" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
@@ -6864,20 +6867,20 @@
       <c r="A253" t="s">
         <v>184</v>
       </c>
-      <c r="B253">
-        <v>14023</v>
-      </c>
-      <c r="C253">
-        <v>14023</v>
+      <c r="B253" t="s">
+        <v>48</v>
+      </c>
+      <c r="C253" t="s">
+        <v>49</v>
       </c>
       <c r="D253">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E253" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F253" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
@@ -6887,20 +6890,20 @@
       <c r="A254" t="s">
         <v>184</v>
       </c>
-      <c r="B254" t="s">
-        <v>52</v>
-      </c>
-      <c r="C254" t="s">
-        <v>53</v>
+      <c r="B254">
+        <v>14023</v>
+      </c>
+      <c r="C254">
+        <v>14023</v>
       </c>
       <c r="D254">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E254" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F254" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G254" t="b">
         <v>1</v>
@@ -6910,20 +6913,20 @@
       <c r="A255" t="s">
         <v>184</v>
       </c>
-      <c r="B255">
-        <v>14000</v>
-      </c>
-      <c r="C255">
-        <v>14000</v>
+      <c r="B255" t="s">
+        <v>52</v>
+      </c>
+      <c r="C255" t="s">
+        <v>53</v>
       </c>
       <c r="D255">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E255" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F255" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
@@ -6933,20 +6936,20 @@
       <c r="A256" t="s">
         <v>184</v>
       </c>
-      <c r="B256" t="s">
-        <v>56</v>
-      </c>
-      <c r="C256" t="s">
-        <v>57</v>
+      <c r="B256">
+        <v>14000</v>
+      </c>
+      <c r="C256">
+        <v>14000</v>
       </c>
       <c r="D256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E256" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F256" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G256" t="b">
         <v>1</v>
@@ -6956,20 +6959,20 @@
       <c r="A257" t="s">
         <v>184</v>
       </c>
-      <c r="B257">
-        <v>14110</v>
-      </c>
-      <c r="C257">
-        <v>14110</v>
+      <c r="B257" t="s">
+        <v>56</v>
+      </c>
+      <c r="C257" t="s">
+        <v>57</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E257" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G257" t="b">
         <v>1</v>
@@ -6979,20 +6982,20 @@
       <c r="A258" t="s">
         <v>184</v>
       </c>
-      <c r="B258" t="s">
-        <v>60</v>
-      </c>
-      <c r="C258" t="s">
-        <v>61</v>
+      <c r="B258">
+        <v>14110</v>
+      </c>
+      <c r="C258">
+        <v>14110</v>
       </c>
       <c r="D258">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E258" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F258" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G258" t="b">
         <v>1</v>
@@ -7002,20 +7005,20 @@
       <c r="A259" t="s">
         <v>184</v>
       </c>
-      <c r="B259">
-        <v>14080</v>
-      </c>
-      <c r="C259">
-        <v>14080</v>
+      <c r="B259" t="s">
+        <v>60</v>
+      </c>
+      <c r="C259" t="s">
+        <v>61</v>
       </c>
       <c r="D259">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E259" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F259" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
@@ -7025,20 +7028,20 @@
       <c r="A260" t="s">
         <v>184</v>
       </c>
-      <c r="B260" t="s">
-        <v>64</v>
-      </c>
-      <c r="C260" t="s">
-        <v>65</v>
+      <c r="B260">
+        <v>14080</v>
+      </c>
+      <c r="C260">
+        <v>14080</v>
       </c>
       <c r="D260">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E260" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F260" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
@@ -7048,20 +7051,20 @@
       <c r="A261" t="s">
         <v>184</v>
       </c>
-      <c r="B261">
-        <v>14025</v>
-      </c>
-      <c r="C261">
-        <v>14025</v>
+      <c r="B261" t="s">
+        <v>64</v>
+      </c>
+      <c r="C261" t="s">
+        <v>65</v>
       </c>
       <c r="D261">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E261" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F261" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
@@ -7071,20 +7074,20 @@
       <c r="A262" t="s">
         <v>184</v>
       </c>
-      <c r="B262" t="s">
-        <v>68</v>
-      </c>
-      <c r="C262" t="s">
-        <v>69</v>
+      <c r="B262">
+        <v>14025</v>
+      </c>
+      <c r="C262">
+        <v>14025</v>
       </c>
       <c r="D262">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E262" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F262" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
@@ -7094,20 +7097,20 @@
       <c r="A263" t="s">
         <v>184</v>
       </c>
-      <c r="B263">
-        <v>14050</v>
-      </c>
-      <c r="C263">
-        <v>14050</v>
+      <c r="B263" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" t="s">
+        <v>69</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E263" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F263" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
@@ -7117,20 +7120,20 @@
       <c r="A264" t="s">
         <v>184</v>
       </c>
-      <c r="B264" t="s">
-        <v>72</v>
-      </c>
-      <c r="C264" t="s">
-        <v>73</v>
+      <c r="B264">
+        <v>14050</v>
+      </c>
+      <c r="C264">
+        <v>14050</v>
       </c>
       <c r="D264">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E264" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F264" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
@@ -7141,19 +7144,19 @@
         <v>184</v>
       </c>
       <c r="B265" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C265" t="s">
         <v>73</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F265" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
@@ -7164,19 +7167,19 @@
         <v>184</v>
       </c>
       <c r="B266" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C266" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D266">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E266" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F266" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
@@ -7186,20 +7189,20 @@
       <c r="A267" t="s">
         <v>184</v>
       </c>
-      <c r="B267">
-        <v>10106</v>
-      </c>
-      <c r="C267">
-        <v>10106</v>
+      <c r="B267" t="s">
+        <v>76</v>
+      </c>
+      <c r="C267" t="s">
+        <v>77</v>
       </c>
       <c r="D267">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E267" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
@@ -7209,20 +7212,20 @@
       <c r="A268" t="s">
         <v>184</v>
       </c>
-      <c r="B268" t="s">
-        <v>80</v>
-      </c>
-      <c r="C268" t="s">
-        <v>81</v>
+      <c r="B268">
+        <v>10106</v>
+      </c>
+      <c r="C268">
+        <v>10106</v>
       </c>
       <c r="D268">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E268" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F268" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
@@ -7232,20 +7235,20 @@
       <c r="A269" t="s">
         <v>184</v>
       </c>
-      <c r="B269">
-        <v>10000</v>
-      </c>
-      <c r="C269">
-        <v>10000</v>
+      <c r="B269" t="s">
+        <v>80</v>
+      </c>
+      <c r="C269" t="s">
+        <v>81</v>
       </c>
       <c r="D269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F269" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
@@ -7255,20 +7258,20 @@
       <c r="A270" t="s">
         <v>184</v>
       </c>
-      <c r="B270" t="s">
-        <v>84</v>
-      </c>
-      <c r="C270" t="s">
-        <v>85</v>
+      <c r="B270">
+        <v>10000</v>
+      </c>
+      <c r="C270">
+        <v>10000</v>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F270" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G270" t="b">
         <v>1</v>
@@ -7278,20 +7281,20 @@
       <c r="A271" t="s">
         <v>184</v>
       </c>
-      <c r="B271">
-        <v>10105</v>
-      </c>
-      <c r="C271">
-        <v>10105</v>
+      <c r="B271" t="s">
+        <v>84</v>
+      </c>
+      <c r="C271" t="s">
+        <v>85</v>
       </c>
       <c r="D271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E271" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F271" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
@@ -7302,10 +7305,10 @@
         <v>184</v>
       </c>
       <c r="B272">
-        <v>10112</v>
+        <v>10105</v>
       </c>
       <c r="C272">
-        <v>10112</v>
+        <v>10105</v>
       </c>
       <c r="D272">
         <v>5</v>
@@ -7314,7 +7317,7 @@
         <v>186</v>
       </c>
       <c r="F272" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G272" t="b">
         <v>1</v>
@@ -7324,20 +7327,20 @@
       <c r="A273" t="s">
         <v>184</v>
       </c>
-      <c r="B273" t="s">
-        <v>92</v>
-      </c>
-      <c r="C273" t="s">
-        <v>93</v>
+      <c r="B273">
+        <v>10112</v>
+      </c>
+      <c r="C273">
+        <v>10112</v>
       </c>
       <c r="D273">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E273" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F273" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
@@ -7347,20 +7350,20 @@
       <c r="A274" t="s">
         <v>184</v>
       </c>
-      <c r="B274">
-        <v>10104</v>
-      </c>
-      <c r="C274">
-        <v>10104</v>
+      <c r="B274" t="s">
+        <v>92</v>
+      </c>
+      <c r="C274" t="s">
+        <v>93</v>
       </c>
       <c r="D274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F274" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
@@ -7370,20 +7373,20 @@
       <c r="A275" t="s">
         <v>184</v>
       </c>
-      <c r="B275" t="s">
-        <v>96</v>
-      </c>
-      <c r="C275" t="s">
-        <v>97</v>
+      <c r="B275">
+        <v>10104</v>
+      </c>
+      <c r="C275">
+        <v>10104</v>
       </c>
       <c r="D275">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E275" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F275" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
@@ -7393,20 +7396,20 @@
       <c r="A276" t="s">
         <v>184</v>
       </c>
-      <c r="B276">
-        <v>10036</v>
-      </c>
-      <c r="C276">
-        <v>10036</v>
+      <c r="B276" t="s">
+        <v>96</v>
+      </c>
+      <c r="C276" t="s">
+        <v>97</v>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F276" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
@@ -7416,20 +7419,20 @@
       <c r="A277" t="s">
         <v>184</v>
       </c>
-      <c r="B277" t="s">
-        <v>101</v>
-      </c>
-      <c r="C277" t="s">
-        <v>102</v>
+      <c r="B277">
+        <v>10036</v>
+      </c>
+      <c r="C277">
+        <v>10036</v>
       </c>
       <c r="D277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E277" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F277" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
@@ -7439,20 +7442,20 @@
       <c r="A278" t="s">
         <v>184</v>
       </c>
-      <c r="B278">
-        <v>10190</v>
-      </c>
-      <c r="C278">
-        <v>10190</v>
+      <c r="B278" t="s">
+        <v>101</v>
+      </c>
+      <c r="C278" t="s">
+        <v>102</v>
       </c>
       <c r="D278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F278" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
@@ -7463,10 +7466,10 @@
         <v>184</v>
       </c>
       <c r="B279">
-        <v>10110</v>
+        <v>10190</v>
       </c>
       <c r="C279">
-        <v>10110</v>
+        <v>10190</v>
       </c>
       <c r="D279">
         <v>5</v>
@@ -7475,7 +7478,7 @@
         <v>186</v>
       </c>
       <c r="F279" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
@@ -7486,10 +7489,10 @@
         <v>184</v>
       </c>
       <c r="B280">
-        <v>10111</v>
+        <v>10110</v>
       </c>
       <c r="C280">
-        <v>10111</v>
+        <v>10110</v>
       </c>
       <c r="D280">
         <v>5</v>
@@ -7509,10 +7512,10 @@
         <v>184</v>
       </c>
       <c r="B281">
-        <v>10113</v>
+        <v>10111</v>
       </c>
       <c r="C281">
-        <v>10113</v>
+        <v>10111</v>
       </c>
       <c r="D281">
         <v>5</v>
@@ -7527,8 +7530,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>184</v>
+      </c>
+      <c r="B282">
+        <v>10113</v>
+      </c>
+      <c r="C282">
+        <v>10113</v>
+      </c>
+      <c r="D282">
+        <v>5</v>
+      </c>
+      <c r="E282" t="s">
+        <v>186</v>
+      </c>
+      <c r="F282" t="s">
+        <v>35</v>
+      </c>
+      <c r="G282" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G121" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:G122" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="0"/>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D42D72-8A60-4B4B-BAE9-EF7BD352DE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CB9CCE-F6E6-4FCE-B735-4ACC9F84969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="6800" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$118</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>lang_code</t>
   </si>
@@ -73,6 +73,60 @@
   </si>
   <si>
     <t>Utopia</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>UTO/REG</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>PROVINCE</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN</t>
+  </si>
+  <si>
+    <t>ZON</t>
+  </si>
+  <si>
+    <t>ZONE</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN/ZON</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>UTO/REG/PRO/CAN/250</t>
   </si>
 </sst>
 </file>
@@ -532,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
@@ -571,7 +625,7 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
@@ -583,66 +637,196 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="5:5" ht="22.5">
-      <c r="E19" s="4"/>
-    </row>
-    <row r="25" spans="5:5" ht="22.5">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="31" spans="5:5" ht="22.5">
-      <c r="E31" s="4"/>
-    </row>
-    <row r="37" spans="5:5" ht="22.5">
-      <c r="E37" s="4"/>
-    </row>
-    <row r="43" spans="5:5" ht="22.5">
-      <c r="E43" s="4"/>
-    </row>
-    <row r="49" spans="5:5" ht="22.5">
-      <c r="E49" s="4"/>
-    </row>
-    <row r="55" spans="5:5" ht="22.5">
-      <c r="E55" s="4"/>
-    </row>
-    <row r="61" spans="5:5" ht="22.5">
-      <c r="E61" s="4"/>
-    </row>
-    <row r="73" spans="5:5" ht="22.5">
-      <c r="E73" s="4"/>
-    </row>
-    <row r="79" spans="5:5" ht="22.5">
-      <c r="E79" s="4"/>
-    </row>
-    <row r="85" spans="5:5" ht="22.5">
-      <c r="E85" s="4"/>
-    </row>
-    <row r="91" spans="5:5" ht="22.5">
-      <c r="E91" s="4"/>
-    </row>
-    <row r="97" spans="5:5" ht="22.5">
-      <c r="E97" s="4"/>
-    </row>
-    <row r="103" spans="5:5" ht="22.5">
-      <c r="E103" s="4"/>
-    </row>
-    <row r="109" spans="5:5" ht="22.5">
-      <c r="E109" s="4"/>
-    </row>
-    <row r="119" spans="5:5" ht="22.5">
-      <c r="E119" s="4"/>
-    </row>
-    <row r="120" spans="5:5" ht="22.5">
-      <c r="E120" s="4"/>
-    </row>
-    <row r="121" spans="5:5" ht="22.5">
-      <c r="E121" s="4"/>
-    </row>
-    <row r="122" spans="5:5" ht="22.5">
-      <c r="E122" s="4"/>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>250</v>
+      </c>
+      <c r="C7">
+        <v>2500</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="22.5">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="21" spans="5:5" ht="22.5">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="27" spans="5:5" ht="22.5">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="33" spans="5:5" ht="22.5">
+      <c r="E33" s="4"/>
+    </row>
+    <row r="39" spans="5:5" ht="22.5">
+      <c r="E39" s="4"/>
+    </row>
+    <row r="45" spans="5:5" ht="22.5">
+      <c r="E45" s="4"/>
+    </row>
+    <row r="51" spans="5:5" ht="22.5">
+      <c r="E51" s="4"/>
+    </row>
+    <row r="57" spans="5:5" ht="22.5">
+      <c r="E57" s="4"/>
+    </row>
+    <row r="69" spans="5:5" ht="22.5">
+      <c r="E69" s="4"/>
+    </row>
+    <row r="75" spans="5:5" ht="22.5">
+      <c r="E75" s="4"/>
+    </row>
+    <row r="81" spans="5:5" ht="22.5">
+      <c r="E81" s="4"/>
+    </row>
+    <row r="87" spans="5:5" ht="22.5">
+      <c r="E87" s="4"/>
+    </row>
+    <row r="93" spans="5:5" ht="22.5">
+      <c r="E93" s="4"/>
+    </row>
+    <row r="99" spans="5:5" ht="22.5">
+      <c r="E99" s="4"/>
+    </row>
+    <row r="105" spans="5:5" ht="22.5">
+      <c r="E105" s="4"/>
+    </row>
+    <row r="115" spans="5:5" ht="22.5">
+      <c r="E115" s="4"/>
+    </row>
+    <row r="116" spans="5:5" ht="22.5">
+      <c r="E116" s="4"/>
+    </row>
+    <row r="117" spans="5:5" ht="22.5">
+      <c r="E117" s="4"/>
+    </row>
+    <row r="118" spans="5:5" ht="22.5">
+      <c r="E118" s="4"/>
+    </row>
+    <row r="124" spans="5:5">
+      <c r="E124" s="5"/>
+    </row>
+    <row r="125" spans="5:5">
+      <c r="E125" s="5"/>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" s="5"/>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" s="5"/>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" s="5"/>
@@ -677,18 +861,18 @@
     <row r="138" spans="5:5">
       <c r="E138" s="5"/>
     </row>
-    <row r="139" spans="5:5">
-      <c r="E139" s="5"/>
-    </row>
-    <row r="140" spans="5:5">
-      <c r="E140" s="5"/>
-    </row>
     <row r="141" spans="5:5">
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="5:5">
       <c r="E142" s="5"/>
     </row>
+    <row r="143" spans="5:5">
+      <c r="E143" s="5"/>
+    </row>
+    <row r="144" spans="5:5">
+      <c r="E144" s="5"/>
+    </row>
     <row r="145" spans="5:5">
       <c r="E145" s="5"/>
     </row>
@@ -716,17 +900,17 @@
     <row r="153" spans="5:5">
       <c r="E153" s="5"/>
     </row>
-    <row r="154" spans="5:5">
-      <c r="E154" s="5"/>
-    </row>
-    <row r="155" spans="5:5">
-      <c r="E155" s="5"/>
-    </row>
-    <row r="156" spans="5:5">
-      <c r="E156" s="5"/>
-    </row>
-    <row r="157" spans="5:5">
-      <c r="E157" s="5"/>
+    <row r="164" spans="5:5">
+      <c r="E164" s="5"/>
+    </row>
+    <row r="165" spans="5:5">
+      <c r="E165" s="5"/>
+    </row>
+    <row r="166" spans="5:5">
+      <c r="E166" s="5"/>
+    </row>
+    <row r="167" spans="5:5">
+      <c r="E167" s="5"/>
     </row>
     <row r="168" spans="5:5">
       <c r="E168" s="5"/>
@@ -761,9 +945,6 @@
     <row r="178" spans="5:5">
       <c r="E178" s="5"/>
     </row>
-    <row r="179" spans="5:5">
-      <c r="E179" s="5"/>
-    </row>
     <row r="180" spans="5:5">
       <c r="E180" s="5"/>
     </row>
@@ -773,6 +954,9 @@
     <row r="182" spans="5:5">
       <c r="E182" s="5"/>
     </row>
+    <row r="183" spans="5:5">
+      <c r="E183" s="5"/>
+    </row>
     <row r="184" spans="5:5">
       <c r="E184" s="5"/>
     </row>
@@ -803,21 +987,21 @@
     <row r="193" spans="5:5">
       <c r="E193" s="5"/>
     </row>
-    <row r="194" spans="5:5">
-      <c r="E194" s="5"/>
-    </row>
-    <row r="195" spans="5:5">
-      <c r="E195" s="5"/>
-    </row>
-    <row r="196" spans="5:5">
-      <c r="E196" s="5"/>
-    </row>
-    <row r="197" spans="5:5">
-      <c r="E197" s="5"/>
+    <row r="202" spans="5:5">
+      <c r="E202" s="5"/>
+    </row>
+    <row r="204" spans="5:5">
+      <c r="E204" s="5"/>
+    </row>
+    <row r="205" spans="5:5">
+      <c r="E205" s="5"/>
     </row>
     <row r="206" spans="5:5">
       <c r="E206" s="5"/>
     </row>
+    <row r="207" spans="5:5">
+      <c r="E207" s="5"/>
+    </row>
     <row r="208" spans="5:5">
       <c r="E208" s="5"/>
     </row>
@@ -854,9 +1038,6 @@
     <row r="219" spans="5:5">
       <c r="E219" s="5"/>
     </row>
-    <row r="220" spans="5:5">
-      <c r="E220" s="5"/>
-    </row>
     <row r="221" spans="5:5">
       <c r="E221" s="5"/>
     </row>
@@ -866,41 +1047,48 @@
     <row r="223" spans="5:5">
       <c r="E223" s="5"/>
     </row>
-    <row r="225" spans="5:5">
+    <row r="224" spans="5:5">
+      <c r="E224" s="5"/>
+    </row>
+    <row r="225" spans="2:7">
       <c r="E225" s="5"/>
     </row>
-    <row r="226" spans="5:5">
+    <row r="226" spans="2:7">
       <c r="E226" s="5"/>
     </row>
-    <row r="227" spans="5:5">
+    <row r="227" spans="2:7">
       <c r="E227" s="5"/>
     </row>
-    <row r="228" spans="5:5">
+    <row r="228" spans="2:7">
       <c r="E228" s="5"/>
     </row>
-    <row r="229" spans="5:5">
+    <row r="229" spans="2:7">
       <c r="E229" s="5"/>
     </row>
-    <row r="230" spans="5:5">
+    <row r="230" spans="2:7">
       <c r="E230" s="5"/>
     </row>
-    <row r="231" spans="5:5">
+    <row r="231" spans="2:7">
       <c r="E231" s="5"/>
     </row>
-    <row r="232" spans="5:5">
+    <row r="232" spans="2:7">
       <c r="E232" s="5"/>
     </row>
-    <row r="233" spans="5:5">
-      <c r="E233" s="5"/>
-    </row>
-    <row r="234" spans="5:5">
-      <c r="E234" s="5"/>
-    </row>
-    <row r="235" spans="5:5">
-      <c r="E235" s="5"/>
-    </row>
-    <row r="236" spans="5:5">
-      <c r="E236" s="5"/>
+    <row r="239" spans="2:7">
+      <c r="B239"/>
+      <c r="G239"/>
+    </row>
+    <row r="240" spans="2:7">
+      <c r="B240"/>
+      <c r="G240"/>
+    </row>
+    <row r="241" spans="2:7">
+      <c r="B241"/>
+      <c r="G241"/>
+    </row>
+    <row r="242" spans="2:7">
+      <c r="B242"/>
+      <c r="G242"/>
     </row>
     <row r="243" spans="2:7">
       <c r="B243"/>
@@ -1046,24 +1234,8 @@
       <c r="B278"/>
       <c r="G278"/>
     </row>
-    <row r="279" spans="2:7">
-      <c r="B279"/>
-      <c r="G279"/>
-    </row>
-    <row r="280" spans="2:7">
-      <c r="B280"/>
-      <c r="G280"/>
-    </row>
-    <row r="281" spans="2:7">
-      <c r="B281"/>
-      <c r="G281"/>
-    </row>
-    <row r="282" spans="2:7">
-      <c r="B282"/>
-      <c r="G282"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G122" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G118" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CB9CCE-F6E6-4FCE-B735-4ACC9F84969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B7DBAE-0F19-40E9-B196-B826A465EF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="3940" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>250</v>
+        <v>2550</v>
       </c>
       <c r="C7">
         <v>2500</v>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A9544-3E11-4EA9-B23C-23EBA65A32C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7637675B-33C1-4CDA-AE53-D6D73427FF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4790" yWindow="4270" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$127</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="203">
   <si>
     <t>lang_code</t>
   </si>
@@ -613,13 +613,46 @@
   </si>
   <si>
     <t>Ciudad</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>Utopia</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>ZON</t>
+  </si>
+  <si>
+    <t>ZONE</t>
+  </si>
+  <si>
+    <t>2500</t>
+  </si>
+  <si>
+    <t>PROVINCE</t>
+  </si>
+  <si>
+    <t>REGION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -638,6 +671,11 @@
       <color rgb="FF202124"/>
       <name val="Inherit"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -675,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -690,6 +728,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,9 +831,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -816,7 +871,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -922,7 +977,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,7 +1119,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1073,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G281"/>
+  <dimension ref="A1:G287"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
@@ -1108,132 +1163,139 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" s="8" customFormat="1">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="9">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="8" customFormat="1">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+      <c r="B3" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="8" customFormat="1">
+      <c r="A4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="8" customFormat="1">
+      <c r="A5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="8" customFormat="1">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="8" customFormat="1">
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2500</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1242,19 +1304,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>11</v>
@@ -1265,19 +1324,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
@@ -1288,19 +1344,16 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>11</v>
@@ -1311,19 +1364,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
@@ -1334,19 +1387,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
@@ -1357,19 +1410,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>11</v>
@@ -1380,19 +1433,19 @@
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
@@ -1403,19 +1456,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>11</v>
@@ -1426,19 +1479,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>11</v>
@@ -1449,42 +1502,42 @@
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.5">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18">
-        <v>14022</v>
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
       </c>
       <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
@@ -1495,19 +1548,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>11</v>
@@ -1518,10 +1571,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1541,10 +1594,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1564,10 +1617,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1587,10 +1640,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -1599,7 +1652,7 @@
         <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>11</v>
@@ -1610,10 +1663,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C24">
-        <v>14053</v>
+        <v>14022</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -1622,7 +1675,7 @@
         <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>11</v>
@@ -1633,10 +1686,10 @@
         <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -1645,7 +1698,7 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>11</v>
@@ -1656,10 +1709,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1679,10 +1732,10 @@
         <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1702,10 +1755,10 @@
         <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -1725,10 +1778,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1737,7 +1790,7 @@
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>11</v>
@@ -1748,10 +1801,10 @@
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C30">
-        <v>14023</v>
+        <v>14053</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1760,7 +1813,7 @@
         <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>11</v>
@@ -1771,10 +1824,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -1783,7 +1836,7 @@
         <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>11</v>
@@ -1794,10 +1847,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -1817,10 +1870,10 @@
         <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1840,10 +1893,10 @@
         <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1863,10 +1916,10 @@
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1875,7 +1928,7 @@
         <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>11</v>
@@ -1886,10 +1939,10 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C36">
-        <v>14000</v>
+        <v>14023</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1898,7 +1951,7 @@
         <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>11</v>
@@ -1909,10 +1962,10 @@
         <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1921,7 +1974,7 @@
         <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>11</v>
@@ -1932,10 +1985,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -1955,10 +2008,10 @@
         <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1978,10 +2031,10 @@
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2001,10 +2054,10 @@
         <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -2013,7 +2066,7 @@
         <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>11</v>
@@ -2024,10 +2077,10 @@
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C42">
-        <v>14110</v>
+        <v>14000</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -2036,7 +2089,7 @@
         <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>11</v>
@@ -2047,10 +2100,10 @@
         <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -2059,7 +2112,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>11</v>
@@ -2070,10 +2123,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -2093,10 +2146,10 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2116,10 +2169,10 @@
         <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2139,10 +2192,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -2151,7 +2204,7 @@
         <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>11</v>
@@ -2162,10 +2215,10 @@
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C48">
-        <v>14080</v>
+        <v>14110</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -2174,7 +2227,7 @@
         <v>42</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>11</v>
@@ -2185,10 +2238,10 @@
         <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2197,7 +2250,7 @@
         <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>11</v>
@@ -2208,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2231,10 +2284,10 @@
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2254,10 +2307,10 @@
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -2277,10 +2330,10 @@
         <v>7</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -2289,7 +2342,7 @@
         <v>41</v>
       </c>
       <c r="F53" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>11</v>
@@ -2300,10 +2353,10 @@
         <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C54">
-        <v>14025</v>
+        <v>14080</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -2312,7 +2365,7 @@
         <v>42</v>
       </c>
       <c r="F54" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>11</v>
@@ -2323,10 +2376,10 @@
         <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -2335,7 +2388,7 @@
         <v>43</v>
       </c>
       <c r="F55" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>11</v>
@@ -2346,10 +2399,10 @@
         <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2369,10 +2422,10 @@
         <v>12</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -2392,10 +2445,10 @@
         <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2415,10 +2468,10 @@
         <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D59">
         <v>5</v>
@@ -2427,7 +2480,7 @@
         <v>41</v>
       </c>
       <c r="F59" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>11</v>
@@ -2438,10 +2491,10 @@
         <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C60">
-        <v>14050</v>
+        <v>14025</v>
       </c>
       <c r="D60">
         <v>5</v>
@@ -2450,7 +2503,7 @@
         <v>42</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>11</v>
@@ -2461,10 +2514,10 @@
         <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -2473,7 +2526,7 @@
         <v>43</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>11</v>
@@ -2484,19 +2537,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>11</v>
@@ -2507,19 +2560,19 @@
         <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>11</v>
@@ -2530,19 +2583,19 @@
         <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>11</v>
@@ -2553,42 +2606,42 @@
         <v>7</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" ht="22.5">
       <c r="A66" t="s">
         <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="C66">
+        <v>14050</v>
       </c>
       <c r="D66">
-        <v>3</v>
-      </c>
-      <c r="E66" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F66" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>11</v>
@@ -2599,19 +2652,19 @@
         <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F67" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>11</v>
@@ -2622,19 +2675,19 @@
         <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>11</v>
@@ -2645,19 +2698,19 @@
         <v>12</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F69" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>11</v>
@@ -2668,19 +2721,19 @@
         <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>11</v>
@@ -2691,42 +2744,42 @@
         <v>7</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.5">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72">
-        <v>10106</v>
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>74</v>
       </c>
       <c r="D72">
-        <v>5</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>33</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>11</v>
@@ -2737,19 +2790,19 @@
         <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F73" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>11</v>
@@ -2760,10 +2813,10 @@
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -2783,10 +2836,10 @@
         <v>12</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D75">
         <v>4</v>
@@ -2806,10 +2859,10 @@
         <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -2829,10 +2882,10 @@
         <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D77">
         <v>5</v>
@@ -2841,7 +2894,7 @@
         <v>41</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>11</v>
@@ -2852,10 +2905,10 @@
         <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C78">
-        <v>10000</v>
+        <v>10106</v>
       </c>
       <c r="D78">
         <v>5</v>
@@ -2864,7 +2917,7 @@
         <v>42</v>
       </c>
       <c r="F78" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>11</v>
@@ -2875,10 +2928,10 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D79">
         <v>5</v>
@@ -2887,7 +2940,7 @@
         <v>43</v>
       </c>
       <c r="F79" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>11</v>
@@ -2898,10 +2951,10 @@
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -2921,10 +2974,10 @@
         <v>12</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -2944,10 +2997,10 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -2967,10 +3020,10 @@
         <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -2979,7 +3032,7 @@
         <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>11</v>
@@ -2990,10 +3043,10 @@
         <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C84">
-        <v>10105</v>
+        <v>10000</v>
       </c>
       <c r="D84">
         <v>5</v>
@@ -3002,7 +3055,7 @@
         <v>42</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>11</v>
@@ -3013,10 +3066,10 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -3025,7 +3078,7 @@
         <v>43</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>11</v>
@@ -3036,10 +3089,10 @@
         <v>7</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -3059,10 +3112,10 @@
         <v>12</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -3082,10 +3135,10 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D88">
         <v>4</v>
@@ -3105,10 +3158,10 @@
         <v>7</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D89">
         <v>5</v>
@@ -3117,7 +3170,7 @@
         <v>41</v>
       </c>
       <c r="F89" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>11</v>
@@ -3128,10 +3181,10 @@
         <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C90">
-        <v>10112</v>
+        <v>10105</v>
       </c>
       <c r="D90">
         <v>5</v>
@@ -3140,7 +3193,7 @@
         <v>42</v>
       </c>
       <c r="F90" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>11</v>
@@ -3151,10 +3204,10 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D91">
         <v>5</v>
@@ -3163,7 +3216,7 @@
         <v>43</v>
       </c>
       <c r="F91" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>11</v>
@@ -3174,10 +3227,10 @@
         <v>7</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D92">
         <v>4</v>
@@ -3197,10 +3250,10 @@
         <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -3220,10 +3273,10 @@
         <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D94">
         <v>4</v>
@@ -3243,10 +3296,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C95" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D95">
         <v>5</v>
@@ -3255,7 +3308,7 @@
         <v>41</v>
       </c>
       <c r="F95" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>11</v>
@@ -3266,10 +3319,10 @@
         <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C96">
-        <v>10104</v>
+        <v>10112</v>
       </c>
       <c r="D96">
         <v>5</v>
@@ -3278,7 +3331,7 @@
         <v>42</v>
       </c>
       <c r="F96" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>11</v>
@@ -3289,10 +3342,10 @@
         <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D97">
         <v>5</v>
@@ -3301,7 +3354,7 @@
         <v>43</v>
       </c>
       <c r="F97" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>11</v>
@@ -3312,10 +3365,10 @@
         <v>7</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D98">
         <v>4</v>
@@ -3335,10 +3388,10 @@
         <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D99">
         <v>4</v>
@@ -3358,10 +3411,10 @@
         <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -3381,10 +3434,10 @@
         <v>7</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D101">
         <v>5</v>
@@ -3393,7 +3446,7 @@
         <v>41</v>
       </c>
       <c r="F101" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>11</v>
@@ -3404,10 +3457,10 @@
         <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C102">
-        <v>10036</v>
+        <v>10104</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -3416,7 +3469,7 @@
         <v>42</v>
       </c>
       <c r="F102" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>11</v>
@@ -3427,10 +3480,10 @@
         <v>15</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D103">
         <v>5</v>
@@ -3439,7 +3492,7 @@
         <v>43</v>
       </c>
       <c r="F103" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>11</v>
@@ -3450,10 +3503,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D104">
         <v>4</v>
@@ -3473,10 +3526,10 @@
         <v>12</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -3496,10 +3549,10 @@
         <v>15</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C106" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D106">
         <v>4</v>
@@ -3519,10 +3572,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D107">
         <v>5</v>
@@ -3531,7 +3584,7 @@
         <v>41</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>11</v>
@@ -3542,10 +3595,10 @@
         <v>12</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C108">
-        <v>10190</v>
+        <v>10036</v>
       </c>
       <c r="D108">
         <v>5</v>
@@ -3554,7 +3607,7 @@
         <v>42</v>
       </c>
       <c r="F108" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>11</v>
@@ -3565,10 +3618,10 @@
         <v>15</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D109">
         <v>5</v>
@@ -3577,7 +3630,7 @@
         <v>43</v>
       </c>
       <c r="F109" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>11</v>
@@ -3588,19 +3641,19 @@
         <v>7</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>11</v>
@@ -3608,22 +3661,22 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>11</v>
@@ -3631,22 +3684,22 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F112" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>11</v>
@@ -3657,10 +3710,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D113">
         <v>5</v>
@@ -3669,30 +3722,30 @@
         <v>41</v>
       </c>
       <c r="F113" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" ht="22.5">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C114" t="s">
-        <v>106</v>
+        <v>104</v>
+      </c>
+      <c r="C114">
+        <v>10190</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
-      <c r="E114" t="s">
-        <v>43</v>
+      <c r="E114" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F114" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>11</v>
@@ -3703,10 +3756,10 @@
         <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D115">
         <v>5</v>
@@ -3715,7 +3768,7 @@
         <v>43</v>
       </c>
       <c r="F115" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>11</v>
@@ -3723,19 +3776,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D116">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F116" t="s">
         <v>35</v>
@@ -3746,19 +3799,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C117">
-        <v>10114</v>
+        <v>106</v>
+      </c>
+      <c r="C117" t="s">
+        <v>106</v>
       </c>
       <c r="D117">
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F117" t="s">
         <v>35</v>
@@ -3767,21 +3820,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="22.5">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C118">
-        <v>10111</v>
+        <v>107</v>
+      </c>
+      <c r="C118" t="s">
+        <v>107</v>
       </c>
       <c r="D118">
         <v>5</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>42</v>
+      <c r="E118" t="s">
+        <v>41</v>
       </c>
       <c r="F118" t="s">
         <v>35</v>
@@ -3790,21 +3843,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="22.5">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C119">
-        <v>10114</v>
+      <c r="C119" t="s">
+        <v>108</v>
       </c>
       <c r="D119">
         <v>5</v>
       </c>
-      <c r="E119" s="4" t="s">
-        <v>42</v>
+      <c r="E119" t="s">
+        <v>41</v>
       </c>
       <c r="F119" t="s">
         <v>35</v>
@@ -3813,21 +3866,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="22.5">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C120">
-        <v>10113</v>
+        <v>106</v>
+      </c>
+      <c r="C120" t="s">
+        <v>106</v>
       </c>
       <c r="D120">
         <v>5</v>
       </c>
-      <c r="E120" s="4" t="s">
-        <v>42</v>
+      <c r="E120" t="s">
+        <v>43</v>
       </c>
       <c r="F120" t="s">
         <v>35</v>
@@ -3836,21 +3889,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="22.5">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C121">
-        <v>10110</v>
+      <c r="C121" t="s">
+        <v>105</v>
       </c>
       <c r="D121">
         <v>5</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>42</v>
+      <c r="E121" t="s">
+        <v>43</v>
       </c>
       <c r="F121" t="s">
         <v>35</v>
@@ -3861,19 +3914,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>111</v>
+        <v>43</v>
+      </c>
+      <c r="F122" t="s">
+        <v>35</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>11</v>
@@ -3881,111 +3937,111 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C123" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="C123">
+        <v>10114</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E123" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" ht="22.5">
       <c r="A124" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" t="s">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="C124">
+        <v>10111</v>
       </c>
       <c r="D124">
-        <v>2</v>
-      </c>
-      <c r="E124" t="s">
-        <v>115</v>
+        <v>5</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F124" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" ht="22.5">
       <c r="A125" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C125" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="C125">
+        <v>10114</v>
       </c>
       <c r="D125">
-        <v>3</v>
-      </c>
-      <c r="E125" t="s">
-        <v>116</v>
+        <v>5</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" ht="22.5">
       <c r="A126" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C126">
+        <v>10113</v>
+      </c>
+      <c r="D126">
+        <v>5</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" t="s">
         <v>35</v>
       </c>
-      <c r="C126" t="s">
-        <v>117</v>
-      </c>
-      <c r="D126">
-        <v>4</v>
-      </c>
-      <c r="E126" t="s">
-        <v>118</v>
-      </c>
-      <c r="F126" t="s">
-        <v>31</v>
-      </c>
       <c r="G126" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" ht="22.5">
       <c r="A127" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C127" t="s">
-        <v>40</v>
+        <v>105</v>
+      </c>
+      <c r="C127">
+        <v>10110</v>
       </c>
       <c r="D127">
         <v>5</v>
       </c>
-      <c r="E127" s="5" t="s">
-        <v>119</v>
+      <c r="E127" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F127" t="s">
         <v>35</v>
@@ -3999,19 +4055,16 @@
         <v>109</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D128">
-        <v>4</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F128" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>111</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>11</v>
@@ -4022,19 +4075,19 @@
         <v>109</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C129" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D129">
-        <v>5</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="E129" t="s">
+        <v>113</v>
       </c>
       <c r="F129" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>11</v>
@@ -4045,19 +4098,19 @@
         <v>109</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D130">
-        <v>4</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>118</v>
+        <v>2</v>
+      </c>
+      <c r="E130" t="s">
+        <v>115</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>11</v>
@@ -4068,19 +4121,19 @@
         <v>109</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C131" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="D131">
-        <v>5</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>119</v>
+        <v>3</v>
+      </c>
+      <c r="E131" t="s">
+        <v>116</v>
       </c>
       <c r="F131" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>11</v>
@@ -4091,15 +4144,15 @@
         <v>109</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D132">
         <v>4</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" t="s">
         <v>118</v>
       </c>
       <c r="F132" t="s">
@@ -4114,10 +4167,10 @@
         <v>109</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D133">
         <v>5</v>
@@ -4126,7 +4179,7 @@
         <v>119</v>
       </c>
       <c r="F133" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>11</v>
@@ -4137,10 +4190,10 @@
         <v>109</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D134">
         <v>4</v>
@@ -4160,10 +4213,10 @@
         <v>109</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C135" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -4172,7 +4225,7 @@
         <v>119</v>
       </c>
       <c r="F135" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>11</v>
@@ -4183,10 +4236,10 @@
         <v>109</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D136">
         <v>4</v>
@@ -4206,10 +4259,10 @@
         <v>109</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C137" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D137">
         <v>5</v>
@@ -4218,7 +4271,7 @@
         <v>119</v>
       </c>
       <c r="F137" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>11</v>
@@ -4229,10 +4282,10 @@
         <v>109</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C138" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D138">
         <v>4</v>
@@ -4252,10 +4305,10 @@
         <v>109</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C139" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D139">
         <v>5</v>
@@ -4264,7 +4317,7 @@
         <v>119</v>
       </c>
       <c r="F139" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>11</v>
@@ -4275,10 +4328,10 @@
         <v>109</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C140" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D140">
         <v>4</v>
@@ -4298,10 +4351,10 @@
         <v>109</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C141" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D141">
         <v>5</v>
@@ -4310,7 +4363,7 @@
         <v>119</v>
       </c>
       <c r="F141" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>11</v>
@@ -4321,19 +4374,19 @@
         <v>109</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D142">
-        <v>2</v>
-      </c>
-      <c r="E142" t="s">
-        <v>115</v>
+        <v>4</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F142" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>11</v>
@@ -4344,19 +4397,19 @@
         <v>109</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C143" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="D143">
-        <v>3</v>
-      </c>
-      <c r="E143" t="s">
-        <v>116</v>
+        <v>5</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="F143" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>11</v>
@@ -4367,10 +4420,10 @@
         <v>109</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C144" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D144">
         <v>4</v>
@@ -4379,7 +4432,7 @@
         <v>118</v>
       </c>
       <c r="F144" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>11</v>
@@ -4390,10 +4443,10 @@
         <v>109</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C145" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D145">
         <v>5</v>
@@ -4402,7 +4455,7 @@
         <v>119</v>
       </c>
       <c r="F145" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>11</v>
@@ -4413,10 +4466,10 @@
         <v>109</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C146" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D146">
         <v>4</v>
@@ -4425,7 +4478,7 @@
         <v>118</v>
       </c>
       <c r="F146" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>11</v>
@@ -4436,10 +4489,10 @@
         <v>109</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C147" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D147">
         <v>5</v>
@@ -4448,7 +4501,7 @@
         <v>119</v>
       </c>
       <c r="F147" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>11</v>
@@ -4459,19 +4512,19 @@
         <v>109</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D148">
-        <v>4</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>118</v>
+        <v>2</v>
+      </c>
+      <c r="E148" t="s">
+        <v>115</v>
       </c>
       <c r="F148" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>11</v>
@@ -4482,19 +4535,19 @@
         <v>109</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C149" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D149">
-        <v>5</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>119</v>
+        <v>3</v>
+      </c>
+      <c r="E149" t="s">
+        <v>116</v>
       </c>
       <c r="F149" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>11</v>
@@ -4505,10 +4558,10 @@
         <v>109</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C150" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D150">
         <v>4</v>
@@ -4528,10 +4581,10 @@
         <v>109</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D151">
         <v>5</v>
@@ -4540,7 +4593,7 @@
         <v>119</v>
       </c>
       <c r="F151" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>11</v>
@@ -4551,10 +4604,10 @@
         <v>109</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D152">
         <v>4</v>
@@ -4574,10 +4627,10 @@
         <v>109</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C153" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D153">
         <v>5</v>
@@ -4586,7 +4639,7 @@
         <v>119</v>
       </c>
       <c r="F153" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>11</v>
@@ -4597,10 +4650,10 @@
         <v>109</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C154" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D154">
         <v>4</v>
@@ -4620,10 +4673,10 @@
         <v>109</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D155">
         <v>5</v>
@@ -4632,7 +4685,7 @@
         <v>119</v>
       </c>
       <c r="F155" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>11</v>
@@ -4643,10 +4696,10 @@
         <v>109</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C156" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D156">
         <v>4</v>
@@ -4666,19 +4719,19 @@
         <v>109</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C157" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D157">
         <v>5</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F157" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>11</v>
@@ -4689,19 +4742,19 @@
         <v>109</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="D158">
-        <v>5</v>
-      </c>
-      <c r="E158" t="s">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F158" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>11</v>
@@ -4712,19 +4765,19 @@
         <v>109</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D159">
         <v>5</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F159" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>11</v>
@@ -4735,19 +4788,19 @@
         <v>109</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="D160">
-        <v>5</v>
-      </c>
-      <c r="E160" t="s">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F160" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>11</v>
@@ -4758,19 +4811,19 @@
         <v>109</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C161" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D161">
         <v>5</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F161" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>11</v>
@@ -4778,19 +4831,22 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="C162" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="E162" t="s">
-        <v>137</v>
+        <v>4</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F162" t="s">
+        <v>75</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>11</v>
@@ -4798,22 +4854,22 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="C163" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E163" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>11</v>
@@ -4821,22 +4877,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C164" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F164" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>11</v>
@@ -4844,22 +4900,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="C165" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="D165">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>11</v>
@@ -4867,22 +4923,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B166" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C166" t="s">
+        <v>107</v>
+      </c>
+      <c r="D166">
+        <v>5</v>
+      </c>
+      <c r="E166" t="s">
+        <v>119</v>
+      </c>
+      <c r="F166" t="s">
         <v>35</v>
-      </c>
-      <c r="C166" t="s">
-        <v>143</v>
-      </c>
-      <c r="D166">
-        <v>4</v>
-      </c>
-      <c r="E166" t="s">
-        <v>144</v>
-      </c>
-      <c r="F166" t="s">
-        <v>31</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>11</v>
@@ -4890,19 +4946,19 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C167" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="D167">
         <v>5</v>
       </c>
-      <c r="E167" s="5" t="s">
-        <v>145</v>
+      <c r="E167" t="s">
+        <v>119</v>
       </c>
       <c r="F167" t="s">
         <v>35</v>
@@ -4916,19 +4972,16 @@
         <v>135</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D168">
-        <v>4</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F168" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="E168" t="s">
+        <v>137</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>11</v>
@@ -4939,19 +4992,19 @@
         <v>135</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C169" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="D169">
-        <v>5</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>145</v>
+        <v>1</v>
+      </c>
+      <c r="E169" t="s">
+        <v>139</v>
       </c>
       <c r="F169" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>11</v>
@@ -4962,19 +5015,19 @@
         <v>135</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D170">
-        <v>4</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>144</v>
+        <v>2</v>
+      </c>
+      <c r="E170" t="s">
+        <v>141</v>
       </c>
       <c r="F170" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>11</v>
@@ -4985,19 +5038,19 @@
         <v>135</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C171" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D171">
-        <v>5</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>145</v>
+        <v>3</v>
+      </c>
+      <c r="E171" t="s">
+        <v>142</v>
       </c>
       <c r="F171" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>11</v>
@@ -5008,15 +5061,15 @@
         <v>135</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C172" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D172">
         <v>4</v>
       </c>
-      <c r="E172" s="5" t="s">
+      <c r="E172" t="s">
         <v>144</v>
       </c>
       <c r="F172" t="s">
@@ -5031,10 +5084,10 @@
         <v>135</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C173" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D173">
         <v>5</v>
@@ -5043,7 +5096,7 @@
         <v>145</v>
       </c>
       <c r="F173" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>11</v>
@@ -5054,10 +5107,10 @@
         <v>135</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D174">
         <v>4</v>
@@ -5077,10 +5130,10 @@
         <v>135</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C175" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D175">
         <v>5</v>
@@ -5089,7 +5142,7 @@
         <v>145</v>
       </c>
       <c r="F175" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>11</v>
@@ -5100,10 +5153,10 @@
         <v>135</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C176" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D176">
         <v>4</v>
@@ -5123,10 +5176,10 @@
         <v>135</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C177" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D177">
         <v>5</v>
@@ -5135,7 +5188,7 @@
         <v>145</v>
       </c>
       <c r="F177" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>11</v>
@@ -5146,10 +5199,10 @@
         <v>135</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C178" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D178">
         <v>4</v>
@@ -5169,10 +5222,10 @@
         <v>135</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C179" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D179">
         <v>5</v>
@@ -5181,7 +5234,7 @@
         <v>145</v>
       </c>
       <c r="F179" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>11</v>
@@ -5192,10 +5245,10 @@
         <v>135</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C180" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D180">
         <v>4</v>
@@ -5215,10 +5268,10 @@
         <v>135</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C181" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D181">
         <v>5</v>
@@ -5227,7 +5280,7 @@
         <v>145</v>
       </c>
       <c r="F181" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>11</v>
@@ -5238,19 +5291,19 @@
         <v>135</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C182" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D182">
-        <v>2</v>
-      </c>
-      <c r="E182" t="s">
-        <v>141</v>
+        <v>4</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="F182" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>11</v>
@@ -5261,19 +5314,19 @@
         <v>135</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C183" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="D183">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F183" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>11</v>
@@ -5284,10 +5337,10 @@
         <v>135</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C184" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D184">
         <v>4</v>
@@ -5296,7 +5349,7 @@
         <v>144</v>
       </c>
       <c r="F184" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>11</v>
@@ -5307,10 +5360,10 @@
         <v>135</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C185" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D185">
         <v>5</v>
@@ -5319,7 +5372,7 @@
         <v>145</v>
       </c>
       <c r="F185" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>11</v>
@@ -5330,10 +5383,10 @@
         <v>135</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C186" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D186">
         <v>4</v>
@@ -5342,7 +5395,7 @@
         <v>144</v>
       </c>
       <c r="F186" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>11</v>
@@ -5353,10 +5406,10 @@
         <v>135</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C187" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D187">
         <v>5</v>
@@ -5365,7 +5418,7 @@
         <v>145</v>
       </c>
       <c r="F187" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>11</v>
@@ -5376,19 +5429,19 @@
         <v>135</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C188" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D188">
-        <v>4</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>144</v>
+        <v>2</v>
+      </c>
+      <c r="E188" t="s">
+        <v>141</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>11</v>
@@ -5399,19 +5452,19 @@
         <v>135</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C189" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F189" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>11</v>
@@ -5422,10 +5475,10 @@
         <v>135</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C190" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D190">
         <v>4</v>
@@ -5445,10 +5498,10 @@
         <v>135</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C191" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -5457,7 +5510,7 @@
         <v>145</v>
       </c>
       <c r="F191" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>11</v>
@@ -5468,10 +5521,10 @@
         <v>135</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C192" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D192">
         <v>4</v>
@@ -5491,10 +5544,10 @@
         <v>135</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C193" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D193">
         <v>5</v>
@@ -5503,7 +5556,7 @@
         <v>145</v>
       </c>
       <c r="F193" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>11</v>
@@ -5514,10 +5567,10 @@
         <v>135</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C194" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D194">
         <v>4</v>
@@ -5537,10 +5590,10 @@
         <v>135</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C195" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D195">
         <v>5</v>
@@ -5549,7 +5602,7 @@
         <v>145</v>
       </c>
       <c r="F195" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>11</v>
@@ -5560,10 +5613,10 @@
         <v>135</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C196" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D196">
         <v>4</v>
@@ -5583,19 +5636,19 @@
         <v>135</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C197" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D197">
         <v>5</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="5" t="s">
         <v>145</v>
       </c>
       <c r="F197" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>11</v>
@@ -5606,19 +5659,19 @@
         <v>135</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C198" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="D198">
-        <v>5</v>
-      </c>
-      <c r="E198" t="s">
-        <v>145</v>
+        <v>4</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="F198" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>11</v>
@@ -5629,19 +5682,19 @@
         <v>135</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C199" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D199">
         <v>5</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="5" t="s">
         <v>145</v>
       </c>
       <c r="F199" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>11</v>
@@ -5652,19 +5705,19 @@
         <v>135</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C200" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="D200">
-        <v>5</v>
-      </c>
-      <c r="E200" t="s">
-        <v>145</v>
+        <v>4</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="F200" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>11</v>
@@ -5675,19 +5728,19 @@
         <v>135</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C201" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D201">
         <v>5</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="5" t="s">
         <v>145</v>
       </c>
       <c r="F201" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>11</v>
@@ -5695,19 +5748,22 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="E202" t="s">
-        <v>162</v>
+        <v>4</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F202" t="s">
+        <v>75</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>11</v>
@@ -5715,22 +5771,22 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E203" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="F203" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>11</v>
@@ -5738,22 +5794,22 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C204" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E204" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="F204" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>11</v>
@@ -5761,22 +5817,22 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="C205" t="s">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="D205">
-        <v>3</v>
-      </c>
-      <c r="E205" s="5" t="s">
-        <v>167</v>
+        <v>5</v>
+      </c>
+      <c r="E205" t="s">
+        <v>145</v>
       </c>
       <c r="F205" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>11</v>
@@ -5784,22 +5840,22 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B206" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C206" t="s">
+        <v>107</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+      <c r="E206" t="s">
+        <v>145</v>
+      </c>
+      <c r="F206" t="s">
         <v>35</v>
-      </c>
-      <c r="C206" t="s">
-        <v>168</v>
-      </c>
-      <c r="D206">
-        <v>4</v>
-      </c>
-      <c r="E206" t="s">
-        <v>169</v>
-      </c>
-      <c r="F206" t="s">
-        <v>31</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>11</v>
@@ -5807,19 +5863,19 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C207" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="D207">
         <v>5</v>
       </c>
-      <c r="E207" s="5" t="s">
-        <v>170</v>
+      <c r="E207" t="s">
+        <v>145</v>
       </c>
       <c r="F207" t="s">
         <v>35</v>
@@ -5833,19 +5889,16 @@
         <v>161</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D208">
-        <v>4</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F208" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="E208" t="s">
+        <v>162</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>11</v>
@@ -5856,19 +5909,19 @@
         <v>161</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="D209">
-        <v>5</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>170</v>
+        <v>1</v>
+      </c>
+      <c r="E209" t="s">
+        <v>164</v>
       </c>
       <c r="F209" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>11</v>
@@ -5879,19 +5932,19 @@
         <v>161</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C210" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D210">
-        <v>4</v>
-      </c>
-      <c r="E210" s="5" t="s">
-        <v>169</v>
+        <v>2</v>
+      </c>
+      <c r="E210" t="s">
+        <v>166</v>
       </c>
       <c r="F210" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>11</v>
@@ -5902,19 +5955,19 @@
         <v>161</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C211" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="D211">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F211" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>11</v>
@@ -5925,15 +5978,15 @@
         <v>161</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C212" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D212">
         <v>4</v>
       </c>
-      <c r="E212" s="5" t="s">
+      <c r="E212" t="s">
         <v>169</v>
       </c>
       <c r="F212" t="s">
@@ -5948,10 +6001,10 @@
         <v>161</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C213" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D213">
         <v>5</v>
@@ -5960,7 +6013,7 @@
         <v>170</v>
       </c>
       <c r="F213" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>11</v>
@@ -5971,10 +6024,10 @@
         <v>161</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C214" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="D214">
         <v>4</v>
@@ -5994,10 +6047,10 @@
         <v>161</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C215" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D215">
         <v>5</v>
@@ -6006,7 +6059,7 @@
         <v>170</v>
       </c>
       <c r="F215" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>11</v>
@@ -6017,10 +6070,10 @@
         <v>161</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C216" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D216">
         <v>4</v>
@@ -6040,10 +6093,10 @@
         <v>161</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C217" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D217">
         <v>5</v>
@@ -6052,7 +6105,7 @@
         <v>170</v>
       </c>
       <c r="F217" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>11</v>
@@ -6063,10 +6116,10 @@
         <v>161</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -6086,10 +6139,10 @@
         <v>161</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C219" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D219">
         <v>5</v>
@@ -6098,7 +6151,7 @@
         <v>170</v>
       </c>
       <c r="F219" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>11</v>
@@ -6109,10 +6162,10 @@
         <v>161</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C220" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="D220">
         <v>4</v>
@@ -6132,10 +6185,10 @@
         <v>161</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C221" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D221">
         <v>5</v>
@@ -6144,7 +6197,7 @@
         <v>170</v>
       </c>
       <c r="F221" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>11</v>
@@ -6155,19 +6208,19 @@
         <v>161</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C222" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F222" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>11</v>
@@ -6178,19 +6231,19 @@
         <v>161</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C223" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="D223">
-        <v>3</v>
-      </c>
-      <c r="E223" t="s">
-        <v>167</v>
+        <v>5</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="F223" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>11</v>
@@ -6201,10 +6254,10 @@
         <v>161</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C224" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D224">
         <v>4</v>
@@ -6213,7 +6266,7 @@
         <v>169</v>
       </c>
       <c r="F224" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>11</v>
@@ -6224,10 +6277,10 @@
         <v>161</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C225" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D225">
         <v>5</v>
@@ -6236,7 +6289,7 @@
         <v>170</v>
       </c>
       <c r="F225" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>11</v>
@@ -6247,10 +6300,10 @@
         <v>161</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D226">
         <v>4</v>
@@ -6259,7 +6312,7 @@
         <v>169</v>
       </c>
       <c r="F226" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>11</v>
@@ -6270,10 +6323,10 @@
         <v>161</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C227" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D227">
         <v>5</v>
@@ -6282,7 +6335,7 @@
         <v>170</v>
       </c>
       <c r="F227" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>11</v>
@@ -6293,19 +6346,19 @@
         <v>161</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C228" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="D228">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F228" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>11</v>
@@ -6316,19 +6369,19 @@
         <v>161</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C229" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="D229">
-        <v>5</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>170</v>
+        <v>3</v>
+      </c>
+      <c r="E229" t="s">
+        <v>167</v>
       </c>
       <c r="F229" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>11</v>
@@ -6339,10 +6392,10 @@
         <v>161</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D230">
         <v>4</v>
@@ -6362,10 +6415,10 @@
         <v>161</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C231" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D231">
         <v>5</v>
@@ -6374,7 +6427,7 @@
         <v>170</v>
       </c>
       <c r="F231" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>11</v>
@@ -6385,10 +6438,10 @@
         <v>161</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C232" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D232">
         <v>4</v>
@@ -6408,10 +6461,10 @@
         <v>161</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C233" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D233">
         <v>5</v>
@@ -6420,7 +6473,7 @@
         <v>170</v>
       </c>
       <c r="F233" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>11</v>
@@ -6431,10 +6484,10 @@
         <v>161</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="D234">
         <v>4</v>
@@ -6454,10 +6507,10 @@
         <v>161</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C235" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D235">
         <v>5</v>
@@ -6466,7 +6519,7 @@
         <v>170</v>
       </c>
       <c r="F235" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>11</v>
@@ -6477,15 +6530,15 @@
         <v>161</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C236" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D236">
         <v>4</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E236" s="5" t="s">
         <v>169</v>
       </c>
       <c r="F236" t="s">
@@ -6500,19 +6553,19 @@
         <v>161</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C237" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D237">
         <v>5</v>
       </c>
-      <c r="E237" t="s">
+      <c r="E237" s="5" t="s">
         <v>170</v>
       </c>
       <c r="F237" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>11</v>
@@ -6523,19 +6576,19 @@
         <v>161</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C238" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="D238">
-        <v>5</v>
-      </c>
-      <c r="E238" t="s">
-        <v>170</v>
+        <v>4</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>11</v>
@@ -6546,19 +6599,19 @@
         <v>161</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C239" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D239">
         <v>5</v>
       </c>
-      <c r="E239" t="s">
+      <c r="E239" s="5" t="s">
         <v>170</v>
       </c>
       <c r="F239" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>11</v>
@@ -6569,19 +6622,19 @@
         <v>161</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C240" t="s">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="D240">
-        <v>5</v>
-      </c>
-      <c r="E240" t="s">
-        <v>170</v>
+        <v>4</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>11</v>
@@ -6592,19 +6645,19 @@
         <v>161</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C241" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D241">
         <v>5</v>
       </c>
-      <c r="E241" t="s">
+      <c r="E241" s="5" t="s">
         <v>170</v>
       </c>
       <c r="F241" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>11</v>
@@ -6612,137 +6665,140 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>184</v>
-      </c>
-      <c r="B242" t="s">
-        <v>88</v>
+        <v>161</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C242" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="D242">
         <v>4</v>
       </c>
       <c r="E242" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F242" t="s">
         <v>75</v>
       </c>
-      <c r="G242" t="b">
-        <v>1</v>
+      <c r="G242" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>184</v>
-      </c>
-      <c r="B243">
-        <v>10114</v>
-      </c>
-      <c r="C243">
-        <v>10114</v>
+        <v>161</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C243" t="s">
+        <v>104</v>
       </c>
       <c r="D243">
         <v>5</v>
       </c>
       <c r="E243" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
-      </c>
-      <c r="G243" t="b">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>184</v>
-      </c>
-      <c r="B244" t="s">
-        <v>8</v>
+        <v>161</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C244" t="s">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
-        <v>188</v>
-      </c>
-      <c r="G244" t="b">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="F244" t="s">
+        <v>35</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>184</v>
-      </c>
-      <c r="B245" t="s">
-        <v>18</v>
+        <v>161</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C245" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E245" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F245" t="s">
-        <v>8</v>
-      </c>
-      <c r="G245" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>184</v>
-      </c>
-      <c r="B246" t="s">
-        <v>25</v>
+        <v>161</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C246" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E246" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="F246" t="s">
-        <v>18</v>
-      </c>
-      <c r="G246" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>184</v>
-      </c>
-      <c r="B247" t="s">
-        <v>31</v>
+        <v>161</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D247">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E247" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F247" t="s">
-        <v>25</v>
-      </c>
-      <c r="G247" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6750,10 +6806,10 @@
         <v>184</v>
       </c>
       <c r="B248" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="C248" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D248">
         <v>4</v>
@@ -6762,7 +6818,7 @@
         <v>185</v>
       </c>
       <c r="F248" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
@@ -6773,10 +6829,10 @@
         <v>184</v>
       </c>
       <c r="B249">
-        <v>14022</v>
+        <v>10114</v>
       </c>
       <c r="C249">
-        <v>14022</v>
+        <v>10114</v>
       </c>
       <c r="D249">
         <v>5</v>
@@ -6796,19 +6852,16 @@
         <v>184</v>
       </c>
       <c r="B250" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C250" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="D250">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>185</v>
-      </c>
-      <c r="F250" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
@@ -6818,20 +6871,20 @@
       <c r="A251" t="s">
         <v>184</v>
       </c>
-      <c r="B251">
-        <v>14053</v>
-      </c>
-      <c r="C251">
-        <v>14053</v>
+      <c r="B251" t="s">
+        <v>18</v>
+      </c>
+      <c r="C251" t="s">
+        <v>19</v>
       </c>
       <c r="D251">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
@@ -6842,19 +6895,19 @@
         <v>184</v>
       </c>
       <c r="B252" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C252" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D252">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F252" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
@@ -6864,20 +6917,20 @@
       <c r="A253" t="s">
         <v>184</v>
       </c>
-      <c r="B253">
-        <v>14023</v>
-      </c>
-      <c r="C253">
-        <v>14023</v>
+      <c r="B253" t="s">
+        <v>31</v>
+      </c>
+      <c r="C253" t="s">
+        <v>26</v>
       </c>
       <c r="D253">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E253" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F253" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
@@ -6888,10 +6941,10 @@
         <v>184</v>
       </c>
       <c r="B254" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C254" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D254">
         <v>4</v>
@@ -6911,10 +6964,10 @@
         <v>184</v>
       </c>
       <c r="B255">
-        <v>14000</v>
+        <v>14022</v>
       </c>
       <c r="C255">
-        <v>14000</v>
+        <v>14022</v>
       </c>
       <c r="D255">
         <v>5</v>
@@ -6923,7 +6976,7 @@
         <v>186</v>
       </c>
       <c r="F255" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
@@ -6934,10 +6987,10 @@
         <v>184</v>
       </c>
       <c r="B256" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C256" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D256">
         <v>4</v>
@@ -6957,10 +7010,10 @@
         <v>184</v>
       </c>
       <c r="B257">
-        <v>14110</v>
+        <v>14053</v>
       </c>
       <c r="C257">
-        <v>14110</v>
+        <v>14053</v>
       </c>
       <c r="D257">
         <v>5</v>
@@ -6969,7 +7022,7 @@
         <v>186</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G257" t="b">
         <v>1</v>
@@ -6980,10 +7033,10 @@
         <v>184</v>
       </c>
       <c r="B258" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D258">
         <v>4</v>
@@ -7003,10 +7056,10 @@
         <v>184</v>
       </c>
       <c r="B259">
-        <v>14080</v>
+        <v>14023</v>
       </c>
       <c r="C259">
-        <v>14080</v>
+        <v>14023</v>
       </c>
       <c r="D259">
         <v>5</v>
@@ -7015,7 +7068,7 @@
         <v>186</v>
       </c>
       <c r="F259" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
@@ -7026,10 +7079,10 @@
         <v>184</v>
       </c>
       <c r="B260" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C260" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D260">
         <v>4</v>
@@ -7049,10 +7102,10 @@
         <v>184</v>
       </c>
       <c r="B261">
-        <v>14025</v>
+        <v>14000</v>
       </c>
       <c r="C261">
-        <v>14025</v>
+        <v>14000</v>
       </c>
       <c r="D261">
         <v>5</v>
@@ -7061,7 +7114,7 @@
         <v>186</v>
       </c>
       <c r="F261" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
@@ -7072,10 +7125,10 @@
         <v>184</v>
       </c>
       <c r="B262" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C262" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D262">
         <v>4</v>
@@ -7095,10 +7148,10 @@
         <v>184</v>
       </c>
       <c r="B263">
-        <v>14050</v>
+        <v>14110</v>
       </c>
       <c r="C263">
-        <v>14050</v>
+        <v>14110</v>
       </c>
       <c r="D263">
         <v>5</v>
@@ -7107,7 +7160,7 @@
         <v>186</v>
       </c>
       <c r="F263" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
@@ -7118,19 +7171,19 @@
         <v>184</v>
       </c>
       <c r="B264" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C264" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D264">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E264" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F264" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
@@ -7140,20 +7193,20 @@
       <c r="A265" t="s">
         <v>184</v>
       </c>
-      <c r="B265" t="s">
-        <v>75</v>
-      </c>
-      <c r="C265" t="s">
-        <v>73</v>
+      <c r="B265">
+        <v>14080</v>
+      </c>
+      <c r="C265">
+        <v>14080</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E265" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F265" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
@@ -7164,10 +7217,10 @@
         <v>184</v>
       </c>
       <c r="B266" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C266" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D266">
         <v>4</v>
@@ -7176,7 +7229,7 @@
         <v>185</v>
       </c>
       <c r="F266" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
@@ -7187,10 +7240,10 @@
         <v>184</v>
       </c>
       <c r="B267">
-        <v>10106</v>
+        <v>14025</v>
       </c>
       <c r="C267">
-        <v>10106</v>
+        <v>14025</v>
       </c>
       <c r="D267">
         <v>5</v>
@@ -7199,7 +7252,7 @@
         <v>186</v>
       </c>
       <c r="F267" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
@@ -7210,10 +7263,10 @@
         <v>184</v>
       </c>
       <c r="B268" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C268" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D268">
         <v>4</v>
@@ -7222,7 +7275,7 @@
         <v>185</v>
       </c>
       <c r="F268" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
@@ -7233,10 +7286,10 @@
         <v>184</v>
       </c>
       <c r="B269">
-        <v>10000</v>
+        <v>14050</v>
       </c>
       <c r="C269">
-        <v>10000</v>
+        <v>14050</v>
       </c>
       <c r="D269">
         <v>5</v>
@@ -7245,7 +7298,7 @@
         <v>186</v>
       </c>
       <c r="F269" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
@@ -7256,19 +7309,19 @@
         <v>184</v>
       </c>
       <c r="B270" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C270" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E270" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F270" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G270" t="b">
         <v>1</v>
@@ -7278,20 +7331,20 @@
       <c r="A271" t="s">
         <v>184</v>
       </c>
-      <c r="B271">
-        <v>10105</v>
-      </c>
-      <c r="C271">
-        <v>10105</v>
+      <c r="B271" t="s">
+        <v>75</v>
+      </c>
+      <c r="C271" t="s">
+        <v>73</v>
       </c>
       <c r="D271">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E271" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F271" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
@@ -7301,20 +7354,20 @@
       <c r="A272" t="s">
         <v>184</v>
       </c>
-      <c r="B272">
-        <v>10112</v>
-      </c>
-      <c r="C272">
-        <v>10112</v>
+      <c r="B272" t="s">
+        <v>76</v>
+      </c>
+      <c r="C272" t="s">
+        <v>77</v>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F272" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G272" t="b">
         <v>1</v>
@@ -7324,20 +7377,20 @@
       <c r="A273" t="s">
         <v>184</v>
       </c>
-      <c r="B273" t="s">
-        <v>92</v>
-      </c>
-      <c r="C273" t="s">
-        <v>93</v>
+      <c r="B273">
+        <v>10106</v>
+      </c>
+      <c r="C273">
+        <v>10106</v>
       </c>
       <c r="D273">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E273" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F273" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
@@ -7347,20 +7400,20 @@
       <c r="A274" t="s">
         <v>184</v>
       </c>
-      <c r="B274">
-        <v>10104</v>
-      </c>
-      <c r="C274">
-        <v>10104</v>
+      <c r="B274" t="s">
+        <v>80</v>
+      </c>
+      <c r="C274" t="s">
+        <v>81</v>
       </c>
       <c r="D274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F274" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
@@ -7370,20 +7423,20 @@
       <c r="A275" t="s">
         <v>184</v>
       </c>
-      <c r="B275" t="s">
-        <v>96</v>
-      </c>
-      <c r="C275" t="s">
-        <v>97</v>
+      <c r="B275">
+        <v>10000</v>
+      </c>
+      <c r="C275">
+        <v>10000</v>
       </c>
       <c r="D275">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E275" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F275" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
@@ -7393,20 +7446,20 @@
       <c r="A276" t="s">
         <v>184</v>
       </c>
-      <c r="B276">
-        <v>10036</v>
-      </c>
-      <c r="C276">
-        <v>10036</v>
+      <c r="B276" t="s">
+        <v>84</v>
+      </c>
+      <c r="C276" t="s">
+        <v>85</v>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F276" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
@@ -7416,20 +7469,20 @@
       <c r="A277" t="s">
         <v>184</v>
       </c>
-      <c r="B277" t="s">
-        <v>101</v>
-      </c>
-      <c r="C277" t="s">
-        <v>102</v>
+      <c r="B277">
+        <v>10105</v>
+      </c>
+      <c r="C277">
+        <v>10105</v>
       </c>
       <c r="D277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E277" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F277" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
@@ -7440,10 +7493,10 @@
         <v>184</v>
       </c>
       <c r="B278">
-        <v>10190</v>
+        <v>10112</v>
       </c>
       <c r="C278">
-        <v>10190</v>
+        <v>10112</v>
       </c>
       <c r="D278">
         <v>5</v>
@@ -7452,7 +7505,7 @@
         <v>186</v>
       </c>
       <c r="F278" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
@@ -7462,20 +7515,20 @@
       <c r="A279" t="s">
         <v>184</v>
       </c>
-      <c r="B279">
-        <v>10110</v>
-      </c>
-      <c r="C279">
-        <v>10110</v>
+      <c r="B279" t="s">
+        <v>92</v>
+      </c>
+      <c r="C279" t="s">
+        <v>93</v>
       </c>
       <c r="D279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E279" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F279" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
@@ -7486,10 +7539,10 @@
         <v>184</v>
       </c>
       <c r="B280">
-        <v>10111</v>
+        <v>10104</v>
       </c>
       <c r="C280">
-        <v>10111</v>
+        <v>10104</v>
       </c>
       <c r="D280">
         <v>5</v>
@@ -7498,7 +7551,7 @@
         <v>186</v>
       </c>
       <c r="F280" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G280" t="b">
         <v>1</v>
@@ -7508,27 +7561,165 @@
       <c r="A281" t="s">
         <v>184</v>
       </c>
-      <c r="B281">
-        <v>10113</v>
-      </c>
-      <c r="C281">
-        <v>10113</v>
+      <c r="B281" t="s">
+        <v>96</v>
+      </c>
+      <c r="C281" t="s">
+        <v>97</v>
       </c>
       <c r="D281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E281" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F281" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G281" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>184</v>
+      </c>
+      <c r="B282">
+        <v>10036</v>
+      </c>
+      <c r="C282">
+        <v>10036</v>
+      </c>
+      <c r="D282">
+        <v>5</v>
+      </c>
+      <c r="E282" t="s">
+        <v>186</v>
+      </c>
+      <c r="F282" t="s">
+        <v>96</v>
+      </c>
+      <c r="G282" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>184</v>
+      </c>
+      <c r="B283" t="s">
+        <v>101</v>
+      </c>
+      <c r="C283" t="s">
+        <v>102</v>
+      </c>
+      <c r="D283">
+        <v>4</v>
+      </c>
+      <c r="E283" t="s">
+        <v>185</v>
+      </c>
+      <c r="F283" t="s">
+        <v>75</v>
+      </c>
+      <c r="G283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>184</v>
+      </c>
+      <c r="B284">
+        <v>10190</v>
+      </c>
+      <c r="C284">
+        <v>10190</v>
+      </c>
+      <c r="D284">
+        <v>5</v>
+      </c>
+      <c r="E284" t="s">
+        <v>186</v>
+      </c>
+      <c r="F284" t="s">
+        <v>101</v>
+      </c>
+      <c r="G284" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>184</v>
+      </c>
+      <c r="B285">
+        <v>10110</v>
+      </c>
+      <c r="C285">
+        <v>10110</v>
+      </c>
+      <c r="D285">
+        <v>5</v>
+      </c>
+      <c r="E285" t="s">
+        <v>186</v>
+      </c>
+      <c r="F285" t="s">
+        <v>35</v>
+      </c>
+      <c r="G285" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>184</v>
+      </c>
+      <c r="B286">
+        <v>10111</v>
+      </c>
+      <c r="C286">
+        <v>10111</v>
+      </c>
+      <c r="D286">
+        <v>5</v>
+      </c>
+      <c r="E286" t="s">
+        <v>186</v>
+      </c>
+      <c r="F286" t="s">
+        <v>35</v>
+      </c>
+      <c r="G286" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>184</v>
+      </c>
+      <c r="B287">
+        <v>10113</v>
+      </c>
+      <c r="C287">
+        <v>10113</v>
+      </c>
+      <c r="D287">
+        <v>5</v>
+      </c>
+      <c r="E287" t="s">
+        <v>186</v>
+      </c>
+      <c r="F287" t="s">
+        <v>35</v>
+      </c>
+      <c r="G287" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G121" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="0"/>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7637675B-33C1-4CDA-AE53-D6D73427FF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC721DA-9D32-4F10-B452-2A48D7F81925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4790" yWindow="4270" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7740" yWindow="7360" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -728,23 +728,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1163,81 +1161,81 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="8" customFormat="1">
-      <c r="A3" s="9" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="8" customFormat="1">
-      <c r="A4" s="9" t="s">
+      <c r="G3" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>201</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="8" customFormat="1">
-      <c r="A5" s="9" t="s">
+      <c r="G4" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>195</v>
       </c>
       <c r="D5">
@@ -1253,14 +1251,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="8" customFormat="1">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" t="s">
         <v>199</v>
       </c>
       <c r="D6">
@@ -1276,14 +1274,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="8" customFormat="1">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>2500</v>
       </c>
       <c r="D7">

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A9544-3E11-4EA9-B23C-23EBA65A32C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3712FA22-FA50-42F0-9335-278B2E046DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="193">
   <si>
     <t>lang_code</t>
   </si>
@@ -87,9 +87,6 @@
     <t>fra</t>
   </si>
   <si>
-    <t>Maroc</t>
-  </si>
-  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -613,6 +610,12 @@
   </si>
   <si>
     <t>Ciudad</t>
+  </si>
+  <si>
+    <t>UTO</t>
+  </si>
+  <si>
+    <t>Utopia</t>
   </si>
 </sst>
 </file>
@@ -776,9 +779,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -816,7 +819,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -922,7 +925,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,7 +1067,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1074,15 +1077,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G281"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.46484375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="21.7265625" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" customWidth="1"/>
+    <col min="2" max="2" width="15.73046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" customWidth="1"/>
+    <col min="4" max="4" width="21.73046875" customWidth="1"/>
+    <col min="5" max="5" width="23.46484375" customWidth="1"/>
+    <col min="6" max="6" width="19.53125" customWidth="1"/>
+    <col min="7" max="7" width="19.265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1113,10 +1116,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1133,7 +1136,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -1153,16 +1156,16 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>11</v>
@@ -1173,19 +1176,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -1196,19 +1199,19 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>11</v>
@@ -1219,19 +1222,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
@@ -1242,19 +1245,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>11</v>
@@ -1265,19 +1268,19 @@
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
@@ -1288,19 +1291,19 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>11</v>
@@ -1311,19 +1314,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
@@ -1334,19 +1337,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
@@ -1357,19 +1360,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>11</v>
@@ -1380,19 +1383,19 @@
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>36</v>
       </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
@@ -1403,19 +1406,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" t="s">
-        <v>39</v>
-      </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>11</v>
@@ -1426,19 +1429,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>36</v>
       </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>11</v>
@@ -1449,30 +1452,30 @@
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.5">
+    <row r="18" spans="1:7" ht="22.15">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>14022</v>
@@ -1481,10 +1484,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
@@ -1495,19 +1498,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>11</v>
@@ -1518,19 +1521,19 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>11</v>
@@ -1541,19 +1544,19 @@
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>11</v>
@@ -1564,19 +1567,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
         <v>44</v>
       </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>11</v>
@@ -1587,30 +1590,30 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="22.5">
+    <row r="24" spans="1:7" ht="22.15">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>14053</v>
@@ -1619,10 +1622,10 @@
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>11</v>
@@ -1633,19 +1636,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" t="s">
         <v>43</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>11</v>
@@ -1656,19 +1659,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
         <v>48</v>
       </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>11</v>
@@ -1679,19 +1682,19 @@
         <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>11</v>
@@ -1702,19 +1705,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>11</v>
@@ -1725,30 +1728,30 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22.5">
+    <row r="30" spans="1:7" ht="22.15">
       <c r="A30" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>14023</v>
@@ -1757,10 +1760,10 @@
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>11</v>
@@ -1771,19 +1774,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>11</v>
@@ -1794,19 +1797,19 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
-        <v>53</v>
-      </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>11</v>
@@ -1817,19 +1820,19 @@
         <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>11</v>
@@ -1840,19 +1843,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" t="s">
-        <v>53</v>
-      </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>11</v>
@@ -1863,30 +1866,30 @@
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="22.5">
+    <row r="36" spans="1:7" ht="22.15">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>14000</v>
@@ -1895,10 +1898,10 @@
         <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>11</v>
@@ -1909,19 +1912,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>11</v>
@@ -1932,19 +1935,19 @@
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
         <v>56</v>
       </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>11</v>
@@ -1955,19 +1958,19 @@
         <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>11</v>
@@ -1978,19 +1981,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
         <v>56</v>
       </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>11</v>
@@ -2001,30 +2004,30 @@
         <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="22.5">
+    <row r="42" spans="1:7" ht="22.15">
       <c r="A42" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>14110</v>
@@ -2033,10 +2036,10 @@
         <v>5</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>11</v>
@@ -2047,19 +2050,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>11</v>
@@ -2070,19 +2073,19 @@
         <v>7</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="s">
         <v>60</v>
       </c>
-      <c r="C44" t="s">
-        <v>61</v>
-      </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>11</v>
@@ -2093,19 +2096,19 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>11</v>
@@ -2116,19 +2119,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
         <v>60</v>
       </c>
-      <c r="C46" t="s">
-        <v>61</v>
-      </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>11</v>
@@ -2139,30 +2142,30 @@
         <v>7</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D47">
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="22.5">
+    <row r="48" spans="1:7" ht="22.15">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48">
         <v>14080</v>
@@ -2171,10 +2174,10 @@
         <v>5</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>11</v>
@@ -2185,19 +2188,19 @@
         <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49">
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>11</v>
@@ -2208,19 +2211,19 @@
         <v>7</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
         <v>64</v>
       </c>
-      <c r="C50" t="s">
-        <v>65</v>
-      </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>11</v>
@@ -2231,19 +2234,19 @@
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>11</v>
@@ -2254,19 +2257,19 @@
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" t="s">
         <v>64</v>
       </c>
-      <c r="C52" t="s">
-        <v>65</v>
-      </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>11</v>
@@ -2277,30 +2280,30 @@
         <v>7</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D53">
         <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="22.5">
+    <row r="54" spans="1:7" ht="22.15">
       <c r="A54" t="s">
         <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54">
         <v>14025</v>
@@ -2309,10 +2312,10 @@
         <v>5</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>11</v>
@@ -2323,19 +2326,19 @@
         <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D55">
         <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>11</v>
@@ -2346,19 +2349,19 @@
         <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
         <v>68</v>
       </c>
-      <c r="C56" t="s">
-        <v>69</v>
-      </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>11</v>
@@ -2369,19 +2372,19 @@
         <v>12</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>11</v>
@@ -2392,19 +2395,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
         <v>68</v>
       </c>
-      <c r="C58" t="s">
-        <v>69</v>
-      </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>11</v>
@@ -2415,30 +2418,30 @@
         <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59">
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="22.5">
+    <row r="60" spans="1:7" ht="22.15">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>14050</v>
@@ -2447,10 +2450,10 @@
         <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>11</v>
@@ -2461,19 +2464,19 @@
         <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>11</v>
@@ -2484,19 +2487,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" t="s">
         <v>72</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>11</v>
@@ -2507,19 +2510,19 @@
         <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>11</v>
@@ -2530,19 +2533,19 @@
         <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
         <v>72</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>11</v>
@@ -2553,19 +2556,19 @@
         <v>7</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>11</v>
@@ -2576,19 +2579,19 @@
         <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>11</v>
@@ -2599,19 +2602,19 @@
         <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>11</v>
@@ -2622,19 +2625,19 @@
         <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
         <v>76</v>
       </c>
-      <c r="C68" t="s">
-        <v>77</v>
-      </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>11</v>
@@ -2645,19 +2648,19 @@
         <v>12</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>11</v>
@@ -2668,19 +2671,19 @@
         <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" t="s">
         <v>76</v>
       </c>
-      <c r="C70" t="s">
-        <v>77</v>
-      </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>11</v>
@@ -2691,30 +2694,30 @@
         <v>7</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71">
         <v>5</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.5">
+    <row r="72" spans="1:7" ht="22.15">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C72">
         <v>10106</v>
@@ -2723,10 +2726,10 @@
         <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>11</v>
@@ -2737,19 +2740,19 @@
         <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D73">
         <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>11</v>
@@ -2760,19 +2763,19 @@
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
         <v>80</v>
       </c>
-      <c r="C74" t="s">
-        <v>81</v>
-      </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>11</v>
@@ -2783,19 +2786,19 @@
         <v>12</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>11</v>
@@ -2806,19 +2809,19 @@
         <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
         <v>80</v>
       </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
       <c r="D76">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>11</v>
@@ -2829,30 +2832,30 @@
         <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D77">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="22.5">
+    <row r="78" spans="1:7" ht="22.15">
       <c r="A78" t="s">
         <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78">
         <v>10000</v>
@@ -2861,10 +2864,10 @@
         <v>5</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>11</v>
@@ -2875,19 +2878,19 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D79">
         <v>5</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>11</v>
@@ -2898,19 +2901,19 @@
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" t="s">
         <v>84</v>
       </c>
-      <c r="C80" t="s">
-        <v>85</v>
-      </c>
       <c r="D80">
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>11</v>
@@ -2921,19 +2924,19 @@
         <v>12</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>11</v>
@@ -2944,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
         <v>84</v>
       </c>
-      <c r="C82" t="s">
-        <v>85</v>
-      </c>
       <c r="D82">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>11</v>
@@ -2967,30 +2970,30 @@
         <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="22.5">
+    <row r="84" spans="1:7" ht="22.15">
       <c r="A84" t="s">
         <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84">
         <v>10105</v>
@@ -2999,10 +3002,10 @@
         <v>5</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>11</v>
@@ -3013,19 +3016,19 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D85">
         <v>5</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>11</v>
@@ -3036,19 +3039,19 @@
         <v>7</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" t="s">
         <v>88</v>
       </c>
-      <c r="C86" t="s">
-        <v>89</v>
-      </c>
       <c r="D86">
         <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>11</v>
@@ -3059,19 +3062,19 @@
         <v>12</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>11</v>
@@ -3082,19 +3085,19 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
         <v>88</v>
       </c>
-      <c r="C88" t="s">
-        <v>89</v>
-      </c>
       <c r="D88">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F88" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>11</v>
@@ -3105,30 +3108,30 @@
         <v>7</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D89">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="22.5">
+    <row r="90" spans="1:7" ht="22.15">
       <c r="A90" t="s">
         <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90">
         <v>10112</v>
@@ -3137,10 +3140,10 @@
         <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>11</v>
@@ -3151,19 +3154,19 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D91">
         <v>5</v>
       </c>
       <c r="E91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>11</v>
@@ -3174,19 +3177,19 @@
         <v>7</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" t="s">
         <v>92</v>
       </c>
-      <c r="C92" t="s">
-        <v>93</v>
-      </c>
       <c r="D92">
         <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>11</v>
@@ -3197,19 +3200,19 @@
         <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>11</v>
@@ -3220,19 +3223,19 @@
         <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C94" t="s">
         <v>92</v>
       </c>
-      <c r="C94" t="s">
-        <v>93</v>
-      </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>11</v>
@@ -3243,30 +3246,30 @@
         <v>7</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D95">
         <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="22.5">
+    <row r="96" spans="1:7" ht="22.15">
       <c r="A96" t="s">
         <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C96">
         <v>10104</v>
@@ -3275,10 +3278,10 @@
         <v>5</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F96" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>11</v>
@@ -3289,19 +3292,19 @@
         <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F97" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>11</v>
@@ -3312,19 +3315,19 @@
         <v>7</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" t="s">
         <v>96</v>
       </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
       <c r="D98">
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>11</v>
@@ -3335,19 +3338,19 @@
         <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>11</v>
@@ -3358,19 +3361,19 @@
         <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100">
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>11</v>
@@ -3381,30 +3384,30 @@
         <v>7</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D101">
         <v>5</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="22.5">
+    <row r="102" spans="1:7" ht="22.15">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C102">
         <v>10036</v>
@@ -3413,10 +3416,10 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>11</v>
@@ -3427,19 +3430,19 @@
         <v>15</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>11</v>
@@ -3450,19 +3453,19 @@
         <v>7</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104" t="s">
         <v>101</v>
       </c>
-      <c r="C104" t="s">
-        <v>102</v>
-      </c>
       <c r="D104">
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>11</v>
@@ -3473,19 +3476,19 @@
         <v>12</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>11</v>
@@ -3496,19 +3499,19 @@
         <v>15</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
         <v>101</v>
       </c>
-      <c r="C106" t="s">
-        <v>102</v>
-      </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F106" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>11</v>
@@ -3519,30 +3522,30 @@
         <v>7</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D107">
         <v>5</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="22.5">
+    <row r="108" spans="1:7" ht="22.15">
       <c r="A108" t="s">
         <v>12</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108">
         <v>10190</v>
@@ -3551,10 +3554,10 @@
         <v>5</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>11</v>
@@ -3565,19 +3568,19 @@
         <v>15</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D109">
         <v>5</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>11</v>
@@ -3588,19 +3591,19 @@
         <v>7</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>11</v>
@@ -3611,19 +3614,19 @@
         <v>7</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D111">
         <v>5</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>11</v>
@@ -3634,19 +3637,19 @@
         <v>7</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D112">
         <v>5</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>11</v>
@@ -3657,19 +3660,19 @@
         <v>7</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D113">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>11</v>
@@ -3680,19 +3683,19 @@
         <v>15</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>11</v>
@@ -3703,19 +3706,19 @@
         <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D115">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>11</v>
@@ -3726,19 +3729,19 @@
         <v>15</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D116">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>11</v>
@@ -3749,7 +3752,7 @@
         <v>15</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C117">
         <v>10114</v>
@@ -3758,21 +3761,21 @@
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="22.5">
+    <row r="118" spans="1:7" ht="22.15">
       <c r="A118" t="s">
         <v>12</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C118">
         <v>10111</v>
@@ -3781,21 +3784,21 @@
         <v>5</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="22.5">
+    <row r="119" spans="1:7" ht="22.15">
       <c r="A119" t="s">
         <v>12</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C119">
         <v>10114</v>
@@ -3804,21 +3807,21 @@
         <v>5</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="22.5">
+    <row r="120" spans="1:7" ht="22.15">
       <c r="A120" t="s">
         <v>12</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C120">
         <v>10113</v>
@@ -3827,21 +3830,21 @@
         <v>5</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="22.5">
+    <row r="121" spans="1:7" ht="22.15">
       <c r="A121" t="s">
         <v>12</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C121">
         <v>10110</v>
@@ -3850,10 +3853,10 @@
         <v>5</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>11</v>
@@ -3861,19 +3864,19 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>11</v>
@@ -3881,19 +3884,19 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -3904,22 +3907,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D124">
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F124" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>11</v>
@@ -3927,22 +3930,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D125">
         <v>3</v>
       </c>
       <c r="E125" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>11</v>
@@ -3950,22 +3953,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C126" t="s">
+        <v>116</v>
+      </c>
+      <c r="D126">
+        <v>4</v>
+      </c>
+      <c r="E126" t="s">
         <v>117</v>
       </c>
-      <c r="D126">
-        <v>4</v>
-      </c>
-      <c r="E126" t="s">
-        <v>118</v>
-      </c>
       <c r="F126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>11</v>
@@ -3973,22 +3976,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D127">
         <v>5</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>11</v>
@@ -3996,22 +3999,22 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D128">
         <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>11</v>
@@ -4019,22 +4022,22 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D129">
         <v>5</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F129" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>11</v>
@@ -4042,22 +4045,22 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C130" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D130">
         <v>4</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>11</v>
@@ -4065,22 +4068,22 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C131" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D131">
         <v>5</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>11</v>
@@ -4088,22 +4091,22 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D132">
         <v>4</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>11</v>
@@ -4111,22 +4114,22 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D133">
         <v>5</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F133" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>11</v>
@@ -4134,22 +4137,22 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D134">
         <v>4</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F134" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>11</v>
@@ -4157,22 +4160,22 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D135">
         <v>5</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F135" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>11</v>
@@ -4180,22 +4183,22 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D136">
         <v>4</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>11</v>
@@ -4203,22 +4206,22 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C137" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D137">
         <v>5</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F137" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>11</v>
@@ -4226,22 +4229,22 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C138" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D138">
         <v>4</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F138" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>11</v>
@@ -4249,22 +4252,22 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C139" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D139">
         <v>5</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F139" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>11</v>
@@ -4272,22 +4275,22 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C140" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D140">
         <v>4</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>11</v>
@@ -4295,22 +4298,22 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D141">
         <v>5</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F141" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>11</v>
@@ -4318,22 +4321,22 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D142">
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F142" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>11</v>
@@ -4341,22 +4344,22 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C143" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D143">
         <v>3</v>
       </c>
       <c r="E143" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>11</v>
@@ -4364,22 +4367,22 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D144">
         <v>4</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F144" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>11</v>
@@ -4387,22 +4390,22 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C145" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D145">
         <v>5</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>11</v>
@@ -4410,22 +4413,22 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D146">
         <v>4</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F146" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>11</v>
@@ -4433,22 +4436,22 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C147" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D147">
         <v>5</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F147" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>11</v>
@@ -4456,22 +4459,22 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D148">
         <v>4</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F148" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>11</v>
@@ -4479,22 +4482,22 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D149">
         <v>5</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>11</v>
@@ -4502,22 +4505,22 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D150">
         <v>4</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F150" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>11</v>
@@ -4525,22 +4528,22 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151">
         <v>5</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F151" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>11</v>
@@ -4548,22 +4551,22 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C152" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D152">
         <v>4</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F152" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>11</v>
@@ -4571,22 +4574,22 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C153" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153">
         <v>5</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F153" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>11</v>
@@ -4594,22 +4597,22 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D154">
         <v>4</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F154" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>11</v>
@@ -4617,22 +4620,22 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F155" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>11</v>
@@ -4640,22 +4643,22 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D156">
         <v>4</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F156" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>11</v>
@@ -4663,22 +4666,22 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C157" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D157">
         <v>5</v>
       </c>
       <c r="E157" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F157" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>11</v>
@@ -4686,22 +4689,22 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C158" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D158">
         <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F158" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>11</v>
@@ -4709,22 +4712,22 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D159">
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F159" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>11</v>
@@ -4732,22 +4735,22 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D160">
         <v>5</v>
       </c>
       <c r="E160" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F160" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>11</v>
@@ -4755,22 +4758,22 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D161">
         <v>5</v>
       </c>
       <c r="E161" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F161" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>11</v>
@@ -4778,19 +4781,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>11</v>
@@ -4798,19 +4801,19 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F163" t="s">
         <v>8</v>
@@ -4821,22 +4824,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D164">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F164" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>11</v>
@@ -4844,22 +4847,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D165">
         <v>3</v>
       </c>
       <c r="E165" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>11</v>
@@ -4867,22 +4870,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C166" t="s">
+        <v>142</v>
+      </c>
+      <c r="D166">
+        <v>4</v>
+      </c>
+      <c r="E166" t="s">
         <v>143</v>
       </c>
-      <c r="D166">
-        <v>4</v>
-      </c>
-      <c r="E166" t="s">
-        <v>144</v>
-      </c>
       <c r="F166" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>11</v>
@@ -4890,22 +4893,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C167" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D167">
         <v>5</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F167" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>11</v>
@@ -4913,22 +4916,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C168" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D168">
         <v>4</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F168" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>11</v>
@@ -4936,22 +4939,22 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D169">
         <v>5</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F169" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>11</v>
@@ -4959,22 +4962,22 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D170">
         <v>4</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F170" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>11</v>
@@ -4982,22 +4985,22 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C171" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D171">
         <v>5</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F171" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>11</v>
@@ -5005,22 +5008,22 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C172" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D172">
         <v>4</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F172" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>11</v>
@@ -5028,22 +5031,22 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C173" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D173">
         <v>5</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F173" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>11</v>
@@ -5051,22 +5054,22 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D174">
         <v>4</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>11</v>
@@ -5074,22 +5077,22 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C175" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D175">
         <v>5</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F175" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>11</v>
@@ -5097,22 +5100,22 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C176" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D176">
         <v>4</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F176" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>11</v>
@@ -5120,22 +5123,22 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C177" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D177">
         <v>5</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F177" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>11</v>
@@ -5143,22 +5146,22 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C178" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D178">
         <v>4</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F178" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>11</v>
@@ -5166,22 +5169,22 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C179" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D179">
         <v>5</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F179" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>11</v>
@@ -5189,22 +5192,22 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C180" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D180">
         <v>4</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>11</v>
@@ -5212,22 +5215,22 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C181" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D181">
         <v>5</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F181" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>11</v>
@@ -5235,22 +5238,22 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C182" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D182">
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F182" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>11</v>
@@ -5258,22 +5261,22 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C183" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D183">
         <v>3</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F183" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>11</v>
@@ -5281,22 +5284,22 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D184">
         <v>4</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F184" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>11</v>
@@ -5304,22 +5307,22 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C185" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D185">
         <v>5</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F185" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>11</v>
@@ -5327,22 +5330,22 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C186" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D186">
         <v>4</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>11</v>
@@ -5350,22 +5353,22 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C187" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D187">
         <v>5</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F187" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>11</v>
@@ -5373,22 +5376,22 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C188" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D188">
         <v>4</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>11</v>
@@ -5396,22 +5399,22 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C189" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D189">
         <v>5</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F189" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>11</v>
@@ -5419,22 +5422,22 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C190" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D190">
         <v>4</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F190" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>11</v>
@@ -5442,22 +5445,22 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C191" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D191">
         <v>5</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F191" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>11</v>
@@ -5465,22 +5468,22 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C192" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D192">
         <v>4</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F192" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>11</v>
@@ -5488,22 +5491,22 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C193" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D193">
         <v>5</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F193" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>11</v>
@@ -5511,22 +5514,22 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C194" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D194">
         <v>4</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F194" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>11</v>
@@ -5534,22 +5537,22 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C195" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D195">
         <v>5</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F195" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>11</v>
@@ -5557,22 +5560,22 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D196">
         <v>4</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F196" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>11</v>
@@ -5580,22 +5583,22 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C197" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D197">
         <v>5</v>
       </c>
       <c r="E197" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F197" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>11</v>
@@ -5603,22 +5606,22 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C198" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D198">
         <v>5</v>
       </c>
       <c r="E198" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F198" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>11</v>
@@ -5626,22 +5629,22 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C199" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D199">
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F199" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>11</v>
@@ -5649,22 +5652,22 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C200" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D200">
         <v>5</v>
       </c>
       <c r="E200" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F200" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>11</v>
@@ -5672,22 +5675,22 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C201" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D201">
         <v>5</v>
       </c>
       <c r="E201" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F201" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>11</v>
@@ -5695,7 +5698,7 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>8</v>
@@ -5707,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>11</v>
@@ -5715,19 +5718,19 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F203" t="s">
         <v>8</v>
@@ -5738,22 +5741,22 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F204" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>11</v>
@@ -5761,22 +5764,22 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C205" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D205">
         <v>3</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F205" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>11</v>
@@ -5784,22 +5787,22 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C206" t="s">
+        <v>167</v>
+      </c>
+      <c r="D206">
+        <v>4</v>
+      </c>
+      <c r="E206" t="s">
         <v>168</v>
       </c>
-      <c r="D206">
-        <v>4</v>
-      </c>
-      <c r="E206" t="s">
-        <v>169</v>
-      </c>
       <c r="F206" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>11</v>
@@ -5807,22 +5810,22 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C207" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D207">
         <v>5</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>11</v>
@@ -5830,22 +5833,22 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C208" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D208">
         <v>4</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F208" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>11</v>
@@ -5853,22 +5856,22 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D209">
         <v>5</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F209" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>11</v>
@@ -5876,22 +5879,22 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C210" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D210">
         <v>4</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F210" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>11</v>
@@ -5899,22 +5902,22 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C211" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D211">
         <v>5</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F211" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>11</v>
@@ -5922,22 +5925,22 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C212" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D212">
         <v>4</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F212" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>11</v>
@@ -5945,22 +5948,22 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C213" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D213">
         <v>5</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F213" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>11</v>
@@ -5968,22 +5971,22 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B214" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C214" t="s">
         <v>56</v>
       </c>
-      <c r="C214" t="s">
-        <v>57</v>
-      </c>
       <c r="D214">
         <v>4</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>11</v>
@@ -5991,22 +5994,22 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C215" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D215">
         <v>5</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F215" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>11</v>
@@ -6014,22 +6017,22 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C216" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D216">
         <v>4</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F216" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>11</v>
@@ -6037,22 +6040,22 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C217" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D217">
         <v>5</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F217" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>11</v>
@@ -6060,22 +6063,22 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D218">
         <v>4</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>11</v>
@@ -6083,22 +6086,22 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C219" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D219">
         <v>5</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F219" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>11</v>
@@ -6106,22 +6109,22 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C220" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D220">
         <v>4</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F220" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>11</v>
@@ -6129,22 +6132,22 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C221" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D221">
         <v>5</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F221" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>11</v>
@@ -6152,22 +6155,22 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C222" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D222">
         <v>2</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F222" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>11</v>
@@ -6175,22 +6178,22 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C223" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D223">
         <v>3</v>
       </c>
       <c r="E223" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F223" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>11</v>
@@ -6198,22 +6201,22 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C224" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D224">
         <v>4</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F224" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>11</v>
@@ -6221,22 +6224,22 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C225" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D225">
         <v>5</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F225" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>11</v>
@@ -6244,22 +6247,22 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D226">
         <v>4</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F226" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>11</v>
@@ -6267,22 +6270,22 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C227" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D227">
         <v>5</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F227" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>11</v>
@@ -6290,22 +6293,22 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B228" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C228" t="s">
         <v>84</v>
       </c>
-      <c r="C228" t="s">
-        <v>85</v>
-      </c>
       <c r="D228">
         <v>4</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F228" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>11</v>
@@ -6313,22 +6316,22 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C229" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D229">
         <v>5</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F229" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>11</v>
@@ -6336,22 +6339,22 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D230">
         <v>4</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F230" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>11</v>
@@ -6359,22 +6362,22 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C231" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D231">
         <v>5</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>11</v>
@@ -6382,22 +6385,22 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C232" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D232">
         <v>4</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F232" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>11</v>
@@ -6405,22 +6408,22 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C233" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D233">
         <v>5</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F233" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>11</v>
@@ -6428,22 +6431,22 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D234">
         <v>4</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F234" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>11</v>
@@ -6451,22 +6454,22 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C235" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D235">
         <v>5</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F235" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>11</v>
@@ -6474,22 +6477,22 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C236" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D236">
         <v>4</v>
       </c>
       <c r="E236" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F236" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>11</v>
@@ -6497,22 +6500,22 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C237" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D237">
         <v>5</v>
       </c>
       <c r="E237" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F237" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>11</v>
@@ -6520,22 +6523,22 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C238" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D238">
         <v>5</v>
       </c>
       <c r="E238" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>11</v>
@@ -6543,22 +6546,22 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C239" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D239">
         <v>5</v>
       </c>
       <c r="E239" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F239" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>11</v>
@@ -6566,22 +6569,22 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C240" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D240">
         <v>5</v>
       </c>
       <c r="E240" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>11</v>
@@ -6589,22 +6592,22 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C241" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D241">
         <v>5</v>
       </c>
       <c r="E241" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F241" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>11</v>
@@ -6612,22 +6615,22 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
+        <v>183</v>
+      </c>
+      <c r="B242" t="s">
+        <v>87</v>
+      </c>
+      <c r="C242" t="s">
+        <v>88</v>
+      </c>
+      <c r="D242">
+        <v>4</v>
+      </c>
+      <c r="E242" t="s">
         <v>184</v>
       </c>
-      <c r="B242" t="s">
-        <v>88</v>
-      </c>
-      <c r="C242" t="s">
-        <v>89</v>
-      </c>
-      <c r="D242">
-        <v>4</v>
-      </c>
-      <c r="E242" t="s">
-        <v>185</v>
-      </c>
       <c r="F242" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G242" t="b">
         <v>1</v>
@@ -6635,7 +6638,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B243">
         <v>10114</v>
@@ -6647,10 +6650,10 @@
         <v>5</v>
       </c>
       <c r="E243" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
@@ -6658,19 +6661,19 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B244" t="s">
         <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D244">
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G244" t="b">
         <v>1</v>
@@ -6678,19 +6681,19 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B245" t="s">
+        <v>17</v>
+      </c>
+      <c r="C245" t="s">
         <v>18</v>
-      </c>
-      <c r="C245" t="s">
-        <v>19</v>
       </c>
       <c r="D245">
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F245" t="s">
         <v>8</v>
@@ -6701,22 +6704,22 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B246" t="s">
+        <v>24</v>
+      </c>
+      <c r="C246" t="s">
         <v>25</v>
-      </c>
-      <c r="C246" t="s">
-        <v>26</v>
       </c>
       <c r="D246">
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F246" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G246" t="b">
         <v>1</v>
@@ -6724,22 +6727,22 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B247" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D247">
         <v>3</v>
       </c>
       <c r="E247" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F247" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G247" t="b">
         <v>1</v>
@@ -6747,22 +6750,22 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
+        <v>183</v>
+      </c>
+      <c r="B248" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" t="s">
+        <v>35</v>
+      </c>
+      <c r="D248">
+        <v>4</v>
+      </c>
+      <c r="E248" t="s">
         <v>184</v>
       </c>
-      <c r="B248" t="s">
-        <v>35</v>
-      </c>
-      <c r="C248" t="s">
-        <v>36</v>
-      </c>
-      <c r="D248">
-        <v>4</v>
-      </c>
-      <c r="E248" t="s">
-        <v>185</v>
-      </c>
       <c r="F248" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
@@ -6770,7 +6773,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B249">
         <v>14022</v>
@@ -6782,10 +6785,10 @@
         <v>5</v>
       </c>
       <c r="E249" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F249" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G249" t="b">
         <v>1</v>
@@ -6793,22 +6796,22 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
+        <v>183</v>
+      </c>
+      <c r="B250" t="s">
+        <v>43</v>
+      </c>
+      <c r="C250" t="s">
+        <v>44</v>
+      </c>
+      <c r="D250">
+        <v>4</v>
+      </c>
+      <c r="E250" t="s">
         <v>184</v>
       </c>
-      <c r="B250" t="s">
-        <v>44</v>
-      </c>
-      <c r="C250" t="s">
-        <v>45</v>
-      </c>
-      <c r="D250">
-        <v>4</v>
-      </c>
-      <c r="E250" t="s">
-        <v>185</v>
-      </c>
       <c r="F250" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
@@ -6816,7 +6819,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B251">
         <v>14053</v>
@@ -6828,10 +6831,10 @@
         <v>5</v>
       </c>
       <c r="E251" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
@@ -6839,22 +6842,22 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
+        <v>183</v>
+      </c>
+      <c r="B252" t="s">
+        <v>47</v>
+      </c>
+      <c r="C252" t="s">
+        <v>48</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+      <c r="E252" t="s">
         <v>184</v>
       </c>
-      <c r="B252" t="s">
-        <v>48</v>
-      </c>
-      <c r="C252" t="s">
-        <v>49</v>
-      </c>
-      <c r="D252">
-        <v>4</v>
-      </c>
-      <c r="E252" t="s">
-        <v>185</v>
-      </c>
       <c r="F252" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
@@ -6862,7 +6865,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B253">
         <v>14023</v>
@@ -6874,10 +6877,10 @@
         <v>5</v>
       </c>
       <c r="E253" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F253" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
@@ -6885,22 +6888,22 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
+        <v>183</v>
+      </c>
+      <c r="B254" t="s">
+        <v>51</v>
+      </c>
+      <c r="C254" t="s">
+        <v>52</v>
+      </c>
+      <c r="D254">
+        <v>4</v>
+      </c>
+      <c r="E254" t="s">
         <v>184</v>
       </c>
-      <c r="B254" t="s">
-        <v>52</v>
-      </c>
-      <c r="C254" t="s">
-        <v>53</v>
-      </c>
-      <c r="D254">
-        <v>4</v>
-      </c>
-      <c r="E254" t="s">
-        <v>185</v>
-      </c>
       <c r="F254" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G254" t="b">
         <v>1</v>
@@ -6908,7 +6911,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B255">
         <v>14000</v>
@@ -6920,10 +6923,10 @@
         <v>5</v>
       </c>
       <c r="E255" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F255" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
@@ -6931,22 +6934,22 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
+        <v>183</v>
+      </c>
+      <c r="B256" t="s">
+        <v>55</v>
+      </c>
+      <c r="C256" t="s">
+        <v>56</v>
+      </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
+      <c r="E256" t="s">
         <v>184</v>
       </c>
-      <c r="B256" t="s">
-        <v>56</v>
-      </c>
-      <c r="C256" t="s">
-        <v>57</v>
-      </c>
-      <c r="D256">
-        <v>4</v>
-      </c>
-      <c r="E256" t="s">
-        <v>185</v>
-      </c>
       <c r="F256" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G256" t="b">
         <v>1</v>
@@ -6954,7 +6957,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B257">
         <v>14110</v>
@@ -6966,10 +6969,10 @@
         <v>5</v>
       </c>
       <c r="E257" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G257" t="b">
         <v>1</v>
@@ -6977,22 +6980,22 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
+        <v>183</v>
+      </c>
+      <c r="B258" t="s">
+        <v>59</v>
+      </c>
+      <c r="C258" t="s">
+        <v>60</v>
+      </c>
+      <c r="D258">
+        <v>4</v>
+      </c>
+      <c r="E258" t="s">
         <v>184</v>
       </c>
-      <c r="B258" t="s">
-        <v>60</v>
-      </c>
-      <c r="C258" t="s">
-        <v>61</v>
-      </c>
-      <c r="D258">
-        <v>4</v>
-      </c>
-      <c r="E258" t="s">
-        <v>185</v>
-      </c>
       <c r="F258" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G258" t="b">
         <v>1</v>
@@ -7000,7 +7003,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B259">
         <v>14080</v>
@@ -7012,10 +7015,10 @@
         <v>5</v>
       </c>
       <c r="E259" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F259" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
@@ -7023,22 +7026,22 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
+        <v>183</v>
+      </c>
+      <c r="B260" t="s">
+        <v>63</v>
+      </c>
+      <c r="C260" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260">
+        <v>4</v>
+      </c>
+      <c r="E260" t="s">
         <v>184</v>
       </c>
-      <c r="B260" t="s">
-        <v>64</v>
-      </c>
-      <c r="C260" t="s">
-        <v>65</v>
-      </c>
-      <c r="D260">
-        <v>4</v>
-      </c>
-      <c r="E260" t="s">
-        <v>185</v>
-      </c>
       <c r="F260" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
@@ -7046,7 +7049,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B261">
         <v>14025</v>
@@ -7058,10 +7061,10 @@
         <v>5</v>
       </c>
       <c r="E261" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F261" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
@@ -7069,22 +7072,22 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
+        <v>183</v>
+      </c>
+      <c r="B262" t="s">
+        <v>67</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262">
+        <v>4</v>
+      </c>
+      <c r="E262" t="s">
         <v>184</v>
       </c>
-      <c r="B262" t="s">
-        <v>68</v>
-      </c>
-      <c r="C262" t="s">
-        <v>69</v>
-      </c>
-      <c r="D262">
-        <v>4</v>
-      </c>
-      <c r="E262" t="s">
-        <v>185</v>
-      </c>
       <c r="F262" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
@@ -7092,7 +7095,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B263">
         <v>14050</v>
@@ -7104,10 +7107,10 @@
         <v>5</v>
       </c>
       <c r="E263" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F263" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
@@ -7115,22 +7118,22 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B264" t="s">
+        <v>71</v>
+      </c>
+      <c r="C264" t="s">
         <v>72</v>
-      </c>
-      <c r="C264" t="s">
-        <v>73</v>
       </c>
       <c r="D264">
         <v>2</v>
       </c>
       <c r="E264" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F264" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
@@ -7138,22 +7141,22 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B265" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C265" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D265">
         <v>3</v>
       </c>
       <c r="E265" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F265" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
@@ -7161,22 +7164,22 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
+        <v>183</v>
+      </c>
+      <c r="B266" t="s">
+        <v>75</v>
+      </c>
+      <c r="C266" t="s">
+        <v>76</v>
+      </c>
+      <c r="D266">
+        <v>4</v>
+      </c>
+      <c r="E266" t="s">
         <v>184</v>
       </c>
-      <c r="B266" t="s">
-        <v>76</v>
-      </c>
-      <c r="C266" t="s">
-        <v>77</v>
-      </c>
-      <c r="D266">
-        <v>4</v>
-      </c>
-      <c r="E266" t="s">
-        <v>185</v>
-      </c>
       <c r="F266" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
@@ -7184,7 +7187,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B267">
         <v>10106</v>
@@ -7196,10 +7199,10 @@
         <v>5</v>
       </c>
       <c r="E267" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
@@ -7207,22 +7210,22 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
+        <v>183</v>
+      </c>
+      <c r="B268" t="s">
+        <v>79</v>
+      </c>
+      <c r="C268" t="s">
+        <v>80</v>
+      </c>
+      <c r="D268">
+        <v>4</v>
+      </c>
+      <c r="E268" t="s">
         <v>184</v>
       </c>
-      <c r="B268" t="s">
-        <v>80</v>
-      </c>
-      <c r="C268" t="s">
-        <v>81</v>
-      </c>
-      <c r="D268">
-        <v>4</v>
-      </c>
-      <c r="E268" t="s">
-        <v>185</v>
-      </c>
       <c r="F268" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B269">
         <v>10000</v>
@@ -7242,10 +7245,10 @@
         <v>5</v>
       </c>
       <c r="E269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F269" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
@@ -7253,22 +7256,22 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
+        <v>183</v>
+      </c>
+      <c r="B270" t="s">
+        <v>83</v>
+      </c>
+      <c r="C270" t="s">
+        <v>84</v>
+      </c>
+      <c r="D270">
+        <v>4</v>
+      </c>
+      <c r="E270" t="s">
         <v>184</v>
       </c>
-      <c r="B270" t="s">
-        <v>84</v>
-      </c>
-      <c r="C270" t="s">
-        <v>85</v>
-      </c>
-      <c r="D270">
-        <v>4</v>
-      </c>
-      <c r="E270" t="s">
-        <v>185</v>
-      </c>
       <c r="F270" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G270" t="b">
         <v>1</v>
@@ -7276,7 +7279,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B271">
         <v>10105</v>
@@ -7288,10 +7291,10 @@
         <v>5</v>
       </c>
       <c r="E271" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F271" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
@@ -7299,7 +7302,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B272">
         <v>10112</v>
@@ -7311,10 +7314,10 @@
         <v>5</v>
       </c>
       <c r="E272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F272" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G272" t="b">
         <v>1</v>
@@ -7322,22 +7325,22 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
+        <v>183</v>
+      </c>
+      <c r="B273" t="s">
+        <v>91</v>
+      </c>
+      <c r="C273" t="s">
+        <v>92</v>
+      </c>
+      <c r="D273">
+        <v>4</v>
+      </c>
+      <c r="E273" t="s">
         <v>184</v>
       </c>
-      <c r="B273" t="s">
-        <v>92</v>
-      </c>
-      <c r="C273" t="s">
-        <v>93</v>
-      </c>
-      <c r="D273">
-        <v>4</v>
-      </c>
-      <c r="E273" t="s">
-        <v>185</v>
-      </c>
       <c r="F273" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
@@ -7345,7 +7348,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B274">
         <v>10104</v>
@@ -7357,10 +7360,10 @@
         <v>5</v>
       </c>
       <c r="E274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F274" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
@@ -7368,22 +7371,22 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
+        <v>183</v>
+      </c>
+      <c r="B275" t="s">
+        <v>95</v>
+      </c>
+      <c r="C275" t="s">
+        <v>96</v>
+      </c>
+      <c r="D275">
+        <v>4</v>
+      </c>
+      <c r="E275" t="s">
         <v>184</v>
       </c>
-      <c r="B275" t="s">
-        <v>96</v>
-      </c>
-      <c r="C275" t="s">
-        <v>97</v>
-      </c>
-      <c r="D275">
-        <v>4</v>
-      </c>
-      <c r="E275" t="s">
-        <v>185</v>
-      </c>
       <c r="F275" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
@@ -7391,7 +7394,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B276">
         <v>10036</v>
@@ -7403,10 +7406,10 @@
         <v>5</v>
       </c>
       <c r="E276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F276" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
@@ -7414,22 +7417,22 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
+        <v>183</v>
+      </c>
+      <c r="B277" t="s">
+        <v>100</v>
+      </c>
+      <c r="C277" t="s">
+        <v>101</v>
+      </c>
+      <c r="D277">
+        <v>4</v>
+      </c>
+      <c r="E277" t="s">
         <v>184</v>
       </c>
-      <c r="B277" t="s">
-        <v>101</v>
-      </c>
-      <c r="C277" t="s">
-        <v>102</v>
-      </c>
-      <c r="D277">
-        <v>4</v>
-      </c>
-      <c r="E277" t="s">
-        <v>185</v>
-      </c>
       <c r="F277" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
@@ -7437,7 +7440,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B278">
         <v>10190</v>
@@ -7449,10 +7452,10 @@
         <v>5</v>
       </c>
       <c r="E278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F278" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
@@ -7460,7 +7463,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B279">
         <v>10110</v>
@@ -7472,10 +7475,10 @@
         <v>5</v>
       </c>
       <c r="E279" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F279" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
@@ -7483,7 +7486,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B280">
         <v>10111</v>
@@ -7495,10 +7498,10 @@
         <v>5</v>
       </c>
       <c r="E280" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F280" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G280" t="b">
         <v>1</v>
@@ -7506,7 +7509,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B281">
         <v>10113</v>
@@ -7518,10 +7521,10 @@
         <v>5</v>
       </c>
       <c r="E281" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F281" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G281" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA69F8F-4026-4C40-8C22-EF10A125BB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A9544-3E11-4EA9-B23C-23EBA65A32C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
   <si>
     <t>lang_code</t>
   </si>
@@ -63,6 +63,12 @@
     <t>eng</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>MyCountry</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -81,6 +87,9 @@
     <t>fra</t>
   </si>
   <si>
+    <t>Maroc</t>
+  </si>
+  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -591,6 +600,9 @@
     <t xml:space="preserve"> Código Postal</t>
   </si>
   <si>
+    <t>MyPaís</t>
+  </si>
+  <si>
     <t>País</t>
   </si>
   <si>
@@ -601,12 +613,6 @@
   </si>
   <si>
     <t>Ciudad</t>
-  </si>
-  <si>
-    <t>UTO</t>
-  </si>
-  <si>
-    <t>Utopia</t>
   </si>
 </sst>
 </file>
@@ -770,9 +776,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -810,7 +816,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -916,7 +922,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1058,7 +1064,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1066,16 +1072,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G281"/>
-  <sheetFormatPr defaultColWidth="8.46484375" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.265625" customWidth="1"/>
-    <col min="2" max="2" width="15.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.796875" customWidth="1"/>
-    <col min="4" max="4" width="21.73046875" customWidth="1"/>
-    <col min="5" max="5" width="23.46484375" customWidth="1"/>
-    <col min="6" max="6" width="19.53125" customWidth="1"/>
-    <col min="7" max="7" width="19.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.54296875" customWidth="1"/>
+    <col min="7" max="7" width="19.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1106,59 +1113,59 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1166,68 +1173,68 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1235,68 +1242,68 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1304,68 +1311,68 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1373,68 +1380,68 @@
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1442,30 +1449,30 @@
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="22.5">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>14022</v>
@@ -1474,36 +1481,36 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1511,68 +1518,68 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1580,30 +1587,30 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="22.5">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>14053</v>
@@ -1612,36 +1619,36 @@
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
         <v>44</v>
       </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25">
-        <v>5</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1649,68 +1656,68 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1718,30 +1725,30 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
         <v>48</v>
       </c>
-      <c r="C29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s">
-        <v>45</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="22.5">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>14023</v>
@@ -1750,36 +1757,36 @@
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
         <v>48</v>
       </c>
-      <c r="C31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31">
-        <v>5</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" t="s">
-        <v>45</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1787,68 +1794,68 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1856,30 +1863,30 @@
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" t="s">
         <v>52</v>
       </c>
-      <c r="C35" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="22.5">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C36">
         <v>14000</v>
@@ -1888,36 +1895,36 @@
         <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37">
-        <v>5</v>
-      </c>
-      <c r="E37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1925,68 +1932,68 @@
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1994,30 +2001,30 @@
         <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" t="s">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="22.5">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C42">
         <v>14110</v>
@@ -2026,36 +2033,36 @@
         <v>5</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" t="s">
         <v>56</v>
       </c>
-      <c r="C43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-      <c r="E43" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2063,68 +2070,68 @@
         <v>7</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2132,30 +2139,30 @@
         <v>7</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47" t="s">
         <v>60</v>
       </c>
-      <c r="C47" t="s">
-        <v>60</v>
-      </c>
-      <c r="D47">
-        <v>5</v>
-      </c>
-      <c r="E47" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="22.5">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>14080</v>
@@ -2164,36 +2171,36 @@
         <v>5</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" t="s">
         <v>60</v>
       </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" t="s">
-        <v>57</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2201,68 +2208,68 @@
         <v>7</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F50" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2270,30 +2277,30 @@
         <v>7</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D53">
-        <v>5</v>
-      </c>
-      <c r="E53" t="s">
-        <v>38</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="22.5">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C54">
         <v>14025</v>
@@ -2302,36 +2309,36 @@
         <v>5</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" t="s">
         <v>64</v>
       </c>
-      <c r="C55" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55">
-        <v>5</v>
-      </c>
-      <c r="E55" t="s">
-        <v>40</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2339,68 +2346,68 @@
         <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F58" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2408,30 +2415,30 @@
         <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59" t="s">
+        <v>41</v>
+      </c>
+      <c r="F59" t="s">
         <v>68</v>
       </c>
-      <c r="C59" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59">
-        <v>5</v>
-      </c>
-      <c r="E59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
       <c r="G59" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="22.5">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C60">
         <v>14050</v>
@@ -2440,36 +2447,36 @@
         <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F60" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" t="s">
         <v>68</v>
       </c>
-      <c r="C61" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61">
-        <v>5</v>
-      </c>
-      <c r="E61" t="s">
-        <v>40</v>
-      </c>
-      <c r="F61" t="s">
-        <v>65</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2477,68 +2484,68 @@
         <v>7</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2546,68 +2553,68 @@
         <v>7</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2615,68 +2622,68 @@
         <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
+        <v>78</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F69" t="s">
         <v>75</v>
       </c>
-      <c r="D69">
-        <v>4</v>
-      </c>
-      <c r="E69" t="s">
-        <v>36</v>
-      </c>
-      <c r="F69" t="s">
-        <v>72</v>
-      </c>
       <c r="G69" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2684,30 +2691,30 @@
         <v>7</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
         <v>76</v>
       </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71">
-        <v>5</v>
-      </c>
-      <c r="E71" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" t="s">
-        <v>73</v>
-      </c>
       <c r="G71" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="22.5">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C72">
         <v>10106</v>
@@ -2716,36 +2723,36 @@
         <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73" t="s">
+        <v>43</v>
+      </c>
+      <c r="F73" t="s">
         <v>76</v>
       </c>
-      <c r="C73" t="s">
-        <v>76</v>
-      </c>
-      <c r="D73">
-        <v>5</v>
-      </c>
-      <c r="E73" t="s">
-        <v>40</v>
-      </c>
-      <c r="F73" t="s">
-        <v>73</v>
-      </c>
       <c r="G73" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2753,68 +2760,68 @@
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F74" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F75" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D76">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2822,30 +2829,30 @@
         <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" t="s">
         <v>80</v>
       </c>
-      <c r="C77" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77">
-        <v>5</v>
-      </c>
-      <c r="E77" t="s">
-        <v>38</v>
-      </c>
-      <c r="F77" t="s">
-        <v>77</v>
-      </c>
       <c r="G77" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="22.5">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C78">
         <v>10000</v>
@@ -2854,36 +2861,36 @@
         <v>5</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+      <c r="E79" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79">
-        <v>5</v>
-      </c>
-      <c r="E79" t="s">
-        <v>40</v>
-      </c>
-      <c r="F79" t="s">
-        <v>77</v>
-      </c>
       <c r="G79" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2891,68 +2898,68 @@
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D80">
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F80" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F81" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D82">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F82" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2960,30 +2967,30 @@
         <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83">
+        <v>5</v>
+      </c>
+      <c r="E83" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>84</v>
-      </c>
-      <c r="D83">
-        <v>5</v>
-      </c>
-      <c r="E83" t="s">
-        <v>38</v>
-      </c>
-      <c r="F83" t="s">
-        <v>81</v>
-      </c>
       <c r="G83" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="22.5">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C84">
         <v>10105</v>
@@ -2992,36 +2999,36 @@
         <v>5</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F84" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+      <c r="E85" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" t="s">
         <v>84</v>
       </c>
-      <c r="C85" t="s">
-        <v>84</v>
-      </c>
-      <c r="D85">
-        <v>5</v>
-      </c>
-      <c r="E85" t="s">
-        <v>40</v>
-      </c>
-      <c r="F85" t="s">
-        <v>81</v>
-      </c>
       <c r="G85" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3029,68 +3036,68 @@
         <v>7</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D86">
         <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F86" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D87">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F87" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D88">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F88" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3098,30 +3105,30 @@
         <v>7</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89">
+        <v>5</v>
+      </c>
+      <c r="E89" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" t="s">
         <v>88</v>
       </c>
-      <c r="C89" t="s">
-        <v>88</v>
-      </c>
-      <c r="D89">
-        <v>5</v>
-      </c>
-      <c r="E89" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" t="s">
-        <v>85</v>
-      </c>
       <c r="G89" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="22.5">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C90">
         <v>10112</v>
@@ -3130,36 +3137,36 @@
         <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F90" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C91" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+      <c r="E91" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" t="s">
         <v>88</v>
       </c>
-      <c r="C91" t="s">
-        <v>88</v>
-      </c>
-      <c r="D91">
-        <v>5</v>
-      </c>
-      <c r="E91" t="s">
-        <v>40</v>
-      </c>
-      <c r="F91" t="s">
-        <v>85</v>
-      </c>
       <c r="G91" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3167,68 +3174,68 @@
         <v>7</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D92">
         <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F92" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D93">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F93" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3236,30 +3243,30 @@
         <v>7</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" t="s">
+        <v>95</v>
+      </c>
+      <c r="D95">
+        <v>5</v>
+      </c>
+      <c r="E95" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" t="s">
         <v>92</v>
       </c>
-      <c r="C95" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95">
-        <v>5</v>
-      </c>
-      <c r="E95" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" t="s">
-        <v>89</v>
-      </c>
       <c r="G95" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="22.5">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C96">
         <v>10104</v>
@@ -3268,36 +3275,36 @@
         <v>5</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F96" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" t="s">
+        <v>95</v>
+      </c>
+      <c r="D97">
+        <v>5</v>
+      </c>
+      <c r="E97" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" t="s">
         <v>92</v>
       </c>
-      <c r="C97" t="s">
-        <v>92</v>
-      </c>
-      <c r="D97">
-        <v>5</v>
-      </c>
-      <c r="E97" t="s">
-        <v>40</v>
-      </c>
-      <c r="F97" t="s">
-        <v>89</v>
-      </c>
       <c r="G97" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3305,68 +3312,68 @@
         <v>7</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D98">
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F98" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C99" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D99">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F99" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C100" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D100">
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3374,30 +3381,30 @@
         <v>7</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D101">
         <v>5</v>
       </c>
       <c r="E101" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F101" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="22.5">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C102">
         <v>10036</v>
@@ -3406,36 +3413,36 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F102" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3443,68 +3450,68 @@
         <v>7</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D104">
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F104" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F105" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F106" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3512,30 +3519,30 @@
         <v>7</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107">
+        <v>5</v>
+      </c>
+      <c r="E107" t="s">
+        <v>41</v>
+      </c>
+      <c r="F107" t="s">
         <v>101</v>
       </c>
-      <c r="C107" t="s">
-        <v>101</v>
-      </c>
-      <c r="D107">
-        <v>5</v>
-      </c>
-      <c r="E107" t="s">
-        <v>38</v>
-      </c>
-      <c r="F107" t="s">
-        <v>98</v>
-      </c>
       <c r="G107" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="22.5">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C108">
         <v>10190</v>
@@ -3544,36 +3551,36 @@
         <v>5</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F108" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C109" t="s">
+        <v>104</v>
+      </c>
+      <c r="D109">
+        <v>5</v>
+      </c>
+      <c r="E109" t="s">
+        <v>43</v>
+      </c>
+      <c r="F109" t="s">
         <v>101</v>
       </c>
-      <c r="C109" t="s">
-        <v>101</v>
-      </c>
-      <c r="D109">
-        <v>5</v>
-      </c>
-      <c r="E109" t="s">
-        <v>40</v>
-      </c>
-      <c r="F109" t="s">
-        <v>98</v>
-      </c>
       <c r="G109" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3581,22 +3588,22 @@
         <v>7</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C110" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F110" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3604,22 +3611,22 @@
         <v>7</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D111">
         <v>5</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3627,22 +3634,22 @@
         <v>7</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C112" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D112">
         <v>5</v>
       </c>
       <c r="E112" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3650,99 +3657,99 @@
         <v>7</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C113" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D113">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F113" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F114" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C115" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D115">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F115" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D116">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F116" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C117">
         <v>10114</v>
@@ -3751,21 +3758,21 @@
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F117" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="22.5">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C118">
         <v>10111</v>
@@ -3774,21 +3781,21 @@
         <v>5</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F118" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="22.5">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C119">
         <v>10114</v>
@@ -3797,21 +3804,21 @@
         <v>5</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F119" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="22.5">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C120">
         <v>10113</v>
@@ -3820,21 +3827,21 @@
         <v>5</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F120" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="22.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="22.5">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C121">
         <v>10110</v>
@@ -3843,2784 +3850,2784 @@
         <v>5</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F121" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F123" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D124">
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F124" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C125" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D125">
         <v>3</v>
       </c>
       <c r="E125" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F125" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D126">
         <v>4</v>
       </c>
       <c r="E126" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F126" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C127" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D127">
         <v>5</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F127" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C128" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D128">
         <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F128" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C129" t="s">
+        <v>47</v>
+      </c>
+      <c r="D129">
+        <v>5</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F129" t="s">
         <v>44</v>
       </c>
-      <c r="C129" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129">
-        <v>5</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F129" t="s">
-        <v>41</v>
-      </c>
       <c r="G129" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C130" t="s">
+        <v>121</v>
+      </c>
+      <c r="D130">
+        <v>4</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D130">
-        <v>4</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="F130" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C131" t="s">
+        <v>51</v>
+      </c>
+      <c r="D131">
+        <v>5</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F131" t="s">
         <v>48</v>
       </c>
-      <c r="C131" t="s">
-        <v>48</v>
-      </c>
-      <c r="D131">
-        <v>5</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F131" t="s">
-        <v>45</v>
-      </c>
       <c r="G131" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C132" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D132">
         <v>4</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C133" t="s">
+        <v>55</v>
+      </c>
+      <c r="D133">
+        <v>5</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F133" t="s">
         <v>52</v>
       </c>
-      <c r="C133" t="s">
-        <v>52</v>
-      </c>
-      <c r="D133">
-        <v>5</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F133" t="s">
-        <v>49</v>
-      </c>
       <c r="G133" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D134">
         <v>4</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F134" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135" t="s">
+        <v>59</v>
+      </c>
+      <c r="D135">
+        <v>5</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F135" t="s">
         <v>56</v>
       </c>
-      <c r="C135" t="s">
-        <v>56</v>
-      </c>
-      <c r="D135">
-        <v>5</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F135" t="s">
-        <v>53</v>
-      </c>
       <c r="G135" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C136" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D136">
         <v>4</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F136" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C137" t="s">
+        <v>63</v>
+      </c>
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F137" t="s">
         <v>60</v>
       </c>
-      <c r="C137" t="s">
-        <v>60</v>
-      </c>
-      <c r="D137">
-        <v>5</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F137" t="s">
-        <v>57</v>
-      </c>
       <c r="G137" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C138" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D138">
         <v>4</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F138" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C139" t="s">
+        <v>67</v>
+      </c>
+      <c r="D139">
+        <v>5</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F139" t="s">
         <v>64</v>
       </c>
-      <c r="C139" t="s">
-        <v>64</v>
-      </c>
-      <c r="D139">
-        <v>5</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F139" t="s">
-        <v>61</v>
-      </c>
       <c r="G139" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C140" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D140">
         <v>4</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F140" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C141" t="s">
+        <v>71</v>
+      </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F141" t="s">
         <v>68</v>
       </c>
-      <c r="C141" t="s">
-        <v>68</v>
-      </c>
-      <c r="D141">
-        <v>5</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F141" t="s">
-        <v>65</v>
-      </c>
       <c r="G141" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C142" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D142">
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C143" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D143">
         <v>3</v>
       </c>
       <c r="E143" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F143" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C144" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D144">
         <v>4</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F144" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C145" t="s">
+        <v>79</v>
+      </c>
+      <c r="D145">
+        <v>5</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F145" t="s">
         <v>76</v>
       </c>
-      <c r="C145" t="s">
-        <v>76</v>
-      </c>
-      <c r="D145">
-        <v>5</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F145" t="s">
-        <v>73</v>
-      </c>
       <c r="G145" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C146" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D146">
         <v>4</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F146" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C147" t="s">
+        <v>83</v>
+      </c>
+      <c r="D147">
+        <v>5</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F147" t="s">
         <v>80</v>
       </c>
-      <c r="C147" t="s">
-        <v>80</v>
-      </c>
-      <c r="D147">
-        <v>5</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F147" t="s">
-        <v>77</v>
-      </c>
       <c r="G147" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C148" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D148">
         <v>4</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F148" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C149" t="s">
+        <v>87</v>
+      </c>
+      <c r="D149">
+        <v>5</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F149" t="s">
         <v>84</v>
       </c>
-      <c r="C149" t="s">
-        <v>84</v>
-      </c>
-      <c r="D149">
-        <v>5</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F149" t="s">
-        <v>81</v>
-      </c>
       <c r="G149" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C150" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D150">
         <v>4</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F150" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C151" t="s">
+        <v>91</v>
+      </c>
+      <c r="D151">
+        <v>5</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F151" t="s">
         <v>88</v>
       </c>
-      <c r="C151" t="s">
-        <v>88</v>
-      </c>
-      <c r="D151">
-        <v>5</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F151" t="s">
-        <v>85</v>
-      </c>
       <c r="G151" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C152" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D152">
         <v>4</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F152" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C153" t="s">
+        <v>95</v>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F153" t="s">
         <v>92</v>
       </c>
-      <c r="C153" t="s">
-        <v>92</v>
-      </c>
-      <c r="D153">
-        <v>5</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F153" t="s">
-        <v>89</v>
-      </c>
       <c r="G153" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C154" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D154">
         <v>4</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F154" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C155" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F155" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C156" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D156">
         <v>4</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F156" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C157" t="s">
+        <v>104</v>
+      </c>
+      <c r="D157">
+        <v>5</v>
+      </c>
+      <c r="E157" t="s">
+        <v>119</v>
+      </c>
+      <c r="F157" t="s">
         <v>101</v>
       </c>
-      <c r="C157" t="s">
-        <v>101</v>
-      </c>
-      <c r="D157">
-        <v>5</v>
-      </c>
-      <c r="E157" t="s">
-        <v>116</v>
-      </c>
-      <c r="F157" t="s">
-        <v>98</v>
-      </c>
       <c r="G157" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C158" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D158">
         <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F158" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
+        <v>109</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C159" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D159">
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F159" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C160" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D160">
         <v>5</v>
       </c>
       <c r="E160" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F160" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C161" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D161">
         <v>5</v>
       </c>
       <c r="E161" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F161" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C163" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F163" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C164" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D164">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F164" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D165">
         <v>3</v>
       </c>
       <c r="E165" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F165" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D166">
         <v>4</v>
       </c>
       <c r="E166" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F166" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C167" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D167">
         <v>5</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F167" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C168" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D168">
         <v>4</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F168" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C169" t="s">
+        <v>47</v>
+      </c>
+      <c r="D169">
+        <v>5</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F169" t="s">
         <v>44</v>
       </c>
-      <c r="C169" t="s">
-        <v>44</v>
-      </c>
-      <c r="D169">
-        <v>5</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F169" t="s">
-        <v>41</v>
-      </c>
       <c r="G169" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C170" t="s">
+        <v>147</v>
+      </c>
+      <c r="D170">
+        <v>4</v>
+      </c>
+      <c r="E170" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D170">
-        <v>4</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="F170" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C171" t="s">
+        <v>51</v>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F171" t="s">
         <v>48</v>
       </c>
-      <c r="C171" t="s">
-        <v>48</v>
-      </c>
-      <c r="D171">
-        <v>5</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F171" t="s">
-        <v>45</v>
-      </c>
       <c r="G171" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C172" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D172">
         <v>4</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F172" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C173" t="s">
+        <v>55</v>
+      </c>
+      <c r="D173">
+        <v>5</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F173" t="s">
         <v>52</v>
       </c>
-      <c r="C173" t="s">
-        <v>52</v>
-      </c>
-      <c r="D173">
-        <v>5</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F173" t="s">
-        <v>49</v>
-      </c>
       <c r="G173" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C174" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D174">
         <v>4</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F174" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C175" t="s">
+        <v>59</v>
+      </c>
+      <c r="D175">
+        <v>5</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F175" t="s">
         <v>56</v>
       </c>
-      <c r="C175" t="s">
-        <v>56</v>
-      </c>
-      <c r="D175">
-        <v>5</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F175" t="s">
-        <v>53</v>
-      </c>
       <c r="G175" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C176" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D176">
         <v>4</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F176" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C177" t="s">
+        <v>63</v>
+      </c>
+      <c r="D177">
+        <v>5</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F177" t="s">
         <v>60</v>
       </c>
-      <c r="C177" t="s">
-        <v>60</v>
-      </c>
-      <c r="D177">
-        <v>5</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F177" t="s">
-        <v>57</v>
-      </c>
       <c r="G177" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C178" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D178">
         <v>4</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F178" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C179" t="s">
+        <v>67</v>
+      </c>
+      <c r="D179">
+        <v>5</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F179" t="s">
         <v>64</v>
       </c>
-      <c r="C179" t="s">
-        <v>64</v>
-      </c>
-      <c r="D179">
-        <v>5</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F179" t="s">
-        <v>61</v>
-      </c>
       <c r="G179" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C180" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D180">
         <v>4</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F180" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C181" t="s">
+        <v>71</v>
+      </c>
+      <c r="D181">
+        <v>5</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F181" t="s">
         <v>68</v>
       </c>
-      <c r="C181" t="s">
-        <v>68</v>
-      </c>
-      <c r="D181">
-        <v>5</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F181" t="s">
-        <v>65</v>
-      </c>
       <c r="G181" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C182" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D182">
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F182" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C183" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D183">
         <v>3</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F183" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C184" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D184">
         <v>4</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F184" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B185" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185" t="s">
+        <v>79</v>
+      </c>
+      <c r="D185">
+        <v>5</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F185" t="s">
         <v>76</v>
       </c>
-      <c r="C185" t="s">
-        <v>76</v>
-      </c>
-      <c r="D185">
-        <v>5</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F185" t="s">
-        <v>73</v>
-      </c>
       <c r="G185" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C186" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D186">
         <v>4</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F186" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B187" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C187" t="s">
+        <v>83</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F187" t="s">
         <v>80</v>
       </c>
-      <c r="C187" t="s">
-        <v>80</v>
-      </c>
-      <c r="D187">
-        <v>5</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F187" t="s">
-        <v>77</v>
-      </c>
       <c r="G187" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C188" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D188">
         <v>4</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F188" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B189" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C189" t="s">
+        <v>87</v>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F189" t="s">
         <v>84</v>
       </c>
-      <c r="C189" t="s">
-        <v>84</v>
-      </c>
-      <c r="D189">
-        <v>5</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F189" t="s">
-        <v>81</v>
-      </c>
       <c r="G189" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C190" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D190">
         <v>4</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F190" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B191" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C191" t="s">
+        <v>91</v>
+      </c>
+      <c r="D191">
+        <v>5</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F191" t="s">
         <v>88</v>
       </c>
-      <c r="C191" t="s">
-        <v>88</v>
-      </c>
-      <c r="D191">
-        <v>5</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F191" t="s">
-        <v>85</v>
-      </c>
       <c r="G191" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C192" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D192">
         <v>4</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F192" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B193" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C193" t="s">
+        <v>95</v>
+      </c>
+      <c r="D193">
+        <v>5</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F193" t="s">
         <v>92</v>
       </c>
-      <c r="C193" t="s">
-        <v>92</v>
-      </c>
-      <c r="D193">
-        <v>5</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F193" t="s">
-        <v>89</v>
-      </c>
       <c r="G193" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C194" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D194">
         <v>4</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F194" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D195">
         <v>5</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F195" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C196" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D196">
         <v>4</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F196" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C197" t="s">
+        <v>104</v>
+      </c>
+      <c r="D197">
+        <v>5</v>
+      </c>
+      <c r="E197" t="s">
+        <v>145</v>
+      </c>
+      <c r="F197" t="s">
         <v>101</v>
       </c>
-      <c r="C197" t="s">
-        <v>101</v>
-      </c>
-      <c r="D197">
-        <v>5</v>
-      </c>
-      <c r="E197" t="s">
-        <v>142</v>
-      </c>
-      <c r="F197" t="s">
-        <v>98</v>
-      </c>
       <c r="G197" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C198" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D198">
         <v>5</v>
       </c>
       <c r="E198" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F198" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C199" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D199">
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F199" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C200" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D200">
         <v>5</v>
       </c>
       <c r="E200" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F200" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C201" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D201">
         <v>5</v>
       </c>
       <c r="E201" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F201" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>189</v>
+        <v>9</v>
       </c>
       <c r="D202">
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C203" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F203" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C204" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F204" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C205" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D205">
         <v>3</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F205" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C206" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D206">
         <v>4</v>
       </c>
       <c r="E206" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F206" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C207" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D207">
         <v>5</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F207" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C208" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D208">
         <v>4</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F208" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B209" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C209" t="s">
+        <v>47</v>
+      </c>
+      <c r="D209">
+        <v>5</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F209" t="s">
         <v>44</v>
       </c>
-      <c r="C209" t="s">
-        <v>44</v>
-      </c>
-      <c r="D209">
-        <v>5</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F209" t="s">
-        <v>41</v>
-      </c>
       <c r="G209" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C210" t="s">
+        <v>172</v>
+      </c>
+      <c r="D210">
+        <v>4</v>
+      </c>
+      <c r="E210" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D210">
-        <v>4</v>
-      </c>
-      <c r="E210" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="F210" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B211" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C211" t="s">
+        <v>51</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F211" t="s">
         <v>48</v>
       </c>
-      <c r="C211" t="s">
-        <v>48</v>
-      </c>
-      <c r="D211">
-        <v>5</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F211" t="s">
-        <v>45</v>
-      </c>
       <c r="G211" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C212" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D212">
         <v>4</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F212" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B213" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C213" t="s">
+        <v>55</v>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F213" t="s">
         <v>52</v>
       </c>
-      <c r="C213" t="s">
-        <v>52</v>
-      </c>
-      <c r="D213">
-        <v>5</v>
-      </c>
-      <c r="E213" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F213" t="s">
-        <v>49</v>
-      </c>
       <c r="G213" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C214" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D214">
         <v>4</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F214" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C215" t="s">
+        <v>59</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F215" t="s">
         <v>56</v>
       </c>
-      <c r="C215" t="s">
-        <v>56</v>
-      </c>
-      <c r="D215">
-        <v>5</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F215" t="s">
-        <v>53</v>
-      </c>
       <c r="G215" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C216" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D216">
         <v>4</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F216" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B217" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C217" t="s">
+        <v>63</v>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F217" t="s">
         <v>60</v>
       </c>
-      <c r="C217" t="s">
-        <v>60</v>
-      </c>
-      <c r="D217">
-        <v>5</v>
-      </c>
-      <c r="E217" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F217" t="s">
-        <v>57</v>
-      </c>
       <c r="G217" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C218" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D218">
         <v>4</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F218" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C219" t="s">
+        <v>67</v>
+      </c>
+      <c r="D219">
+        <v>5</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F219" t="s">
         <v>64</v>
       </c>
-      <c r="C219" t="s">
-        <v>64</v>
-      </c>
-      <c r="D219">
-        <v>5</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F219" t="s">
-        <v>61</v>
-      </c>
       <c r="G219" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C220" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D220">
         <v>4</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F220" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B221" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C221" t="s">
+        <v>71</v>
+      </c>
+      <c r="D221">
+        <v>5</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F221" t="s">
         <v>68</v>
       </c>
-      <c r="C221" t="s">
-        <v>68</v>
-      </c>
-      <c r="D221">
-        <v>5</v>
-      </c>
-      <c r="E221" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F221" t="s">
-        <v>65</v>
-      </c>
       <c r="G221" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C222" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D222">
         <v>2</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F222" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C223" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D223">
         <v>3</v>
       </c>
       <c r="E223" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F223" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C224" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D224">
         <v>4</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F224" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B225" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C225" t="s">
+        <v>79</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F225" t="s">
         <v>76</v>
       </c>
-      <c r="C225" t="s">
-        <v>76</v>
-      </c>
-      <c r="D225">
-        <v>5</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F225" t="s">
-        <v>73</v>
-      </c>
       <c r="G225" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C226" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D226">
         <v>4</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F226" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B227" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C227" t="s">
+        <v>83</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F227" t="s">
         <v>80</v>
       </c>
-      <c r="C227" t="s">
-        <v>80</v>
-      </c>
-      <c r="D227">
-        <v>5</v>
-      </c>
-      <c r="E227" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F227" t="s">
-        <v>77</v>
-      </c>
       <c r="G227" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C228" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D228">
         <v>4</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F228" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C229" t="s">
+        <v>87</v>
+      </c>
+      <c r="D229">
+        <v>5</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F229" t="s">
         <v>84</v>
       </c>
-      <c r="C229" t="s">
-        <v>84</v>
-      </c>
-      <c r="D229">
-        <v>5</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F229" t="s">
-        <v>81</v>
-      </c>
       <c r="G229" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C230" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D230">
         <v>4</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F230" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B231" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C231" t="s">
+        <v>91</v>
+      </c>
+      <c r="D231">
+        <v>5</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F231" t="s">
         <v>88</v>
       </c>
-      <c r="C231" t="s">
-        <v>88</v>
-      </c>
-      <c r="D231">
-        <v>5</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F231" t="s">
-        <v>85</v>
-      </c>
       <c r="G231" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C232" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D232">
         <v>4</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F232" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B233" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C233" t="s">
+        <v>95</v>
+      </c>
+      <c r="D233">
+        <v>5</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F233" t="s">
         <v>92</v>
       </c>
-      <c r="C233" t="s">
-        <v>92</v>
-      </c>
-      <c r="D233">
-        <v>5</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F233" t="s">
-        <v>89</v>
-      </c>
       <c r="G233" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C234" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D234">
         <v>4</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F234" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C235" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D235">
         <v>5</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F235" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C236" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D236">
         <v>4</v>
       </c>
       <c r="E236" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F236" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B237" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C237" t="s">
+        <v>104</v>
+      </c>
+      <c r="D237">
+        <v>5</v>
+      </c>
+      <c r="E237" t="s">
+        <v>170</v>
+      </c>
+      <c r="F237" t="s">
         <v>101</v>
       </c>
-      <c r="C237" t="s">
-        <v>101</v>
-      </c>
-      <c r="D237">
-        <v>5</v>
-      </c>
-      <c r="E237" t="s">
-        <v>167</v>
-      </c>
-      <c r="F237" t="s">
-        <v>98</v>
-      </c>
       <c r="G237" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C238" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D238">
         <v>5</v>
       </c>
       <c r="E238" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F238" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C239" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D239">
         <v>5</v>
       </c>
       <c r="E239" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F239" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C240" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D240">
         <v>5</v>
       </c>
       <c r="E240" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F240" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C241" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D241">
         <v>5</v>
       </c>
       <c r="E241" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F241" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B242" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C242" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D242">
         <v>4</v>
       </c>
       <c r="E242" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F242" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G242" t="b">
         <v>1</v>
@@ -6628,7 +6635,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B243">
         <v>10114</v>
@@ -6640,10 +6647,10 @@
         <v>5</v>
       </c>
       <c r="E243" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F243" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
@@ -6651,19 +6658,19 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>181</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
+      </c>
+      <c r="B244" t="s">
+        <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D244">
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G244" t="b">
         <v>1</v>
@@ -6671,22 +6678,22 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B245" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C245" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D245">
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F245" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="G245" t="b">
         <v>1</v>
@@ -6694,22 +6701,22 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B246" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D246">
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F246" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G246" t="b">
         <v>1</v>
@@ -6717,22 +6724,22 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B247" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C247" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D247">
         <v>3</v>
       </c>
       <c r="E247" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F247" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G247" t="b">
         <v>1</v>
@@ -6740,22 +6747,22 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B248" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C248" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D248">
         <v>4</v>
       </c>
       <c r="E248" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F248" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
@@ -6763,7 +6770,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B249">
         <v>14022</v>
@@ -6775,10 +6782,10 @@
         <v>5</v>
       </c>
       <c r="E249" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F249" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G249" t="b">
         <v>1</v>
@@ -6786,22 +6793,22 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B250" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C250" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D250">
         <v>4</v>
       </c>
       <c r="E250" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F250" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
@@ -6809,7 +6816,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B251">
         <v>14053</v>
@@ -6821,10 +6828,10 @@
         <v>5</v>
       </c>
       <c r="E251" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F251" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
@@ -6832,22 +6839,22 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B252" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C252" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D252">
         <v>4</v>
       </c>
       <c r="E252" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F252" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
@@ -6855,7 +6862,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B253">
         <v>14023</v>
@@ -6867,10 +6874,10 @@
         <v>5</v>
       </c>
       <c r="E253" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F253" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
@@ -6878,22 +6885,22 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B254" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C254" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D254">
         <v>4</v>
       </c>
       <c r="E254" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F254" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G254" t="b">
         <v>1</v>
@@ -6901,7 +6908,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B255">
         <v>14000</v>
@@ -6913,10 +6920,10 @@
         <v>5</v>
       </c>
       <c r="E255" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F255" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
@@ -6924,22 +6931,22 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B256" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C256" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D256">
         <v>4</v>
       </c>
       <c r="E256" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F256" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G256" t="b">
         <v>1</v>
@@ -6947,7 +6954,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B257">
         <v>14110</v>
@@ -6959,10 +6966,10 @@
         <v>5</v>
       </c>
       <c r="E257" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F257" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G257" t="b">
         <v>1</v>
@@ -6970,22 +6977,22 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B258" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C258" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D258">
         <v>4</v>
       </c>
       <c r="E258" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F258" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G258" t="b">
         <v>1</v>
@@ -6993,7 +7000,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B259">
         <v>14080</v>
@@ -7005,10 +7012,10 @@
         <v>5</v>
       </c>
       <c r="E259" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F259" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
@@ -7016,22 +7023,22 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B260" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C260" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D260">
         <v>4</v>
       </c>
       <c r="E260" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F260" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
@@ -7039,7 +7046,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B261">
         <v>14025</v>
@@ -7051,10 +7058,10 @@
         <v>5</v>
       </c>
       <c r="E261" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F261" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
@@ -7062,22 +7069,22 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B262" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C262" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D262">
         <v>4</v>
       </c>
       <c r="E262" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F262" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
@@ -7085,7 +7092,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B263">
         <v>14050</v>
@@ -7097,10 +7104,10 @@
         <v>5</v>
       </c>
       <c r="E263" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F263" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
@@ -7108,22 +7115,22 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B264" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C264" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D264">
         <v>2</v>
       </c>
       <c r="E264" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F264" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G264" t="b">
         <v>1</v>
@@ -7131,22 +7138,22 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B265" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C265" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D265">
         <v>3</v>
       </c>
       <c r="E265" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F265" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
@@ -7154,22 +7161,22 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B266" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C266" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D266">
         <v>4</v>
       </c>
       <c r="E266" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F266" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
@@ -7177,7 +7184,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B267">
         <v>10106</v>
@@ -7189,10 +7196,10 @@
         <v>5</v>
       </c>
       <c r="E267" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F267" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
@@ -7200,22 +7207,22 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B268" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C268" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D268">
         <v>4</v>
       </c>
       <c r="E268" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F268" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
@@ -7223,7 +7230,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B269">
         <v>10000</v>
@@ -7235,10 +7242,10 @@
         <v>5</v>
       </c>
       <c r="E269" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F269" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
@@ -7246,22 +7253,22 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B270" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C270" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D270">
         <v>4</v>
       </c>
       <c r="E270" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F270" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G270" t="b">
         <v>1</v>
@@ -7269,7 +7276,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B271">
         <v>10105</v>
@@ -7281,10 +7288,10 @@
         <v>5</v>
       </c>
       <c r="E271" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F271" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
@@ -7292,7 +7299,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B272">
         <v>10112</v>
@@ -7304,10 +7311,10 @@
         <v>5</v>
       </c>
       <c r="E272" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F272" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G272" t="b">
         <v>1</v>
@@ -7315,22 +7322,22 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B273" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C273" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D273">
         <v>4</v>
       </c>
       <c r="E273" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F273" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
@@ -7338,7 +7345,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B274">
         <v>10104</v>
@@ -7350,10 +7357,10 @@
         <v>5</v>
       </c>
       <c r="E274" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F274" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
@@ -7361,22 +7368,22 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B275" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C275" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D275">
         <v>4</v>
       </c>
       <c r="E275" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F275" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
@@ -7384,7 +7391,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B276">
         <v>10036</v>
@@ -7396,10 +7403,10 @@
         <v>5</v>
       </c>
       <c r="E276" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F276" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
@@ -7407,22 +7414,22 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B277" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C277" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D277">
         <v>4</v>
       </c>
       <c r="E277" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F277" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
@@ -7430,7 +7437,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B278">
         <v>10190</v>
@@ -7442,10 +7449,10 @@
         <v>5</v>
       </c>
       <c r="E278" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F278" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
@@ -7453,7 +7460,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B279">
         <v>10110</v>
@@ -7465,10 +7472,10 @@
         <v>5</v>
       </c>
       <c r="E279" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F279" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
@@ -7476,7 +7483,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B280">
         <v>10111</v>
@@ -7488,10 +7495,10 @@
         <v>5</v>
       </c>
       <c r="E280" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F280" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G280" t="b">
         <v>1</v>
@@ -7499,7 +7506,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B281">
         <v>10113</v>
@@ -7511,17 +7518,23 @@
         <v>5</v>
       </c>
       <c r="E281" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F281" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G281" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G121" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A9544-3E11-4EA9-B23C-23EBA65A32C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76134161-A38A-4236-A2A3-FA291C89C9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="193">
   <si>
     <t>lang_code</t>
   </si>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Barnaby</t>
   </si>
 </sst>
 </file>
@@ -776,9 +779,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -816,7 +819,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -922,7 +925,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,7 +1067,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1074,15 +1077,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G281"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.46484375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="21.7265625" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" customWidth="1"/>
+    <col min="2" max="2" width="15.73046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" customWidth="1"/>
+    <col min="4" max="4" width="21.73046875" customWidth="1"/>
+    <col min="5" max="5" width="23.46484375" customWidth="1"/>
+    <col min="6" max="6" width="19.53125" customWidth="1"/>
+    <col min="7" max="7" width="19.265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1176,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1467,7 +1470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.5">
+    <row r="18" spans="1:7" ht="22.15">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="22.5">
+    <row r="24" spans="1:7" ht="22.15">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22.5">
+    <row r="30" spans="1:7" ht="22.15">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1881,7 +1884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="22.5">
+    <row r="36" spans="1:7" ht="22.15">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2019,7 +2022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="22.5">
+    <row r="42" spans="1:7" ht="22.15">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="22.5">
+    <row r="48" spans="1:7" ht="22.15">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -2295,7 +2298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="22.5">
+    <row r="54" spans="1:7" ht="22.15">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -2433,7 +2436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="22.5">
+    <row r="60" spans="1:7" ht="22.15">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2709,7 +2712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.5">
+    <row r="72" spans="1:7" ht="22.15">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -2847,7 +2850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="22.5">
+    <row r="78" spans="1:7" ht="22.15">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -2985,7 +2988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="22.5">
+    <row r="84" spans="1:7" ht="22.15">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -3123,7 +3126,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="22.5">
+    <row r="90" spans="1:7" ht="22.15">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="22.5">
+    <row r="96" spans="1:7" ht="22.15">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -3399,7 +3402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="22.5">
+    <row r="102" spans="1:7" ht="22.15">
       <c r="A102" t="s">
         <v>12</v>
       </c>
@@ -3537,7 +3540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="22.5">
+    <row r="108" spans="1:7" ht="22.15">
       <c r="A108" t="s">
         <v>12</v>
       </c>
@@ -3767,7 +3770,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="22.5">
+    <row r="118" spans="1:7" ht="22.15">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="22.5">
+    <row r="119" spans="1:7" ht="22.15">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="22.5">
+    <row r="120" spans="1:7" ht="22.15">
       <c r="A120" t="s">
         <v>12</v>
       </c>
@@ -3836,7 +3839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="22.5">
+    <row r="121" spans="1:7" ht="22.15">
       <c r="A121" t="s">
         <v>12</v>
       </c>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76134161-A38A-4236-A2A3-FA291C89C9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90093D57-11D5-4FD8-813E-FBF079BA9210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$281</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="192">
   <si>
     <t>lang_code</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>RSK</t>
-  </si>
-  <si>
-    <t>Rabat Sale Kenitra</t>
   </si>
   <si>
     <t>Region</t>
@@ -1111,7 +1108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1131,7 +1128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1151,7 +1148,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1179,13 +1176,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -1202,13 +1199,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1225,13 +1222,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1240,21 +1237,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -1263,21 +1260,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -1286,21 +1283,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -1309,173 +1306,173 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>36</v>
       </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" t="s">
-        <v>39</v>
-      </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>36</v>
       </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.15">
+    <row r="18" spans="1:7" ht="22.15" hidden="1">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>14022</v>
@@ -1484,136 +1481,136 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
         <v>44</v>
       </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="22.15">
+    <row r="24" spans="1:7" ht="22.15" hidden="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>14053</v>
@@ -1622,136 +1619,136 @@
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" t="s">
         <v>43</v>
       </c>
-      <c r="F25" t="s">
-        <v>44</v>
-      </c>
       <c r="G25" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
         <v>48</v>
       </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22.15">
+    <row r="30" spans="1:7" ht="22.15" hidden="1">
       <c r="A30" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>14023</v>
@@ -1760,136 +1757,136 @@
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
-        <v>53</v>
-      </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" t="s">
-        <v>53</v>
-      </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="22.15">
+    <row r="36" spans="1:7" ht="22.15" hidden="1">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>14000</v>
@@ -1898,136 +1895,136 @@
         <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
         <v>56</v>
       </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
         <v>56</v>
       </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="22.15">
+    <row r="42" spans="1:7" ht="22.15" hidden="1">
       <c r="A42" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>14110</v>
@@ -2036,136 +2033,136 @@
         <v>5</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="s">
         <v>60</v>
       </c>
-      <c r="C44" t="s">
-        <v>61</v>
-      </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
         <v>60</v>
       </c>
-      <c r="C46" t="s">
-        <v>61</v>
-      </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>7</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D47">
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="22.15">
+    <row r="48" spans="1:7" ht="22.15" hidden="1">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48">
         <v>14080</v>
@@ -2174,136 +2171,136 @@
         <v>5</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49">
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
         <v>64</v>
       </c>
-      <c r="C50" t="s">
-        <v>65</v>
-      </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" t="s">
         <v>64</v>
       </c>
-      <c r="C52" t="s">
-        <v>65</v>
-      </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>7</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D53">
         <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="22.15">
+    <row r="54" spans="1:7" ht="22.15" hidden="1">
       <c r="A54" t="s">
         <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54">
         <v>14025</v>
@@ -2312,136 +2309,136 @@
         <v>5</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D55">
         <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
         <v>68</v>
       </c>
-      <c r="C56" t="s">
-        <v>69</v>
-      </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>12</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
         <v>68</v>
       </c>
-      <c r="C58" t="s">
-        <v>69</v>
-      </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59">
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="22.15">
+    <row r="60" spans="1:7" ht="22.15" hidden="1">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>14050</v>
@@ -2450,53 +2447,53 @@
         <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>7</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" t="s">
         <v>72</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F62" t="s">
         <v>18</v>
@@ -2505,21 +2502,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -2528,21 +2525,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
         <v>72</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -2551,173 +2548,173 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" hidden="1">
       <c r="A65" t="s">
         <v>7</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>7</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
         <v>76</v>
       </c>
-      <c r="C68" t="s">
-        <v>77</v>
-      </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>12</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" t="s">
         <v>76</v>
       </c>
-      <c r="C70" t="s">
-        <v>77</v>
-      </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>7</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71">
         <v>5</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.15">
+    <row r="72" spans="1:7" ht="22.15" hidden="1">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C72">
         <v>10106</v>
@@ -2726,136 +2723,136 @@
         <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D73">
         <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
         <v>80</v>
       </c>
-      <c r="C74" t="s">
-        <v>81</v>
-      </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>12</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
         <v>80</v>
       </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
       <c r="D76">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D77">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="22.15">
+    <row r="78" spans="1:7" ht="22.15" hidden="1">
       <c r="A78" t="s">
         <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78">
         <v>10000</v>
@@ -2864,136 +2861,136 @@
         <v>5</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D79">
         <v>5</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" hidden="1">
       <c r="A80" t="s">
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" t="s">
         <v>84</v>
       </c>
-      <c r="C80" t="s">
-        <v>85</v>
-      </c>
       <c r="D80">
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>12</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
         <v>84</v>
       </c>
-      <c r="C82" t="s">
-        <v>85</v>
-      </c>
       <c r="D82">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="22.15">
+    <row r="84" spans="1:7" ht="22.15" hidden="1">
       <c r="A84" t="s">
         <v>12</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84">
         <v>10105</v>
@@ -3002,136 +2999,136 @@
         <v>5</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D85">
         <v>5</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>7</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" t="s">
         <v>88</v>
       </c>
-      <c r="C86" t="s">
-        <v>89</v>
-      </c>
       <c r="D86">
         <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>12</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" t="s">
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
         <v>88</v>
       </c>
-      <c r="C88" t="s">
-        <v>89</v>
-      </c>
       <c r="D88">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F88" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>7</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D89">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="22.15">
+    <row r="90" spans="1:7" ht="22.15" hidden="1">
       <c r="A90" t="s">
         <v>12</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90">
         <v>10112</v>
@@ -3140,136 +3137,136 @@
         <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D91">
         <v>5</v>
       </c>
       <c r="E91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>7</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" t="s">
         <v>92</v>
       </c>
-      <c r="C92" t="s">
-        <v>93</v>
-      </c>
       <c r="D92">
         <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C94" t="s">
         <v>92</v>
       </c>
-      <c r="C94" t="s">
-        <v>93</v>
-      </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>7</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D95">
         <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="22.15">
+    <row r="96" spans="1:7" ht="22.15" hidden="1">
       <c r="A96" t="s">
         <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C96">
         <v>10104</v>
@@ -3278,136 +3275,136 @@
         <v>5</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F96" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F97" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
         <v>7</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" t="s">
         <v>96</v>
       </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
       <c r="D98">
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
         <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
         <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100">
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
         <v>7</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D101">
         <v>5</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="22.15">
+    <row r="102" spans="1:7" ht="22.15" hidden="1">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C102">
         <v>10036</v>
@@ -3416,136 +3413,136 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" hidden="1">
       <c r="A103" t="s">
         <v>15</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" hidden="1">
       <c r="A104" t="s">
         <v>7</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104" t="s">
         <v>101</v>
       </c>
-      <c r="C104" t="s">
-        <v>102</v>
-      </c>
       <c r="D104">
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" hidden="1">
       <c r="A105" t="s">
         <v>12</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" hidden="1">
       <c r="A106" t="s">
         <v>15</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
         <v>101</v>
       </c>
-      <c r="C106" t="s">
-        <v>102</v>
-      </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F106" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" hidden="1">
       <c r="A107" t="s">
         <v>7</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D107">
         <v>5</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="22.15">
+    <row r="108" spans="1:7" ht="22.15" hidden="1">
       <c r="A108" t="s">
         <v>12</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108">
         <v>10190</v>
@@ -3554,205 +3551,205 @@
         <v>5</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" hidden="1">
       <c r="A109" t="s">
         <v>15</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D109">
         <v>5</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" hidden="1">
       <c r="A110" t="s">
         <v>7</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" hidden="1">
       <c r="A111" t="s">
         <v>7</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D111">
         <v>5</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" hidden="1">
       <c r="A112" t="s">
         <v>7</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D112">
         <v>5</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" hidden="1">
       <c r="A113" t="s">
         <v>7</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D113">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" t="s">
         <v>15</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" hidden="1">
       <c r="A115" t="s">
         <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D115">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" t="s">
         <v>15</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D116">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" t="s">
         <v>15</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C117">
         <v>10114</v>
@@ -3761,21 +3758,21 @@
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="22.15">
+    <row r="118" spans="1:7" ht="22.15" hidden="1">
       <c r="A118" t="s">
         <v>12</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C118">
         <v>10111</v>
@@ -3784,21 +3781,21 @@
         <v>5</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="22.15">
+    <row r="119" spans="1:7" ht="22.15" hidden="1">
       <c r="A119" t="s">
         <v>12</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C119">
         <v>10114</v>
@@ -3807,21 +3804,21 @@
         <v>5</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="22.15">
+    <row r="120" spans="1:7" ht="22.15" hidden="1">
       <c r="A120" t="s">
         <v>12</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C120">
         <v>10113</v>
@@ -3830,21 +3827,21 @@
         <v>5</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="22.15">
+    <row r="121" spans="1:7" ht="22.15" hidden="1">
       <c r="A121" t="s">
         <v>12</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C121">
         <v>10110</v>
@@ -3853,30 +3850,30 @@
         <v>5</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>11</v>
@@ -3884,19 +3881,19 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -3905,21 +3902,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D124">
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F124" t="s">
         <v>18</v>
@@ -3928,412 +3925,412 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D125">
         <v>3</v>
       </c>
       <c r="E125" t="s">
+        <v>115</v>
+      </c>
+      <c r="F125" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1">
+      <c r="A126" t="s">
+        <v>108</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" t="s">
         <v>116</v>
       </c>
-      <c r="F125" t="s">
-        <v>25</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
-        <v>109</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="D126">
+        <v>4</v>
+      </c>
+      <c r="E126" t="s">
         <v>117</v>
       </c>
-      <c r="D126">
-        <v>4</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
+        <v>30</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1">
+      <c r="A127" t="s">
+        <v>108</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C127" t="s">
+        <v>39</v>
+      </c>
+      <c r="D127">
+        <v>5</v>
+      </c>
+      <c r="E127" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F126" t="s">
-        <v>31</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" t="s">
-        <v>109</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C127" t="s">
-        <v>40</v>
-      </c>
-      <c r="D127">
-        <v>5</v>
-      </c>
-      <c r="E127" s="5" t="s">
+      <c r="F127" t="s">
+        <v>34</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1">
+      <c r="A128" t="s">
+        <v>108</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C128" t="s">
         <v>119</v>
       </c>
-      <c r="F127" t="s">
-        <v>35</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" t="s">
-        <v>109</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="D128">
+        <v>4</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F128" t="s">
+        <v>30</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1">
+      <c r="A129" t="s">
+        <v>108</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C129" t="s">
+        <v>46</v>
+      </c>
+      <c r="D129">
+        <v>5</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F129" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1">
+      <c r="A130" t="s">
+        <v>108</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C130" t="s">
         <v>120</v>
       </c>
-      <c r="D128">
-        <v>4</v>
-      </c>
-      <c r="E128" s="5" t="s">
+      <c r="D130">
+        <v>4</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F130" t="s">
+        <v>30</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1">
+      <c r="A131" t="s">
+        <v>108</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C131" t="s">
+        <v>50</v>
+      </c>
+      <c r="D131">
+        <v>5</v>
+      </c>
+      <c r="E131" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F128" t="s">
-        <v>31</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
-        <v>109</v>
-      </c>
-      <c r="B129" s="1" t="s">
+      <c r="F131" t="s">
         <v>47</v>
       </c>
-      <c r="C129" t="s">
-        <v>47</v>
-      </c>
-      <c r="D129">
-        <v>5</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F129" t="s">
-        <v>44</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
-        <v>109</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="G131" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1">
+      <c r="A132" t="s">
+        <v>108</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C132" t="s">
         <v>121</v>
       </c>
-      <c r="D130">
-        <v>4</v>
-      </c>
-      <c r="E130" s="5" t="s">
+      <c r="D132">
+        <v>4</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F132" t="s">
+        <v>30</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1">
+      <c r="A133" t="s">
+        <v>108</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C133" t="s">
+        <v>54</v>
+      </c>
+      <c r="D133">
+        <v>5</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F130" t="s">
-        <v>31</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
-        <v>109</v>
-      </c>
-      <c r="B131" s="1" t="s">
+      <c r="F133" t="s">
         <v>51</v>
       </c>
-      <c r="C131" t="s">
-        <v>51</v>
-      </c>
-      <c r="D131">
-        <v>5</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F131" t="s">
-        <v>48</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
-        <v>109</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="G133" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1">
+      <c r="A134" t="s">
+        <v>108</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" t="s">
         <v>122</v>
       </c>
-      <c r="D132">
-        <v>4</v>
-      </c>
-      <c r="E132" s="5" t="s">
+      <c r="D134">
+        <v>4</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F134" t="s">
+        <v>30</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1">
+      <c r="A135" t="s">
+        <v>108</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D135">
+        <v>5</v>
+      </c>
+      <c r="E135" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F132" t="s">
-        <v>31</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
-        <v>109</v>
-      </c>
-      <c r="B133" s="1" t="s">
+      <c r="F135" t="s">
         <v>55</v>
       </c>
-      <c r="C133" t="s">
-        <v>55</v>
-      </c>
-      <c r="D133">
-        <v>5</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F133" t="s">
-        <v>52</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
-        <v>109</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="G135" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1">
+      <c r="A136" t="s">
+        <v>108</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" t="s">
         <v>123</v>
       </c>
-      <c r="D134">
-        <v>4</v>
-      </c>
-      <c r="E134" s="5" t="s">
+      <c r="D136">
+        <v>4</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F136" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1">
+      <c r="A137" t="s">
+        <v>108</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C137" t="s">
+        <v>62</v>
+      </c>
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F134" t="s">
-        <v>31</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
-        <v>109</v>
-      </c>
-      <c r="B135" s="1" t="s">
+      <c r="F137" t="s">
         <v>59</v>
       </c>
-      <c r="C135" t="s">
-        <v>59</v>
-      </c>
-      <c r="D135">
-        <v>5</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F135" t="s">
-        <v>56</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
-        <v>109</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="G137" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1">
+      <c r="A138" t="s">
+        <v>108</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C138" t="s">
         <v>124</v>
       </c>
-      <c r="D136">
-        <v>4</v>
-      </c>
-      <c r="E136" s="5" t="s">
+      <c r="D138">
+        <v>4</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F138" t="s">
+        <v>30</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1">
+      <c r="A139" t="s">
+        <v>108</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C139" t="s">
+        <v>66</v>
+      </c>
+      <c r="D139">
+        <v>5</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F136" t="s">
-        <v>31</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
-        <v>109</v>
-      </c>
-      <c r="B137" s="1" t="s">
+      <c r="F139" t="s">
         <v>63</v>
       </c>
-      <c r="C137" t="s">
-        <v>63</v>
-      </c>
-      <c r="D137">
-        <v>5</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F137" t="s">
-        <v>60</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" t="s">
-        <v>109</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="G139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1">
+      <c r="A140" t="s">
+        <v>108</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C140" t="s">
         <v>125</v>
       </c>
-      <c r="D138">
-        <v>4</v>
-      </c>
-      <c r="E138" s="5" t="s">
+      <c r="D140">
+        <v>4</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F140" t="s">
+        <v>30</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1">
+      <c r="A141" t="s">
+        <v>108</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C141" t="s">
+        <v>70</v>
+      </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
+      <c r="E141" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F138" t="s">
-        <v>31</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
-        <v>109</v>
-      </c>
-      <c r="B139" s="1" t="s">
+      <c r="F141" t="s">
         <v>67</v>
       </c>
-      <c r="C139" t="s">
-        <v>67</v>
-      </c>
-      <c r="D139">
-        <v>5</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F139" t="s">
-        <v>64</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
-        <v>109</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="G141" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1">
+      <c r="A142" t="s">
+        <v>108</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C142" t="s">
         <v>126</v>
-      </c>
-      <c r="D140">
-        <v>4</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F140" t="s">
-        <v>31</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
-        <v>109</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C141" t="s">
-        <v>71</v>
-      </c>
-      <c r="D141">
-        <v>5</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F141" t="s">
-        <v>68</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
-        <v>109</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C142" t="s">
-        <v>127</v>
       </c>
       <c r="D142">
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F142" t="s">
         <v>18</v>
@@ -4342,458 +4339,458 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" hidden="1">
       <c r="A143" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C143" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D143">
         <v>3</v>
       </c>
       <c r="E143" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" hidden="1">
       <c r="A144" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
+        <v>127</v>
+      </c>
+      <c r="D144">
+        <v>4</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F144" t="s">
+        <v>74</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1">
+      <c r="A145" t="s">
+        <v>108</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145" t="s">
+        <v>78</v>
+      </c>
+      <c r="D145">
+        <v>5</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1">
+      <c r="A146" t="s">
+        <v>108</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C146" t="s">
         <v>128</v>
       </c>
-      <c r="D144">
-        <v>4</v>
-      </c>
-      <c r="E144" s="5" t="s">
+      <c r="D146">
+        <v>4</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F146" t="s">
+        <v>74</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1">
+      <c r="A147" t="s">
+        <v>108</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" t="s">
+        <v>82</v>
+      </c>
+      <c r="D147">
+        <v>5</v>
+      </c>
+      <c r="E147" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F144" t="s">
-        <v>75</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
-        <v>109</v>
-      </c>
-      <c r="B145" s="1" t="s">
+      <c r="F147" t="s">
         <v>79</v>
       </c>
-      <c r="C145" t="s">
-        <v>79</v>
-      </c>
-      <c r="D145">
-        <v>5</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F145" t="s">
-        <v>76</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>109</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="G147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1">
+      <c r="A148" t="s">
+        <v>108</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
         <v>129</v>
       </c>
-      <c r="D146">
-        <v>4</v>
-      </c>
-      <c r="E146" s="5" t="s">
+      <c r="D148">
+        <v>4</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F148" t="s">
+        <v>74</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1">
+      <c r="A149" t="s">
+        <v>108</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C149" t="s">
+        <v>86</v>
+      </c>
+      <c r="D149">
+        <v>5</v>
+      </c>
+      <c r="E149" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F146" t="s">
-        <v>75</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" t="s">
-        <v>109</v>
-      </c>
-      <c r="B147" s="1" t="s">
+      <c r="F149" t="s">
         <v>83</v>
       </c>
-      <c r="C147" t="s">
-        <v>83</v>
-      </c>
-      <c r="D147">
-        <v>5</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F147" t="s">
-        <v>80</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" t="s">
-        <v>109</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="G149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1">
+      <c r="A150" t="s">
+        <v>108</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C150" t="s">
         <v>130</v>
       </c>
-      <c r="D148">
-        <v>4</v>
-      </c>
-      <c r="E148" s="5" t="s">
+      <c r="D150">
+        <v>4</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F150" t="s">
+        <v>74</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1">
+      <c r="A151" t="s">
+        <v>108</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C151" t="s">
+        <v>90</v>
+      </c>
+      <c r="D151">
+        <v>5</v>
+      </c>
+      <c r="E151" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F148" t="s">
-        <v>75</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" t="s">
-        <v>109</v>
-      </c>
-      <c r="B149" s="1" t="s">
+      <c r="F151" t="s">
         <v>87</v>
       </c>
-      <c r="C149" t="s">
-        <v>87</v>
-      </c>
-      <c r="D149">
-        <v>5</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F149" t="s">
-        <v>84</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" t="s">
-        <v>109</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="G151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1">
+      <c r="A152" t="s">
+        <v>108</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C152" t="s">
         <v>131</v>
       </c>
-      <c r="D150">
-        <v>4</v>
-      </c>
-      <c r="E150" s="5" t="s">
+      <c r="D152">
+        <v>4</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F152" t="s">
+        <v>74</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1">
+      <c r="A153" t="s">
+        <v>108</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C153" t="s">
+        <v>94</v>
+      </c>
+      <c r="D153">
+        <v>5</v>
+      </c>
+      <c r="E153" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F150" t="s">
-        <v>75</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" t="s">
-        <v>109</v>
-      </c>
-      <c r="B151" s="1" t="s">
+      <c r="F153" t="s">
         <v>91</v>
       </c>
-      <c r="C151" t="s">
-        <v>91</v>
-      </c>
-      <c r="D151">
-        <v>5</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F151" t="s">
-        <v>88</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>109</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="G153" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1">
+      <c r="A154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C154" t="s">
         <v>132</v>
       </c>
-      <c r="D152">
-        <v>4</v>
-      </c>
-      <c r="E152" s="5" t="s">
+      <c r="D154">
+        <v>4</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F154" t="s">
+        <v>74</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1">
+      <c r="A155" t="s">
+        <v>108</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C155" t="s">
+        <v>99</v>
+      </c>
+      <c r="D155">
+        <v>5</v>
+      </c>
+      <c r="E155" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F152" t="s">
-        <v>75</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
-        <v>109</v>
-      </c>
-      <c r="B153" s="1" t="s">
+      <c r="F155" t="s">
         <v>95</v>
       </c>
-      <c r="C153" t="s">
-        <v>95</v>
-      </c>
-      <c r="D153">
-        <v>5</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F153" t="s">
-        <v>92</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="G155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1">
+      <c r="A156" t="s">
+        <v>108</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C156" t="s">
         <v>133</v>
       </c>
-      <c r="D154">
-        <v>4</v>
-      </c>
-      <c r="E154" s="5" t="s">
+      <c r="D156">
+        <v>4</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F156" t="s">
+        <v>74</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1">
+      <c r="A157" t="s">
+        <v>108</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C157" t="s">
+        <v>103</v>
+      </c>
+      <c r="D157">
+        <v>5</v>
+      </c>
+      <c r="E157" t="s">
         <v>118</v>
       </c>
-      <c r="F154" t="s">
-        <v>75</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
-        <v>109</v>
-      </c>
-      <c r="B155" s="1" t="s">
+      <c r="F157" t="s">
         <v>100</v>
       </c>
-      <c r="C155" t="s">
-        <v>100</v>
-      </c>
-      <c r="D155">
-        <v>5</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F155" t="s">
-        <v>96</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" t="s">
-        <v>109</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="G157" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1">
+      <c r="A158" t="s">
+        <v>108</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C158" t="s">
+        <v>104</v>
+      </c>
+      <c r="D158">
+        <v>5</v>
+      </c>
+      <c r="E158" t="s">
+        <v>118</v>
+      </c>
+      <c r="F158" t="s">
+        <v>34</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" hidden="1">
+      <c r="A159" t="s">
+        <v>108</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C159" t="s">
+        <v>105</v>
+      </c>
+      <c r="D159">
+        <v>5</v>
+      </c>
+      <c r="E159" t="s">
+        <v>118</v>
+      </c>
+      <c r="F159" t="s">
+        <v>34</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" hidden="1">
+      <c r="A160" t="s">
+        <v>108</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C160" t="s">
+        <v>106</v>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+      <c r="E160" t="s">
+        <v>118</v>
+      </c>
+      <c r="F160" t="s">
+        <v>34</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" hidden="1">
+      <c r="A161" t="s">
+        <v>108</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" t="s">
+        <v>107</v>
+      </c>
+      <c r="D161">
+        <v>5</v>
+      </c>
+      <c r="E161" t="s">
+        <v>118</v>
+      </c>
+      <c r="F161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1">
+      <c r="A162" t="s">
         <v>134</v>
-      </c>
-      <c r="D156">
-        <v>4</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F156" t="s">
-        <v>75</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" t="s">
-        <v>109</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C157" t="s">
-        <v>104</v>
-      </c>
-      <c r="D157">
-        <v>5</v>
-      </c>
-      <c r="E157" t="s">
-        <v>119</v>
-      </c>
-      <c r="F157" t="s">
-        <v>101</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" t="s">
-        <v>109</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C158" t="s">
-        <v>105</v>
-      </c>
-      <c r="D158">
-        <v>5</v>
-      </c>
-      <c r="E158" t="s">
-        <v>119</v>
-      </c>
-      <c r="F158" t="s">
-        <v>35</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
-        <v>109</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C159" t="s">
-        <v>106</v>
-      </c>
-      <c r="D159">
-        <v>5</v>
-      </c>
-      <c r="E159" t="s">
-        <v>119</v>
-      </c>
-      <c r="F159" t="s">
-        <v>35</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" t="s">
-        <v>109</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C160" t="s">
-        <v>107</v>
-      </c>
-      <c r="D160">
-        <v>5</v>
-      </c>
-      <c r="E160" t="s">
-        <v>119</v>
-      </c>
-      <c r="F160" t="s">
-        <v>35</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
-        <v>109</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C161" t="s">
-        <v>108</v>
-      </c>
-      <c r="D161">
-        <v>5</v>
-      </c>
-      <c r="E161" t="s">
-        <v>119</v>
-      </c>
-      <c r="F161" t="s">
-        <v>35</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>135</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>11</v>
@@ -4801,19 +4798,19 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C163" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F163" t="s">
         <v>8</v>
@@ -4822,21 +4819,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" hidden="1">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D164">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F164" t="s">
         <v>18</v>
@@ -4845,412 +4842,412 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" hidden="1">
       <c r="A165" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D165">
         <v>3</v>
       </c>
       <c r="E165" t="s">
+        <v>141</v>
+      </c>
+      <c r="F165" t="s">
+        <v>24</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1">
+      <c r="A166" t="s">
+        <v>134</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C166" t="s">
         <v>142</v>
       </c>
-      <c r="F165" t="s">
-        <v>25</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>135</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="D166">
+        <v>4</v>
+      </c>
+      <c r="E166" t="s">
         <v>143</v>
       </c>
-      <c r="D166">
-        <v>4</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
+        <v>30</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" hidden="1">
+      <c r="A167" t="s">
+        <v>134</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D167">
+        <v>5</v>
+      </c>
+      <c r="E167" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F166" t="s">
-        <v>31</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
-        <v>135</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C167" t="s">
-        <v>40</v>
-      </c>
-      <c r="D167">
-        <v>5</v>
-      </c>
-      <c r="E167" s="5" t="s">
+      <c r="F167" t="s">
+        <v>34</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" hidden="1">
+      <c r="A168" t="s">
+        <v>134</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C168" t="s">
         <v>145</v>
       </c>
-      <c r="F167" t="s">
-        <v>35</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>135</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="D168">
+        <v>4</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F168" t="s">
+        <v>30</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" hidden="1">
+      <c r="A169" t="s">
+        <v>134</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C169" t="s">
+        <v>46</v>
+      </c>
+      <c r="D169">
+        <v>5</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F169" t="s">
+        <v>43</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" hidden="1">
+      <c r="A170" t="s">
+        <v>134</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C170" t="s">
         <v>146</v>
       </c>
-      <c r="D168">
-        <v>4</v>
-      </c>
-      <c r="E168" s="5" t="s">
+      <c r="D170">
+        <v>4</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F170" t="s">
+        <v>30</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" hidden="1">
+      <c r="A171" t="s">
+        <v>134</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C171" t="s">
+        <v>50</v>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F168" t="s">
-        <v>31</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>135</v>
-      </c>
-      <c r="B169" s="1" t="s">
+      <c r="F171" t="s">
         <v>47</v>
       </c>
-      <c r="C169" t="s">
-        <v>47</v>
-      </c>
-      <c r="D169">
-        <v>5</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F169" t="s">
-        <v>44</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>135</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="G171" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" hidden="1">
+      <c r="A172" t="s">
+        <v>134</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C172" t="s">
         <v>147</v>
       </c>
-      <c r="D170">
-        <v>4</v>
-      </c>
-      <c r="E170" s="5" t="s">
+      <c r="D172">
+        <v>4</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F172" t="s">
+        <v>30</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" hidden="1">
+      <c r="A173" t="s">
+        <v>134</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C173" t="s">
+        <v>54</v>
+      </c>
+      <c r="D173">
+        <v>5</v>
+      </c>
+      <c r="E173" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F170" t="s">
-        <v>31</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
-        <v>135</v>
-      </c>
-      <c r="B171" s="1" t="s">
+      <c r="F173" t="s">
         <v>51</v>
       </c>
-      <c r="C171" t="s">
-        <v>51</v>
-      </c>
-      <c r="D171">
-        <v>5</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F171" t="s">
-        <v>48</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
-        <v>135</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="G173" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" hidden="1">
+      <c r="A174" t="s">
+        <v>134</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C174" t="s">
         <v>148</v>
       </c>
-      <c r="D172">
-        <v>4</v>
-      </c>
-      <c r="E172" s="5" t="s">
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F174" t="s">
+        <v>30</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" hidden="1">
+      <c r="A175" t="s">
+        <v>134</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C175" t="s">
+        <v>58</v>
+      </c>
+      <c r="D175">
+        <v>5</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F172" t="s">
-        <v>31</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
-        <v>135</v>
-      </c>
-      <c r="B173" s="1" t="s">
+      <c r="F175" t="s">
         <v>55</v>
       </c>
-      <c r="C173" t="s">
-        <v>55</v>
-      </c>
-      <c r="D173">
-        <v>5</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F173" t="s">
-        <v>52</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
-        <v>135</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="G175" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" hidden="1">
+      <c r="A176" t="s">
+        <v>134</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C176" t="s">
         <v>149</v>
       </c>
-      <c r="D174">
-        <v>4</v>
-      </c>
-      <c r="E174" s="5" t="s">
+      <c r="D176">
+        <v>4</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F176" t="s">
+        <v>30</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" hidden="1">
+      <c r="A177" t="s">
+        <v>134</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C177" t="s">
+        <v>62</v>
+      </c>
+      <c r="D177">
+        <v>5</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F174" t="s">
-        <v>31</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
-        <v>135</v>
-      </c>
-      <c r="B175" s="1" t="s">
+      <c r="F177" t="s">
         <v>59</v>
       </c>
-      <c r="C175" t="s">
-        <v>59</v>
-      </c>
-      <c r="D175">
-        <v>5</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F175" t="s">
-        <v>56</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
-        <v>135</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="G177" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" hidden="1">
+      <c r="A178" t="s">
+        <v>134</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C178" t="s">
         <v>150</v>
       </c>
-      <c r="D176">
-        <v>4</v>
-      </c>
-      <c r="E176" s="5" t="s">
+      <c r="D178">
+        <v>4</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F178" t="s">
+        <v>30</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" hidden="1">
+      <c r="A179" t="s">
+        <v>134</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C179" t="s">
+        <v>66</v>
+      </c>
+      <c r="D179">
+        <v>5</v>
+      </c>
+      <c r="E179" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F176" t="s">
-        <v>31</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177" t="s">
-        <v>135</v>
-      </c>
-      <c r="B177" s="1" t="s">
+      <c r="F179" t="s">
         <v>63</v>
       </c>
-      <c r="C177" t="s">
-        <v>63</v>
-      </c>
-      <c r="D177">
-        <v>5</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F177" t="s">
-        <v>60</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178" t="s">
-        <v>135</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="G179" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" hidden="1">
+      <c r="A180" t="s">
+        <v>134</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C180" t="s">
         <v>151</v>
       </c>
-      <c r="D178">
-        <v>4</v>
-      </c>
-      <c r="E178" s="5" t="s">
+      <c r="D180">
+        <v>4</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F180" t="s">
+        <v>30</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" hidden="1">
+      <c r="A181" t="s">
+        <v>134</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C181" t="s">
+        <v>70</v>
+      </c>
+      <c r="D181">
+        <v>5</v>
+      </c>
+      <c r="E181" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F178" t="s">
-        <v>31</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" t="s">
-        <v>135</v>
-      </c>
-      <c r="B179" s="1" t="s">
+      <c r="F181" t="s">
         <v>67</v>
       </c>
-      <c r="C179" t="s">
-        <v>67</v>
-      </c>
-      <c r="D179">
-        <v>5</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F179" t="s">
-        <v>64</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180" t="s">
-        <v>135</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="G181" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" hidden="1">
+      <c r="A182" t="s">
+        <v>134</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C182" t="s">
         <v>152</v>
-      </c>
-      <c r="D180">
-        <v>4</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F180" t="s">
-        <v>31</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181" t="s">
-        <v>135</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C181" t="s">
-        <v>71</v>
-      </c>
-      <c r="D181">
-        <v>5</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F181" t="s">
-        <v>68</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182" t="s">
-        <v>135</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C182" t="s">
-        <v>153</v>
       </c>
       <c r="D182">
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
@@ -5259,446 +5256,446 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" hidden="1">
       <c r="A183" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C183" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D183">
         <v>3</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F183" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" hidden="1">
       <c r="A184" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s">
+        <v>153</v>
+      </c>
+      <c r="D184">
+        <v>4</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F184" t="s">
+        <v>74</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" hidden="1">
+      <c r="A185" t="s">
+        <v>134</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C185" t="s">
+        <v>78</v>
+      </c>
+      <c r="D185">
+        <v>5</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F185" t="s">
+        <v>75</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" hidden="1">
+      <c r="A186" t="s">
+        <v>134</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C186" t="s">
         <v>154</v>
       </c>
-      <c r="D184">
-        <v>4</v>
-      </c>
-      <c r="E184" s="5" t="s">
+      <c r="D186">
+        <v>4</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F186" t="s">
+        <v>74</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" hidden="1">
+      <c r="A187" t="s">
+        <v>134</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C187" t="s">
+        <v>82</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+      <c r="E187" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F184" t="s">
-        <v>75</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185" t="s">
-        <v>135</v>
-      </c>
-      <c r="B185" s="1" t="s">
+      <c r="F187" t="s">
         <v>79</v>
       </c>
-      <c r="C185" t="s">
-        <v>79</v>
-      </c>
-      <c r="D185">
-        <v>5</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F185" t="s">
-        <v>76</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
-      <c r="A186" t="s">
-        <v>135</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="G187" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" hidden="1">
+      <c r="A188" t="s">
+        <v>134</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C188" t="s">
         <v>155</v>
       </c>
-      <c r="D186">
-        <v>4</v>
-      </c>
-      <c r="E186" s="5" t="s">
+      <c r="D188">
+        <v>4</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F188" t="s">
+        <v>74</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" hidden="1">
+      <c r="A189" t="s">
+        <v>134</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+      <c r="E189" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F186" t="s">
-        <v>75</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
-      <c r="A187" t="s">
-        <v>135</v>
-      </c>
-      <c r="B187" s="1" t="s">
+      <c r="F189" t="s">
         <v>83</v>
       </c>
-      <c r="C187" t="s">
-        <v>83</v>
-      </c>
-      <c r="D187">
-        <v>5</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F187" t="s">
-        <v>80</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
-      <c r="A188" t="s">
-        <v>135</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="G189" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" hidden="1">
+      <c r="A190" t="s">
+        <v>134</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C190" t="s">
         <v>156</v>
       </c>
-      <c r="D188">
-        <v>4</v>
-      </c>
-      <c r="E188" s="5" t="s">
+      <c r="D190">
+        <v>4</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F190" t="s">
+        <v>74</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" hidden="1">
+      <c r="A191" t="s">
+        <v>134</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C191" t="s">
+        <v>90</v>
+      </c>
+      <c r="D191">
+        <v>5</v>
+      </c>
+      <c r="E191" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F188" t="s">
-        <v>75</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
-      <c r="A189" t="s">
-        <v>135</v>
-      </c>
-      <c r="B189" s="1" t="s">
+      <c r="F191" t="s">
         <v>87</v>
       </c>
-      <c r="C189" t="s">
-        <v>87</v>
-      </c>
-      <c r="D189">
-        <v>5</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F189" t="s">
-        <v>84</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
-      <c r="A190" t="s">
-        <v>135</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="G191" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" hidden="1">
+      <c r="A192" t="s">
+        <v>134</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C192" t="s">
         <v>157</v>
       </c>
-      <c r="D190">
-        <v>4</v>
-      </c>
-      <c r="E190" s="5" t="s">
+      <c r="D192">
+        <v>4</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F192" t="s">
+        <v>74</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" hidden="1">
+      <c r="A193" t="s">
+        <v>134</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C193" t="s">
+        <v>94</v>
+      </c>
+      <c r="D193">
+        <v>5</v>
+      </c>
+      <c r="E193" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F190" t="s">
-        <v>75</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
-      <c r="A191" t="s">
-        <v>135</v>
-      </c>
-      <c r="B191" s="1" t="s">
+      <c r="F193" t="s">
         <v>91</v>
       </c>
-      <c r="C191" t="s">
-        <v>91</v>
-      </c>
-      <c r="D191">
-        <v>5</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F191" t="s">
-        <v>88</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
-      <c r="A192" t="s">
-        <v>135</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="G193" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" hidden="1">
+      <c r="A194" t="s">
+        <v>134</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C194" t="s">
         <v>158</v>
       </c>
-      <c r="D192">
-        <v>4</v>
-      </c>
-      <c r="E192" s="5" t="s">
+      <c r="D194">
+        <v>4</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F194" t="s">
+        <v>74</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" hidden="1">
+      <c r="A195" t="s">
+        <v>134</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C195" t="s">
+        <v>99</v>
+      </c>
+      <c r="D195">
+        <v>5</v>
+      </c>
+      <c r="E195" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F192" t="s">
-        <v>75</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
-      <c r="A193" t="s">
-        <v>135</v>
-      </c>
-      <c r="B193" s="1" t="s">
+      <c r="F195" t="s">
         <v>95</v>
       </c>
-      <c r="C193" t="s">
-        <v>95</v>
-      </c>
-      <c r="D193">
-        <v>5</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F193" t="s">
-        <v>92</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194" t="s">
-        <v>135</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="G195" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" hidden="1">
+      <c r="A196" t="s">
+        <v>134</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C196" t="s">
         <v>159</v>
       </c>
-      <c r="D194">
-        <v>4</v>
-      </c>
-      <c r="E194" s="5" t="s">
+      <c r="D196">
+        <v>4</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F196" t="s">
+        <v>74</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" hidden="1">
+      <c r="A197" t="s">
+        <v>134</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C197" t="s">
+        <v>103</v>
+      </c>
+      <c r="D197">
+        <v>5</v>
+      </c>
+      <c r="E197" t="s">
         <v>144</v>
       </c>
-      <c r="F194" t="s">
-        <v>75</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195" t="s">
-        <v>135</v>
-      </c>
-      <c r="B195" s="1" t="s">
+      <c r="F197" t="s">
         <v>100</v>
       </c>
-      <c r="C195" t="s">
-        <v>100</v>
-      </c>
-      <c r="D195">
-        <v>5</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F195" t="s">
-        <v>96</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196" t="s">
-        <v>135</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="G197" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" hidden="1">
+      <c r="A198" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C198" t="s">
+        <v>104</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>144</v>
+      </c>
+      <c r="F198" t="s">
+        <v>34</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" hidden="1">
+      <c r="A199" t="s">
+        <v>134</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C199" t="s">
+        <v>105</v>
+      </c>
+      <c r="D199">
+        <v>5</v>
+      </c>
+      <c r="E199" t="s">
+        <v>144</v>
+      </c>
+      <c r="F199" t="s">
+        <v>34</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" hidden="1">
+      <c r="A200" t="s">
+        <v>134</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C200" t="s">
+        <v>106</v>
+      </c>
+      <c r="D200">
+        <v>5</v>
+      </c>
+      <c r="E200" t="s">
+        <v>144</v>
+      </c>
+      <c r="F200" t="s">
+        <v>34</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" hidden="1">
+      <c r="A201" t="s">
+        <v>134</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C201" t="s">
+        <v>107</v>
+      </c>
+      <c r="D201">
+        <v>5</v>
+      </c>
+      <c r="E201" t="s">
+        <v>144</v>
+      </c>
+      <c r="F201" t="s">
+        <v>34</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" hidden="1">
+      <c r="A202" t="s">
         <v>160</v>
-      </c>
-      <c r="D196">
-        <v>4</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F196" t="s">
-        <v>75</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197" t="s">
-        <v>135</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C197" t="s">
-        <v>104</v>
-      </c>
-      <c r="D197">
-        <v>5</v>
-      </c>
-      <c r="E197" t="s">
-        <v>145</v>
-      </c>
-      <c r="F197" t="s">
-        <v>101</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198" t="s">
-        <v>135</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C198" t="s">
-        <v>105</v>
-      </c>
-      <c r="D198">
-        <v>5</v>
-      </c>
-      <c r="E198" t="s">
-        <v>145</v>
-      </c>
-      <c r="F198" t="s">
-        <v>35</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199" t="s">
-        <v>135</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C199" t="s">
-        <v>106</v>
-      </c>
-      <c r="D199">
-        <v>5</v>
-      </c>
-      <c r="E199" t="s">
-        <v>145</v>
-      </c>
-      <c r="F199" t="s">
-        <v>35</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200" t="s">
-        <v>135</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C200" t="s">
-        <v>107</v>
-      </c>
-      <c r="D200">
-        <v>5</v>
-      </c>
-      <c r="E200" t="s">
-        <v>145</v>
-      </c>
-      <c r="F200" t="s">
-        <v>35</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201" t="s">
-        <v>135</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C201" t="s">
-        <v>108</v>
-      </c>
-      <c r="D201">
-        <v>5</v>
-      </c>
-      <c r="E201" t="s">
-        <v>145</v>
-      </c>
-      <c r="F201" t="s">
-        <v>35</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
-      <c r="A202" t="s">
-        <v>161</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>8</v>
@@ -5710,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>11</v>
@@ -5718,19 +5715,19 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F203" t="s">
         <v>8</v>
@@ -5739,21 +5736,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" hidden="1">
       <c r="A204" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F204" t="s">
         <v>18</v>
@@ -5762,412 +5759,412 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" hidden="1">
       <c r="A205" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C205" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D205">
         <v>3</v>
       </c>
       <c r="E205" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F205" t="s">
+        <v>24</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" hidden="1">
+      <c r="A206" t="s">
+        <v>160</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C206" t="s">
         <v>167</v>
       </c>
-      <c r="F205" t="s">
-        <v>25</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7">
-      <c r="A206" t="s">
-        <v>161</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C206" t="s">
+      <c r="D206">
+        <v>4</v>
+      </c>
+      <c r="E206" t="s">
         <v>168</v>
       </c>
-      <c r="D206">
-        <v>4</v>
-      </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
+        <v>30</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" hidden="1">
+      <c r="A207" t="s">
+        <v>160</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C207" t="s">
+        <v>39</v>
+      </c>
+      <c r="D207">
+        <v>5</v>
+      </c>
+      <c r="E207" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F206" t="s">
-        <v>31</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
-      <c r="A207" t="s">
-        <v>161</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C207" t="s">
-        <v>40</v>
-      </c>
-      <c r="D207">
-        <v>5</v>
-      </c>
-      <c r="E207" s="5" t="s">
+      <c r="F207" t="s">
+        <v>34</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" hidden="1">
+      <c r="A208" t="s">
+        <v>160</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C208" t="s">
         <v>170</v>
       </c>
-      <c r="F207" t="s">
-        <v>35</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
-      <c r="A208" t="s">
-        <v>161</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C208" t="s">
+      <c r="D208">
+        <v>4</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F208" t="s">
+        <v>30</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" hidden="1">
+      <c r="A209" t="s">
+        <v>160</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C209" t="s">
+        <v>46</v>
+      </c>
+      <c r="D209">
+        <v>5</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F209" t="s">
+        <v>43</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" hidden="1">
+      <c r="A210" t="s">
+        <v>160</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C210" t="s">
         <v>171</v>
       </c>
-      <c r="D208">
-        <v>4</v>
-      </c>
-      <c r="E208" s="5" t="s">
+      <c r="D210">
+        <v>4</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F210" t="s">
+        <v>30</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" hidden="1">
+      <c r="A211" t="s">
+        <v>160</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C211" t="s">
+        <v>50</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F208" t="s">
-        <v>31</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7">
-      <c r="A209" t="s">
-        <v>161</v>
-      </c>
-      <c r="B209" s="1" t="s">
+      <c r="F211" t="s">
         <v>47</v>
       </c>
-      <c r="C209" t="s">
-        <v>47</v>
-      </c>
-      <c r="D209">
-        <v>5</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F209" t="s">
-        <v>44</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
-      <c r="A210" t="s">
-        <v>161</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C210" t="s">
+      <c r="G211" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" hidden="1">
+      <c r="A212" t="s">
+        <v>160</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C212" t="s">
         <v>172</v>
       </c>
-      <c r="D210">
-        <v>4</v>
-      </c>
-      <c r="E210" s="5" t="s">
+      <c r="D212">
+        <v>4</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F212" t="s">
+        <v>30</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" hidden="1">
+      <c r="A213" t="s">
+        <v>160</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C213" t="s">
+        <v>54</v>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+      <c r="E213" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F210" t="s">
-        <v>31</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
-      <c r="A211" t="s">
-        <v>161</v>
-      </c>
-      <c r="B211" s="1" t="s">
+      <c r="F213" t="s">
         <v>51</v>
       </c>
-      <c r="C211" t="s">
-        <v>51</v>
-      </c>
-      <c r="D211">
-        <v>5</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F211" t="s">
-        <v>48</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7">
-      <c r="A212" t="s">
-        <v>161</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C212" t="s">
+      <c r="G213" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" hidden="1">
+      <c r="A214" t="s">
+        <v>160</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C214" t="s">
+        <v>56</v>
+      </c>
+      <c r="D214">
+        <v>4</v>
+      </c>
+      <c r="E214" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F214" t="s">
+        <v>30</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" hidden="1">
+      <c r="A215" t="s">
+        <v>160</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C215" t="s">
+        <v>58</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F215" t="s">
+        <v>55</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" hidden="1">
+      <c r="A216" t="s">
+        <v>160</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C216" t="s">
         <v>173</v>
       </c>
-      <c r="D212">
-        <v>4</v>
-      </c>
-      <c r="E212" s="5" t="s">
+      <c r="D216">
+        <v>4</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F216" t="s">
+        <v>30</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" hidden="1">
+      <c r="A217" t="s">
+        <v>160</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C217" t="s">
+        <v>62</v>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+      <c r="E217" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F212" t="s">
-        <v>31</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7">
-      <c r="A213" t="s">
-        <v>161</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C213" t="s">
-        <v>55</v>
-      </c>
-      <c r="D213">
-        <v>5</v>
-      </c>
-      <c r="E213" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F213" t="s">
-        <v>52</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7">
-      <c r="A214" t="s">
-        <v>161</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C214" t="s">
-        <v>57</v>
-      </c>
-      <c r="D214">
-        <v>4</v>
-      </c>
-      <c r="E214" s="5" t="s">
+      <c r="F217" t="s">
+        <v>59</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" hidden="1">
+      <c r="A218" t="s">
+        <v>160</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C218" t="s">
+        <v>174</v>
+      </c>
+      <c r="D218">
+        <v>4</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F218" t="s">
+        <v>30</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" hidden="1">
+      <c r="A219" t="s">
+        <v>160</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C219" t="s">
+        <v>66</v>
+      </c>
+      <c r="D219">
+        <v>5</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F214" t="s">
-        <v>31</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
-      <c r="A215" t="s">
-        <v>161</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C215" t="s">
-        <v>59</v>
-      </c>
-      <c r="D215">
-        <v>5</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F215" t="s">
-        <v>56</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
-      <c r="A216" t="s">
-        <v>161</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C216" t="s">
-        <v>174</v>
-      </c>
-      <c r="D216">
-        <v>4</v>
-      </c>
-      <c r="E216" s="5" t="s">
+      <c r="F219" t="s">
+        <v>63</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" hidden="1">
+      <c r="A220" t="s">
+        <v>160</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C220" t="s">
+        <v>175</v>
+      </c>
+      <c r="D220">
+        <v>4</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F220" t="s">
+        <v>30</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" hidden="1">
+      <c r="A221" t="s">
+        <v>160</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C221" t="s">
+        <v>70</v>
+      </c>
+      <c r="D221">
+        <v>5</v>
+      </c>
+      <c r="E221" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F216" t="s">
-        <v>31</v>
-      </c>
-      <c r="G216" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
-      <c r="A217" t="s">
-        <v>161</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C217" t="s">
-        <v>63</v>
-      </c>
-      <c r="D217">
-        <v>5</v>
-      </c>
-      <c r="E217" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F217" t="s">
-        <v>60</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
-      <c r="A218" t="s">
-        <v>161</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C218" t="s">
-        <v>175</v>
-      </c>
-      <c r="D218">
-        <v>4</v>
-      </c>
-      <c r="E218" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F218" t="s">
-        <v>31</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
-      <c r="A219" t="s">
-        <v>161</v>
-      </c>
-      <c r="B219" s="1" t="s">
+      <c r="F221" t="s">
         <v>67</v>
       </c>
-      <c r="C219" t="s">
-        <v>67</v>
-      </c>
-      <c r="D219">
-        <v>5</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F219" t="s">
-        <v>64</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
-      <c r="A220" t="s">
-        <v>161</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C220" t="s">
+      <c r="G221" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" hidden="1">
+      <c r="A222" t="s">
+        <v>160</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C222" t="s">
         <v>176</v>
-      </c>
-      <c r="D220">
-        <v>4</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F220" t="s">
-        <v>31</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
-      <c r="A221" t="s">
-        <v>161</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C221" t="s">
-        <v>71</v>
-      </c>
-      <c r="D221">
-        <v>5</v>
-      </c>
-      <c r="E221" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F221" t="s">
-        <v>68</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
-      <c r="A222" t="s">
-        <v>161</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C222" t="s">
-        <v>177</v>
       </c>
       <c r="D222">
         <v>2</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F222" t="s">
         <v>18</v>
@@ -6176,469 +6173,469 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" hidden="1">
       <c r="A223" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C223" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D223">
         <v>3</v>
       </c>
       <c r="E223" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F223" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" hidden="1">
       <c r="A224" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C224" t="s">
+        <v>177</v>
+      </c>
+      <c r="D224">
+        <v>4</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F224" t="s">
+        <v>74</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" hidden="1">
+      <c r="A225" t="s">
+        <v>160</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C225" t="s">
+        <v>78</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F225" t="s">
+        <v>75</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" hidden="1">
+      <c r="A226" t="s">
+        <v>160</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C226" t="s">
         <v>178</v>
       </c>
-      <c r="D224">
-        <v>4</v>
-      </c>
-      <c r="E224" s="5" t="s">
+      <c r="D226">
+        <v>4</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F226" t="s">
+        <v>74</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" hidden="1">
+      <c r="A227" t="s">
+        <v>160</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C227" t="s">
+        <v>82</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F224" t="s">
-        <v>75</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
-      <c r="A225" t="s">
-        <v>161</v>
-      </c>
-      <c r="B225" s="1" t="s">
+      <c r="F227" t="s">
         <v>79</v>
       </c>
-      <c r="C225" t="s">
-        <v>79</v>
-      </c>
-      <c r="D225">
-        <v>5</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F225" t="s">
-        <v>76</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
-      <c r="A226" t="s">
-        <v>161</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C226" t="s">
+      <c r="G227" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" hidden="1">
+      <c r="A228" t="s">
+        <v>160</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C228" t="s">
+        <v>84</v>
+      </c>
+      <c r="D228">
+        <v>4</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F228" t="s">
+        <v>74</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" hidden="1">
+      <c r="A229" t="s">
+        <v>160</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C229" t="s">
+        <v>86</v>
+      </c>
+      <c r="D229">
+        <v>5</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F229" t="s">
+        <v>83</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" hidden="1">
+      <c r="A230" t="s">
+        <v>160</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C230" t="s">
         <v>179</v>
       </c>
-      <c r="D226">
-        <v>4</v>
-      </c>
-      <c r="E226" s="5" t="s">
+      <c r="D230">
+        <v>4</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F230" t="s">
+        <v>74</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" hidden="1">
+      <c r="A231" t="s">
+        <v>160</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C231" t="s">
+        <v>90</v>
+      </c>
+      <c r="D231">
+        <v>5</v>
+      </c>
+      <c r="E231" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F226" t="s">
-        <v>75</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="A227" t="s">
-        <v>161</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C227" t="s">
-        <v>83</v>
-      </c>
-      <c r="D227">
-        <v>5</v>
-      </c>
-      <c r="E227" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F227" t="s">
-        <v>80</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" t="s">
-        <v>161</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C228" t="s">
-        <v>85</v>
-      </c>
-      <c r="D228">
-        <v>4</v>
-      </c>
-      <c r="E228" s="5" t="s">
+      <c r="F231" t="s">
+        <v>87</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" hidden="1">
+      <c r="A232" t="s">
+        <v>160</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C232" t="s">
+        <v>180</v>
+      </c>
+      <c r="D232">
+        <v>4</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F232" t="s">
+        <v>74</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" hidden="1">
+      <c r="A233" t="s">
+        <v>160</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C233" t="s">
+        <v>94</v>
+      </c>
+      <c r="D233">
+        <v>5</v>
+      </c>
+      <c r="E233" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F228" t="s">
-        <v>75</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
-      <c r="A229" t="s">
-        <v>161</v>
-      </c>
-      <c r="B229" s="1" t="s">
+      <c r="F233" t="s">
+        <v>91</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" hidden="1">
+      <c r="A234" t="s">
+        <v>160</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C234" t="s">
+        <v>181</v>
+      </c>
+      <c r="D234">
+        <v>4</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F234" t="s">
+        <v>74</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" hidden="1">
+      <c r="A235" t="s">
+        <v>160</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C235" t="s">
+        <v>99</v>
+      </c>
+      <c r="D235">
+        <v>5</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F235" t="s">
+        <v>95</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" hidden="1">
+      <c r="A236" t="s">
+        <v>160</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C236" t="s">
+        <v>182</v>
+      </c>
+      <c r="D236">
+        <v>4</v>
+      </c>
+      <c r="E236" t="s">
+        <v>168</v>
+      </c>
+      <c r="F236" t="s">
+        <v>74</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" hidden="1">
+      <c r="A237" t="s">
+        <v>160</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C237" t="s">
+        <v>103</v>
+      </c>
+      <c r="D237">
+        <v>5</v>
+      </c>
+      <c r="E237" t="s">
+        <v>169</v>
+      </c>
+      <c r="F237" t="s">
+        <v>100</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" hidden="1">
+      <c r="A238" t="s">
+        <v>160</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C238" t="s">
+        <v>104</v>
+      </c>
+      <c r="D238">
+        <v>5</v>
+      </c>
+      <c r="E238" t="s">
+        <v>169</v>
+      </c>
+      <c r="F238" t="s">
+        <v>34</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" hidden="1">
+      <c r="A239" t="s">
+        <v>160</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C239" t="s">
+        <v>105</v>
+      </c>
+      <c r="D239">
+        <v>5</v>
+      </c>
+      <c r="E239" t="s">
+        <v>169</v>
+      </c>
+      <c r="F239" t="s">
+        <v>34</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" hidden="1">
+      <c r="A240" t="s">
+        <v>160</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C240" t="s">
+        <v>106</v>
+      </c>
+      <c r="D240">
+        <v>5</v>
+      </c>
+      <c r="E240" t="s">
+        <v>169</v>
+      </c>
+      <c r="F240" t="s">
+        <v>34</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" hidden="1">
+      <c r="A241" t="s">
+        <v>160</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C241" t="s">
+        <v>107</v>
+      </c>
+      <c r="D241">
+        <v>5</v>
+      </c>
+      <c r="E241" t="s">
+        <v>169</v>
+      </c>
+      <c r="F241" t="s">
+        <v>34</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" hidden="1">
+      <c r="A242" t="s">
+        <v>183</v>
+      </c>
+      <c r="B242" t="s">
         <v>87</v>
       </c>
-      <c r="C229" t="s">
-        <v>87</v>
-      </c>
-      <c r="D229">
-        <v>5</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F229" t="s">
-        <v>84</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
-      <c r="A230" t="s">
-        <v>161</v>
-      </c>
-      <c r="B230" s="1" t="s">
+      <c r="C242" t="s">
         <v>88</v>
       </c>
-      <c r="C230" t="s">
-        <v>180</v>
-      </c>
-      <c r="D230">
-        <v>4</v>
-      </c>
-      <c r="E230" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F230" t="s">
-        <v>75</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
-      <c r="A231" t="s">
-        <v>161</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C231" t="s">
-        <v>91</v>
-      </c>
-      <c r="D231">
-        <v>5</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F231" t="s">
-        <v>88</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" t="s">
-        <v>161</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C232" t="s">
-        <v>181</v>
-      </c>
-      <c r="D232">
-        <v>4</v>
-      </c>
-      <c r="E232" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F232" t="s">
-        <v>75</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="A233" t="s">
-        <v>161</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C233" t="s">
-        <v>95</v>
-      </c>
-      <c r="D233">
-        <v>5</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F233" t="s">
-        <v>92</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" t="s">
-        <v>161</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C234" t="s">
-        <v>182</v>
-      </c>
-      <c r="D234">
-        <v>4</v>
-      </c>
-      <c r="E234" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F234" t="s">
-        <v>75</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="A235" t="s">
-        <v>161</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C235" t="s">
-        <v>100</v>
-      </c>
-      <c r="D235">
-        <v>5</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F235" t="s">
-        <v>96</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" t="s">
-        <v>161</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C236" t="s">
-        <v>183</v>
-      </c>
-      <c r="D236">
-        <v>4</v>
-      </c>
-      <c r="E236" t="s">
-        <v>169</v>
-      </c>
-      <c r="F236" t="s">
-        <v>75</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="A237" t="s">
-        <v>161</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C237" t="s">
-        <v>104</v>
-      </c>
-      <c r="D237">
-        <v>5</v>
-      </c>
-      <c r="E237" t="s">
-        <v>170</v>
-      </c>
-      <c r="F237" t="s">
-        <v>101</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
-      <c r="A238" t="s">
-        <v>161</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C238" t="s">
-        <v>105</v>
-      </c>
-      <c r="D238">
-        <v>5</v>
-      </c>
-      <c r="E238" t="s">
-        <v>170</v>
-      </c>
-      <c r="F238" t="s">
-        <v>35</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
-      <c r="A239" t="s">
-        <v>161</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C239" t="s">
-        <v>106</v>
-      </c>
-      <c r="D239">
-        <v>5</v>
-      </c>
-      <c r="E239" t="s">
-        <v>170</v>
-      </c>
-      <c r="F239" t="s">
-        <v>35</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
-      <c r="A240" t="s">
-        <v>161</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C240" t="s">
-        <v>107</v>
-      </c>
-      <c r="D240">
-        <v>5</v>
-      </c>
-      <c r="E240" t="s">
-        <v>170</v>
-      </c>
-      <c r="F240" t="s">
-        <v>35</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
-      <c r="A241" t="s">
-        <v>161</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C241" t="s">
-        <v>108</v>
-      </c>
-      <c r="D241">
-        <v>5</v>
-      </c>
-      <c r="E241" t="s">
-        <v>170</v>
-      </c>
-      <c r="F241" t="s">
-        <v>35</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
-      <c r="A242" t="s">
+      <c r="D242">
+        <v>4</v>
+      </c>
+      <c r="E242" t="s">
         <v>184</v>
       </c>
-      <c r="B242" t="s">
-        <v>88</v>
-      </c>
-      <c r="C242" t="s">
-        <v>89</v>
-      </c>
-      <c r="D242">
-        <v>4</v>
-      </c>
-      <c r="E242" t="s">
-        <v>185</v>
-      </c>
       <c r="F242" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G242" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" hidden="1">
       <c r="A243" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B243">
         <v>10114</v>
@@ -6650,30 +6647,30 @@
         <v>5</v>
       </c>
       <c r="E243" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G243" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" hidden="1">
       <c r="A244" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B244" t="s">
         <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D244">
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G244" t="b">
         <v>1</v>
@@ -6681,19 +6678,19 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B245" t="s">
         <v>18</v>
       </c>
       <c r="C245" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="D245">
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F245" t="s">
         <v>8</v>
@@ -6702,21 +6699,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" hidden="1">
       <c r="A246" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B246" t="s">
+        <v>24</v>
+      </c>
+      <c r="C246" t="s">
         <v>25</v>
-      </c>
-      <c r="C246" t="s">
-        <v>26</v>
       </c>
       <c r="D246">
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F246" t="s">
         <v>18</v>
@@ -6725,55 +6722,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" hidden="1">
       <c r="A247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B247" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D247">
         <v>3</v>
       </c>
       <c r="E247" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F247" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G247" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" hidden="1">
       <c r="A248" t="s">
+        <v>183</v>
+      </c>
+      <c r="B248" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" t="s">
+        <v>35</v>
+      </c>
+      <c r="D248">
+        <v>4</v>
+      </c>
+      <c r="E248" t="s">
         <v>184</v>
       </c>
-      <c r="B248" t="s">
-        <v>35</v>
-      </c>
-      <c r="C248" t="s">
-        <v>36</v>
-      </c>
-      <c r="D248">
-        <v>4</v>
-      </c>
-      <c r="E248" t="s">
-        <v>185</v>
-      </c>
       <c r="F248" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G248" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" hidden="1">
       <c r="A249" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B249">
         <v>14022</v>
@@ -6785,41 +6782,41 @@
         <v>5</v>
       </c>
       <c r="E249" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F249" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G249" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" hidden="1">
       <c r="A250" t="s">
+        <v>183</v>
+      </c>
+      <c r="B250" t="s">
+        <v>43</v>
+      </c>
+      <c r="C250" t="s">
+        <v>44</v>
+      </c>
+      <c r="D250">
+        <v>4</v>
+      </c>
+      <c r="E250" t="s">
         <v>184</v>
       </c>
-      <c r="B250" t="s">
-        <v>44</v>
-      </c>
-      <c r="C250" t="s">
-        <v>45</v>
-      </c>
-      <c r="D250">
-        <v>4</v>
-      </c>
-      <c r="E250" t="s">
-        <v>185</v>
-      </c>
       <c r="F250" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G250" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" hidden="1">
       <c r="A251" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B251">
         <v>14053</v>
@@ -6831,41 +6828,41 @@
         <v>5</v>
       </c>
       <c r="E251" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G251" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" hidden="1">
       <c r="A252" t="s">
+        <v>183</v>
+      </c>
+      <c r="B252" t="s">
+        <v>47</v>
+      </c>
+      <c r="C252" t="s">
+        <v>48</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+      <c r="E252" t="s">
         <v>184</v>
       </c>
-      <c r="B252" t="s">
-        <v>48</v>
-      </c>
-      <c r="C252" t="s">
-        <v>49</v>
-      </c>
-      <c r="D252">
-        <v>4</v>
-      </c>
-      <c r="E252" t="s">
-        <v>185</v>
-      </c>
       <c r="F252" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G252" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" hidden="1">
       <c r="A253" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B253">
         <v>14023</v>
@@ -6877,41 +6874,41 @@
         <v>5</v>
       </c>
       <c r="E253" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F253" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G253" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" hidden="1">
       <c r="A254" t="s">
+        <v>183</v>
+      </c>
+      <c r="B254" t="s">
+        <v>51</v>
+      </c>
+      <c r="C254" t="s">
+        <v>52</v>
+      </c>
+      <c r="D254">
+        <v>4</v>
+      </c>
+      <c r="E254" t="s">
         <v>184</v>
       </c>
-      <c r="B254" t="s">
-        <v>52</v>
-      </c>
-      <c r="C254" t="s">
-        <v>53</v>
-      </c>
-      <c r="D254">
-        <v>4</v>
-      </c>
-      <c r="E254" t="s">
-        <v>185</v>
-      </c>
       <c r="F254" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G254" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" hidden="1">
       <c r="A255" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B255">
         <v>14000</v>
@@ -6923,41 +6920,41 @@
         <v>5</v>
       </c>
       <c r="E255" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F255" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G255" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" hidden="1">
       <c r="A256" t="s">
+        <v>183</v>
+      </c>
+      <c r="B256" t="s">
+        <v>55</v>
+      </c>
+      <c r="C256" t="s">
+        <v>56</v>
+      </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
+      <c r="E256" t="s">
         <v>184</v>
       </c>
-      <c r="B256" t="s">
-        <v>56</v>
-      </c>
-      <c r="C256" t="s">
-        <v>57</v>
-      </c>
-      <c r="D256">
-        <v>4</v>
-      </c>
-      <c r="E256" t="s">
-        <v>185</v>
-      </c>
       <c r="F256" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G256" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" hidden="1">
       <c r="A257" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B257">
         <v>14110</v>
@@ -6969,41 +6966,41 @@
         <v>5</v>
       </c>
       <c r="E257" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G257" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" hidden="1">
       <c r="A258" t="s">
+        <v>183</v>
+      </c>
+      <c r="B258" t="s">
+        <v>59</v>
+      </c>
+      <c r="C258" t="s">
+        <v>60</v>
+      </c>
+      <c r="D258">
+        <v>4</v>
+      </c>
+      <c r="E258" t="s">
         <v>184</v>
       </c>
-      <c r="B258" t="s">
-        <v>60</v>
-      </c>
-      <c r="C258" t="s">
-        <v>61</v>
-      </c>
-      <c r="D258">
-        <v>4</v>
-      </c>
-      <c r="E258" t="s">
-        <v>185</v>
-      </c>
       <c r="F258" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G258" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" hidden="1">
       <c r="A259" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B259">
         <v>14080</v>
@@ -7015,41 +7012,41 @@
         <v>5</v>
       </c>
       <c r="E259" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F259" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G259" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" hidden="1">
       <c r="A260" t="s">
+        <v>183</v>
+      </c>
+      <c r="B260" t="s">
+        <v>63</v>
+      </c>
+      <c r="C260" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260">
+        <v>4</v>
+      </c>
+      <c r="E260" t="s">
         <v>184</v>
       </c>
-      <c r="B260" t="s">
-        <v>64</v>
-      </c>
-      <c r="C260" t="s">
-        <v>65</v>
-      </c>
-      <c r="D260">
-        <v>4</v>
-      </c>
-      <c r="E260" t="s">
-        <v>185</v>
-      </c>
       <c r="F260" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G260" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" hidden="1">
       <c r="A261" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B261">
         <v>14025</v>
@@ -7061,41 +7058,41 @@
         <v>5</v>
       </c>
       <c r="E261" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F261" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G261" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" hidden="1">
       <c r="A262" t="s">
+        <v>183</v>
+      </c>
+      <c r="B262" t="s">
+        <v>67</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262">
+        <v>4</v>
+      </c>
+      <c r="E262" t="s">
         <v>184</v>
       </c>
-      <c r="B262" t="s">
-        <v>68</v>
-      </c>
-      <c r="C262" t="s">
-        <v>69</v>
-      </c>
-      <c r="D262">
-        <v>4</v>
-      </c>
-      <c r="E262" t="s">
-        <v>185</v>
-      </c>
       <c r="F262" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G262" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" hidden="1">
       <c r="A263" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B263">
         <v>14050</v>
@@ -7107,30 +7104,30 @@
         <v>5</v>
       </c>
       <c r="E263" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F263" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G263" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" hidden="1">
       <c r="A264" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B264" t="s">
+        <v>71</v>
+      </c>
+      <c r="C264" t="s">
         <v>72</v>
-      </c>
-      <c r="C264" t="s">
-        <v>73</v>
       </c>
       <c r="D264">
         <v>2</v>
       </c>
       <c r="E264" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F264" t="s">
         <v>18</v>
@@ -7139,55 +7136,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" hidden="1">
       <c r="A265" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B265" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C265" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D265">
         <v>3</v>
       </c>
       <c r="E265" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F265" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G265" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" hidden="1">
       <c r="A266" t="s">
+        <v>183</v>
+      </c>
+      <c r="B266" t="s">
+        <v>75</v>
+      </c>
+      <c r="C266" t="s">
+        <v>76</v>
+      </c>
+      <c r="D266">
+        <v>4</v>
+      </c>
+      <c r="E266" t="s">
         <v>184</v>
       </c>
-      <c r="B266" t="s">
-        <v>76</v>
-      </c>
-      <c r="C266" t="s">
-        <v>77</v>
-      </c>
-      <c r="D266">
-        <v>4</v>
-      </c>
-      <c r="E266" t="s">
-        <v>185</v>
-      </c>
       <c r="F266" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G266" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" hidden="1">
       <c r="A267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B267">
         <v>10106</v>
@@ -7199,41 +7196,41 @@
         <v>5</v>
       </c>
       <c r="E267" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G267" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" hidden="1">
       <c r="A268" t="s">
+        <v>183</v>
+      </c>
+      <c r="B268" t="s">
+        <v>79</v>
+      </c>
+      <c r="C268" t="s">
+        <v>80</v>
+      </c>
+      <c r="D268">
+        <v>4</v>
+      </c>
+      <c r="E268" t="s">
         <v>184</v>
       </c>
-      <c r="B268" t="s">
-        <v>80</v>
-      </c>
-      <c r="C268" t="s">
-        <v>81</v>
-      </c>
-      <c r="D268">
-        <v>4</v>
-      </c>
-      <c r="E268" t="s">
-        <v>185</v>
-      </c>
       <c r="F268" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G268" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" hidden="1">
       <c r="A269" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B269">
         <v>10000</v>
@@ -7245,41 +7242,41 @@
         <v>5</v>
       </c>
       <c r="E269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F269" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G269" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" hidden="1">
       <c r="A270" t="s">
+        <v>183</v>
+      </c>
+      <c r="B270" t="s">
+        <v>83</v>
+      </c>
+      <c r="C270" t="s">
+        <v>84</v>
+      </c>
+      <c r="D270">
+        <v>4</v>
+      </c>
+      <c r="E270" t="s">
         <v>184</v>
       </c>
-      <c r="B270" t="s">
-        <v>84</v>
-      </c>
-      <c r="C270" t="s">
-        <v>85</v>
-      </c>
-      <c r="D270">
-        <v>4</v>
-      </c>
-      <c r="E270" t="s">
-        <v>185</v>
-      </c>
       <c r="F270" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G270" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" hidden="1">
       <c r="A271" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B271">
         <v>10105</v>
@@ -7291,18 +7288,18 @@
         <v>5</v>
       </c>
       <c r="E271" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F271" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G271" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" hidden="1">
       <c r="A272" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B272">
         <v>10112</v>
@@ -7314,41 +7311,41 @@
         <v>5</v>
       </c>
       <c r="E272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F272" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G272" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" hidden="1">
       <c r="A273" t="s">
+        <v>183</v>
+      </c>
+      <c r="B273" t="s">
+        <v>91</v>
+      </c>
+      <c r="C273" t="s">
+        <v>92</v>
+      </c>
+      <c r="D273">
+        <v>4</v>
+      </c>
+      <c r="E273" t="s">
         <v>184</v>
       </c>
-      <c r="B273" t="s">
-        <v>92</v>
-      </c>
-      <c r="C273" t="s">
-        <v>93</v>
-      </c>
-      <c r="D273">
-        <v>4</v>
-      </c>
-      <c r="E273" t="s">
-        <v>185</v>
-      </c>
       <c r="F273" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G273" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" hidden="1">
       <c r="A274" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B274">
         <v>10104</v>
@@ -7360,41 +7357,41 @@
         <v>5</v>
       </c>
       <c r="E274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F274" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G274" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" hidden="1">
       <c r="A275" t="s">
+        <v>183</v>
+      </c>
+      <c r="B275" t="s">
+        <v>95</v>
+      </c>
+      <c r="C275" t="s">
+        <v>96</v>
+      </c>
+      <c r="D275">
+        <v>4</v>
+      </c>
+      <c r="E275" t="s">
         <v>184</v>
       </c>
-      <c r="B275" t="s">
-        <v>96</v>
-      </c>
-      <c r="C275" t="s">
-        <v>97</v>
-      </c>
-      <c r="D275">
-        <v>4</v>
-      </c>
-      <c r="E275" t="s">
-        <v>185</v>
-      </c>
       <c r="F275" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G275" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" hidden="1">
       <c r="A276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B276">
         <v>10036</v>
@@ -7406,41 +7403,41 @@
         <v>5</v>
       </c>
       <c r="E276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F276" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G276" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" hidden="1">
       <c r="A277" t="s">
+        <v>183</v>
+      </c>
+      <c r="B277" t="s">
+        <v>100</v>
+      </c>
+      <c r="C277" t="s">
+        <v>101</v>
+      </c>
+      <c r="D277">
+        <v>4</v>
+      </c>
+      <c r="E277" t="s">
         <v>184</v>
       </c>
-      <c r="B277" t="s">
-        <v>101</v>
-      </c>
-      <c r="C277" t="s">
-        <v>102</v>
-      </c>
-      <c r="D277">
-        <v>4</v>
-      </c>
-      <c r="E277" t="s">
-        <v>185</v>
-      </c>
       <c r="F277" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G277" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" hidden="1">
       <c r="A278" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B278">
         <v>10190</v>
@@ -7452,18 +7449,18 @@
         <v>5</v>
       </c>
       <c r="E278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F278" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" hidden="1">
       <c r="A279" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B279">
         <v>10110</v>
@@ -7475,18 +7472,18 @@
         <v>5</v>
       </c>
       <c r="E279" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F279" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G279" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" hidden="1">
       <c r="A280" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B280">
         <v>10111</v>
@@ -7498,18 +7495,18 @@
         <v>5</v>
       </c>
       <c r="E280" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F280" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G280" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" hidden="1">
       <c r="A281" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B281">
         <v>10113</v>
@@ -7521,17 +7518,22 @@
         <v>5</v>
       </c>
       <c r="E281" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F281" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G281" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G121" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:G281" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="RSK"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="0"/>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C3141-5DAF-4856-AFAD-F5F555E1EDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D288609-063B-4D66-9900-1B0067F50873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="7845" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,10 +111,10 @@
     <t>UZO</t>
   </si>
   <si>
-    <t>123456</t>
-  </si>
-  <si>
     <t>Utopian Zone</t>
+  </si>
+  <si>
+    <t>UPO</t>
   </si>
 </sst>
 </file>
@@ -133,7 +133,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="18"/>
@@ -706,7 +706,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -726,7 +726,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>123456</v>

--- a/mosip_master/xlsx/location.xlsx
+++ b/mosip_master/xlsx/location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D288609-063B-4D66-9900-1B0067F50873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C62625-1FDF-405F-9823-361D24FCC53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>123456</v>
+        <v>12345</v>
       </c>
       <c r="D7">
         <v>5</v>
